--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C678"/>
+  <dimension ref="A1:C684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -11949,6 +11949,108 @@
         </is>
       </c>
     </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>settings.row.window_mode</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>창 모드</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>settings.value.window_windowed</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Windowed</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>창</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>settings.value.window_borderless</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Borderless</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>테두리 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>settings.value.window_exclusive</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Exclusive</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>전체 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>settings.value.auto</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>ui.skip_hold</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Hold to skip</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>길게 눌러 건너뛰기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C684"/>
+  <dimension ref="A1:C707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>뒤쪽에</t>
+          <t>뒤로</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>적용하다</t>
+          <t>적용</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>뒤쪽에</t>
+          <t>뒤로</t>
         </is>
       </c>
     </row>
@@ -12048,6 +12048,397 @@
       <c r="C684" t="inlineStr">
         <is>
           <t>길게 눌러 건너뛰기</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>settings.row.text_speed</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Text speed</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>글자 속도</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>settings.row.shake</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Screen shake</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>화면 흔들림</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>settings.row.qte_assist</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>QTE assist</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>QTE 보조</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>settings.value.speed_slow</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>느리게</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>settings.value.speed_normal</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>settings.value.speed_fast</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>빠르게</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>settings.value.on</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>On</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>켜짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>settings.value.off</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>꺼짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>settings.line.cps</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Characters per second</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>초당 글자 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>settings.line.monitor</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>모니터</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>settings.line.window_size</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Window size</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>창 크기</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>settings.help.vol_ui</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>How loud menu clicks and other interface sounds are.</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>메뉴 소리와 인터페이스 효과음의 크기입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>settings.help.vol_sfx</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>How loud hits, footsteps and other game sounds are.</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>타격음, 발소리 등 게임 효과음의 크기입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>settings.help.vol_bgm</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>How loud the music is.</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>배경 음악의 크기입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>settings.help.text_speed</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>How fast dialogue text appears.</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>대사가 나타나는 속도입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>settings.help.shake</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Turns the screen shake on hits on or off.</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>공격을 받을 때 화면이 흔들리는 효과를 켜거나 끕니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>settings.help.qte_assist</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Planned: more forgiving timing on button prompts.</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>예정: 버튼 입력 타이밍 판정을 더 너그럽게 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>settings.help.window</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Windowed, borderless fullscreen, or exclusive fullscreen.</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>창 모드, 테두리 없는 전체 화면, 전용 전체 화면 중에서 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>settings.help.scale</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>How many times the picture is enlarged in a window. Only used when windowed.</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>창 모드에서 화면을 몇 배로 키울지 정합니다. 창 모드에서만 쓰입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>settings.help.language</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Language of all text in the game.</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>게임의 모든 글자 언어입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>settings.help.apply</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Saves your changes and applies them now. Back leaves without saving.</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>변경 사항을 저장하고 지금 적용합니다. 뒤로 가면 저장하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>settings.lang.korean</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>한국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>settings.lang.english</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C664"/>
+  <dimension ref="A1:C686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -11711,6 +11711,380 @@
         </is>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>status.desc.poison.data</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Lose {tick} HP each turn, then 1 stack fades ({stacks} stacks, max {max}).{mods}</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>매 턴 {tick} HP를 잃고, 중첩이 1 줄어듭니다 ({stacks}중첩, 최대 {max}).{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>status.desc.poison</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Lose HP equal to its stacks each turn, then 1 stack fades. Stacks up to {max}.{mods}</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>매 턴 중첩 수만큼 HP를 잃고, 중첩이 1 줄어듭니다. 최대 {max}중첩.{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>status.desc.bleed.data</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Lose {tick} HP each time you act ({stacks} stacks, max {max}), for {turns} more turns.{mods}</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>행동할 때마다 {tick} HP를 잃습니다 ({stacks}중첩, 최대 {max}). {turns}턴 더 지속.{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>status.desc.bleed</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Lose {tick} HP per stack each time you act. Stacks up to {max}, lasts {dur} turns.{mods}</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>행동할 때마다 중첩당 {tick} HP를 잃습니다. 최대 {max}중첩, {dur}턴 지속.{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>status.desc.burn.data</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Lose {tick} HP each turn for {turns} more turns.{mods}</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>매 턴 {tick} HP를 잃습니다. {turns}턴 더 지속.{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>status.desc.burn</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Lose a fixed amount of HP (it grows with the caster's MAG) each turn for {dur} turns. Does not stack.{mods}</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>매 턴 정해진 HP(시전자의 MAG에 비례)를 {dur}턴 동안 잃습니다. 중첩되지 않습니다.{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>status.desc.status_stun</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Cannot act.</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>행동할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>status.desc.status_guard</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Blocks the next incoming hit.</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>다음에 받는 공격을 막습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>status.desc.status_dmg_up</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Next attack deals {mult} times the damage.</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>다음 공격이 {mult}배의 피해를 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>status.desc.status_evasion</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Dodges the next incoming attack.</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>다음에 받는 공격을 피합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>status.desc.status_crit_up</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Critical chance +{pct}%.</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>치명타 확률 +{pct}%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>status.desc.status_hit_up</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>For {turns} turns: you see the enemy's next move and every Perfect zone is {pct}% wider.</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>{turns}턴 동안 적의 다음 행동이 보이고 모든 퍼펙트 구간이 {pct}% 넓어집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>status.desc.status_meditation</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Recover {lo}-{hi} MP each turn.</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>매 턴 MP를 {lo}-{hi} 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>status.desc.status_solidify</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Takes {pct}% less damage from the next hit.</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>다음 공격에서 받는 피해가 {pct}% 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>status.desc.status_bloodthirsty</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Until hit: take {take}% less, deal {deal}% more damage.</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>맞을 때까지: 받는 피해 {take}% 감소, 주는 피해 {deal}% 증가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>status.desc.status_blessing</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Next incoming hit deals {pct}% less damage.</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>다음에 받는 공격의 피해가 {pct}% 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>status.desc.status_sunder</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Lose defence.{mods}</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>방어력이 떨어집니다.{mods}</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>combat.msg.status_tick_enemy</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>{status} hurts {enemy} for {dmg}.</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>{status} 때문에 {enemy}가 {dmg}의 피해를 입었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>combat.msg.multi_status_none</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Nothing took hold.</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>아무 효과도 없었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>combat.msg.foresee</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>You foresee: {action}</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>예견: {action}</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>combat.foresee.attack</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>a plain attack</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>일반 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>combat.foresee.stunned</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>nothing, it is stunned</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>기절해서 아무것도 못 합니다</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C731"/>
+  <dimension ref="A1:C737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Cannot act.</t>
+          <t>Pushed back on the turn bar. Then Steadfast: cannot be stunned for 2 turns.</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>행동할 수 없습니다.</t>
+          <t>차례가 뒤로 밀립니다. 그 뒤 2턴 동안은 기절하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -12847,6 +12847,108 @@
       <c r="C731" t="inlineStr">
         <is>
           <t>이전 버전의 저장 파일은 이 버전에서 불러올 수 없습니다. 파일은 그대로 두었습니다. 새 도전을 시작하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>combat.msg.pushed_back</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>{name} is pushed back!</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>{name}의 차례가 뒤로 밀렸습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>combat.msg.pushed_back_you</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>You are pushed back!</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>당신의 차례가 뒤로 밀렸습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>combat.msg.steadfast</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>{name} is Steadfast!</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>{name}은(는) 버티고 있습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>combat.msg.steadfast_you</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>You are Steadfast!</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>당신은 버티고 있습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>combat.msg.break</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>BREAK! {name} takes +50% damage!</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>브레이크! {name}이(가) 받는 피해 +50%!</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>battle.hud.break</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>BREAK!</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>브레이크!</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C731"/>
+  <dimension ref="A1:C837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -12850,6 +12850,1808 @@
         </is>
       </c>
     </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>card.lbl.arrows</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Arrows</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>화살표</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>card.lbl.power</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>위력</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>card.lbl.mp</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>card.lbl.chance</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>확률</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>card.lbl.turns</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Turns</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>card.lbl.stacks</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Stacks</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>중첩</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>card.lbl.atk</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>card.lbl.def</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>card.lbl.spd</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>SPD</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>card.lbl.mag</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>card.lbl.main_stat</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Main stat</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>주력 능력치</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>card.lbl.poison_stacks</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Poison stacks</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>독 중첩</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>card.lbl.after_fight</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>After fight</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>전투 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>card.lbl.potion_find</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Potion find</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>물약 발견</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>card.lbl.perfect</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Perfect zone</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>퍼펙트 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>card.lbl.gold</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>card.lbl.each_turn</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Each turn</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>매 턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>card.lbl.potions</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Potions</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>물약</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>card.lbl.guard</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>방어</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>card.lbl.skill_power</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Skill power</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>스킬 위력</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>card.lbl.skill_mp</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Skill MP</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>스킬 MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>card.lbl.status_turns</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Status turns</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>상태 턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>card.lbl.potion_mp</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Potion MP</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>물약 MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>card.lbl.restores</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Restores</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>회복량</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>card.lbl.skills</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Skills</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>스킬</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>card.mp_short</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>{mp} MP</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>{mp} MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>card.val.hp</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>+{n} HP</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>HP +{n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>card.val.mp</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>+{n} MP</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>MP +{n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>card.val.turns</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>+{n} turns</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>+{n}턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>card.val.restores</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>{pct} HP, MP</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>HP, MP {pct}</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>card.skill.buff</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Gain {status} for {turns} turns.</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>{status} 효과를 {turns}턴 동안 얻는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>card.skill.hit</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Strike for {power} power.</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>위력 {power}로 공격한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>card.skill.hit_status</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>{chance}% to inflict {status}.</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>{chance}% 확률로 {status} 부여.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>card.skill.hits</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Strike {hits} times for {power} power each.</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>{hits}번 공격한다. 한 번에 위력 {power}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>card.skill.other</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>A special technique.</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>특수한 기술.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>card.tag.boon</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Boon</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>은총</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>card.tag.class_passive</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Class passive</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>직업 패시브</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>card.tag.passive</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>패시브</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>card.tag.skill</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>스킬</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>card.tag.upgrade</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Upgrade</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>강화</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>cards.pick.hint</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Left / Right to choose, confirm to take it</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>좌/우로 고르고, 확인으로 받는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>cards.pick.left</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>({n} picks left)</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>(남은 선택 {n}번)</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>cards.pick.skip</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Skip: +{gold} gold</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>건너뛰기: +{gold} 골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>cards.pick.title</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Choose a card</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>카드를 고르세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>cards.replace.keep</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Keep my skills</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>스킬 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>cards.replace.lose</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Gives up: {line}</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>잃는 것: {line}</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>cards.replace.keep_help</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Go back to the cards and choose again.</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>카드 화면으로 돌아가 다시 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>cards.replace.title</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Learn {skill}: replace which?</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>{skill} 배우기: 무엇을 바꿀까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>cards.stat.after</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>이후</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>cards.stat.now</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>현재</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>cards.stat.title</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Level {lvl}: place 1 point</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>레벨 {lvl}: 포인트 1개 배분</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>class.lbl.five</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>5 to find</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>5개 발견 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>class.lbl.none</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>class.line.archer</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Fast and sharp. High speed, poison and double shots to find.</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>빠르고 날카롭다. 높은 속도, 독과 연속 사격을 찾아보자.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>class.line.knight</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>A sturdy fighter. Strong attack and defence, five skills to find.</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>듬직한 전사. 강한 공격과 방어, 찾아야 할 스킬 5개.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>class.line.mage</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>A spell caster. Great magic and mana, five spells to find.</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>주문 시전자. 뛰어난 마법과 마나, 찾아야 할 주문 5개.</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>class.line.nobody</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>No skills at all. Fight with your blade, your passives and your items.</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>스킬이 전혀 없다. 칼, 패시브, 아이템으로 싸운다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>class.nobody.locked</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>잠김</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>class.nobody.locked_hint</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Win a run to unlock this path.</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>한 번 승리하면 이 길이 열립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>class.select.become</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Become {cls}?</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>{cls}(이)가 될까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>menu.common.yes</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>menu.common.no</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>card.pas.quick_feet.name</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Quick Feet</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>빠른 발</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>card.pas.quick_feet.line</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Light on your feet: +{n} SPD for good.</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>가벼운 발걸음: 영구히 SPD +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>card.pas.venom_coat.name</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Venom Coat</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>독 바르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>card.pas.venom_coat.line</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Poison you apply lands {n} extra stack.</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>내가 거는 독이 {n}중첩 더 쌓인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>card.pas.field_medic.name</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Field Medic</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>야전 의무병</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>card.pas.field_medic.line</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Heal {n} HP after each fight you win.</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>전투에서 이길 때마다 HP를 {n} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>card.pas.steady_hands.name</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Steady Hands</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>흔들림 없는 손</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>card.pas.steady_hands.line</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Perfect zones are {n}% wider.</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>퍼펙트 구간이 {n}% 넓어진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>card.pas.coin_sense.name</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Coin Sense</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>돈 냄새</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>card.pas.coin_sense.line</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Find {n}% more gold.</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>골드를 {n}% 더 얻는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>card.pas.mana_spring.name</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Mana Spring</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>마나의 샘</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>card.pas.mana_spring.line</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Regain {n} MP at the start of each of your turns.</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>내 턴이 시작될 때마다 MP를 {n} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>card.pas.potion_lore.name</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Potion Lore</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>물약 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>card.pas.potion_lore.line</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Potions work {n}% better.</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>물약의 효과가 {n}% 커진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>card.pas.k_iron_hide.name</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Iron Hide</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>강철 가죽</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>card.pas.k_iron_hide.line</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Thick armour sense: +{n} DEF for good.</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>단단한 감각: 영구히 DEF +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>card.pas.k_bulwark.name</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>방벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>card.pas.k_bulwark.line</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Guard on yourself lasts {n} turns longer.</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>나에게 건 방어 효과가 {n}턴 더 오래간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>card.pas.k_heavy_hands.name</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Heavy Hands</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>묵직한 손</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>card.pas.k_heavy_hands.line</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>A harder swing: +{n} ATK for good.</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>더 묵직한 일격: 영구히 ATK +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>card.pas.a_fleet_foot.name</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Fleet Foot</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>날랜 발</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>card.pas.a_fleet_foot.line</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Quicker than the wind: +{n} SPD for good.</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>바람보다 빠르게: 영구히 SPD +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>card.pas.a_barbed.name</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Barbed Arrows</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>가시 화살</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>card.pas.a_barbed.line</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Your damage skills hit for {n} more power.</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>내 공격 스킬의 위력이 {n} 높아진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>card.pas.a_second_wind.name</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Second Wind</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>두 번째 숨</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>card.pas.a_second_wind.line</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Regain {n} MP after each fight you win.</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>전투에서 이길 때마다 MP를 {n} 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>card.pas.m_arcane_well.name</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Arcane Well</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>비전의 샘</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>card.pas.m_arcane_well.line</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>A deeper well: +{n} MAG for good.</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>더 깊은 샘: 영구히 MAG +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>card.pas.m_spellweave.name</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Spellweave</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>주문 엮기</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>card.pas.m_spellweave.line</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Your skills cost {n} MP less (never below 1).</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>스킬의 MP 소모가 {n} 줄어든다 (최소 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>card.pas.m_cold_focus.name</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Cold Focus</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>차가운 집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>card.pas.m_cold_focus.line</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Statuses you inflict last {n} turn longer.</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>내가 거는 상태 이상이 {n}턴 더 오래간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>card.pas.n_tonic.name</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Tonic Blend</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>강장제 배합</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>card.pas.n_tonic.line</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Healing potions also restore {n} MP.</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>회복 물약이 MP도 {n} 회복시킨다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>card.pas.n_apothecary.name</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Apothecary</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>약제사</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>card.pas.n_apothecary.line</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Potions work {n}% better.</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>물약의 효과가 {n}% 커진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>card.pas.n_scrounger.name</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Scrounger</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>주워 모으는 자</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>card.pas.n_scrounger.line</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>{n}% chance to find a potion after each fight you win.</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>전투에서 이길 때마다 {n}% 확률로 물약을 줍는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>card.fb.rest.name</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Second Breath</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>숨 고르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>card.fb.rest.line</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Restore {n}% of your HP and MP now.</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>지금 HP와 MP를 {n}% 회복한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>card.fb.gold.name</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Coin Purse</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>동전 주머니</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>card.fb.gold.line</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Take {n} gold.</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>골드 {n}을 얻는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>card.fb.focus.name</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Whetstone</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>숫돌</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>card.fb.focus.line</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Your main stat grows by {n} for good.</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>주력 능력치가 영구히 {n} 오른다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C731"/>
+  <dimension ref="A1:C812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>This was around 2 months of development, and I'm glad you were able to get through our prototype story.</t>
+          <t>We're glad you made it all the way to the end.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>이 게임은 약 2개월 동안 개발되었고, 여러분이 우리의 프로토타입 스토리를 끝까지 플레이해 주셔서 정말 기쁩니다.</t>
+          <t>끝까지 함께해 주셔서 정말 기쁩니다.</t>
         </is>
       </c>
     </row>
@@ -12847,6 +12847,1383 @@
       <c r="C731" t="inlineStr">
         <is>
           <t>이전 버전의 저장 파일은 이 버전에서 불러올 수 없습니다. 파일은 그대로 두었습니다. 새 도전을 시작하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>death.t1.0</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>The dark takes you. Quietly.</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>어둠이 당신을 조용히 데려간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>death.t1.1</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>So this is how it ends.</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>결국 이렇게 끝나는구나.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>death.t1.2</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>The floor gives way beneath you.</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>발밑의 바닥이 꺼진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>death.t2.0</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>You were sure that was the end.</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>분명 이게 끝이라고 생각했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>death.t2.1</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>The tunnel is not finished with you.</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>터널은 아직 당신을 놓아주지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>death.t2.2</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Cold stone. A fall. Again.</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>차가운 돌. 추락. 또다시.</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>death.t3.0</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>You know this fall by heart now.</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>이 추락은 이제 눈 감고도 안다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>death.t3.1</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>How many times has it been?</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>벌써 몇 번째일까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>death.t3.2</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Dying is starting to feel like routine.</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>죽는 일이 일상처럼 느껴지기 시작한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>death.t4.0</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>You stopped counting. The walls didn't.</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>세는 건 그만뒀다. 벽은 아니었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>death.t4.1</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>{killer}. You don't even flinch anymore.</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>{killer}. 이제 놀라지도 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>death.t4.2</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Nobody is coming. Nobody ever did.</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>아무도 오지 않는다. 한 번도 온 적 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>death.t5.0</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Even wanting to leave has gone quiet.</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>떠나고 싶다는 마음마저 조용해졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>death.t5.1</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>{killer}. Of course it was.</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>{killer}. 역시 그랬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>death.t5.2</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Down here, at least, you know what to expect.</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>적어도 여기서는 무엇이 올지 안다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_slime</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>A slime. You were beaten by a slime.</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>고작 더러운 것에게 당했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_direwolf</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>The wolf was faster than your fear.</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>늑대는 당신의 두려움보다 빨랐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_ghostsword</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>A blade with no hand to hold it.</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>손도 없이 휘둘러지는 검.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_spider</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Eight eyes. The last thing you saw.</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>여덟 개의 눈. 마지막으로 본 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_madwhisp</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>The glow led you here. It always does.</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>그 빛이 여기까지 이끌었다. 언제나 그렇다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_snake</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>A hiss. Then nothing.</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>쉬익. 그리고 아무것도 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_killer_plant</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Even the plants here want you gone.</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>여기선 식물조차 당신을 죽이려 든다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_stranger</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>The stranger smiled the whole time.</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>낯선 이는 내내 웃고 있었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_mini_boss</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>{killer} did not even slow down.</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>{killer}은(는) 속도조차 늦추지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>death.killer.enemy_final_boss</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>The choir sings. You were its last note.</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>성가대가 노래한다. 당신은 그 마지막 음이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>death.killer.status_poison</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>The poison finished what the fight began.</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>독이 싸움이 남긴 일을 끝냈다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>death.killer.status_burn</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>The fire was warm, at least.</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>적어도 불은 따뜻했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>death.killer.status_bleed</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>You bled out, counting the drops.</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>방울을 세며 피를 흘렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>death.killer.abandoned</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>You let go. The tunnel did not mind.</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>당신은 손을 놓았다. 터널은 개의치 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>death.killer.unknown_name</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Something</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>무언가</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>wake.t1</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>You wake where you first fell. Alive.</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>처음 떨어진 곳에서 눈을 뜬다. 살아 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>wake.t2</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>The same stone. The same cold. You wake again.</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>같은 돌바닥. 같은 냉기. 다시 눈을 뜬다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>wake.t3</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>You wake at the entrance. It almost feels like home.</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>입구에서 눈을 뜬다. 어쩐지 집처럼 느껴진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>wake.t4</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>You wake. You no longer ask why.</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>눈을 뜬다. 더는 이유를 묻지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>runflow.sum.floor</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Floor reached</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>도달한 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>runflow.sum.class</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>직업</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>runflow.sum.level</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>runflow.sum.kills</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Foes beaten</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>쓰러뜨린 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>runflow.sum.falls</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Falls so far</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>지금까지 추락</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>note.map_page.title</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Torn survey page</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>찢어진 측량 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>note.map_page.0</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>A page torn from a survey book. Your handwriting.</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>측량 수첩에서 뜯긴 한 장. 당신의 필체다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>note.map_page.1</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>"No tunnel here. Not on any map I ever drew."</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>"이곳에 터널은 없다. 내가 그린 어떤 지도에도."</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>note.map_page.2</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>The ink still looks wet. You don't remember writing it.</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>잉크가 아직 젖어 있다. 쓴 기억은 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>note.wall_breath.title</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Wall scratches</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>벽의 긁힌 자국</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>note.wall_breath.0</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Scratched deep into the stone, slowly and carefully:</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>돌에 깊고 신중하게 새겨져 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>note.wall_breath.1</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>"It breathes. Hold still and you can feel it."</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>"숨을 쉰다. 가만히 있으면 느껴진다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>note.wall_breath.2</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>"Every step goes deeper. None of them go back."</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>"한 걸음마다 더 깊어진다. 돌아가는 길은 없다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>note.lost_others.title</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Unfinished letter</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>쓰다 만 편지</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>note.lost_others.0</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>A letter that stops in the middle of a sentence.</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>문장 중간에서 끊긴 편지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>note.lost_others.1</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>"The others went ahead. Or I did. I can't tell anymore."</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>"다른 이들이 먼저 갔다. 아니면 내가. 이제 모르겠다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>note.lost_others.2</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>"I keep calling for them. Only the walls answer."</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>"계속 불러보지만 벽만 대답한다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>note.carved_arrow.title</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Carved arrow</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>새겨진 화살표</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>note.carved_arrow.0</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>An arrow is carved here, pointing up.</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>위쪽을 가리키는 화살표가 새겨져 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>note.carved_arrow.1</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Someone crossed it out. Beneath it, one word:</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>누군가 그 위에 줄을 긋고, 아래에 한 단어를 남겼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>note.carved_arrow.2</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>"Don't."</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>"가지 마."</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>note.three_marks.title</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Three marks</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>세 줄의 흔적</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>note.three_marks.0</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Three short scratches in the stone.</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>돌에 짧은 긁힘이 세 개 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>note.three_marks.1</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>You made these. You don't remember making them.</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>당신이 새긴 것이다. 새긴 기억은 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>note.mapmaker_scrap.title</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Mapmaker's scrap</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>지도 제작자의 쪽지</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>note.mapmaker_scrap.0</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>A scrap of paper in your own hand:</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>당신의 필체로 쓰인 쪽지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>note.mapmaker_scrap.1</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>"The fall was no accident. It wanted a mapmaker."</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>"추락은 사고가 아니었다. 터널은 지도 제작자를 원했다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>note.mapmaker_scrap.2</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>"Someone who would map it, and come back to map it again."</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>"그리고 돌아와서 다시 지도를 그릴 사람을."</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>note.six_marks.title</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Six marks</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>여섯 줄의 흔적</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>note.six_marks.0</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Six scratches in a row, tidy as a ledger.</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>장부처럼 가지런한 긁힘 여섯 개.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>note.six_marks.1</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Beside them, in a shakier hand: "Stop counting."</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>그 옆에 떨리는 필체로: "세지 마."</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>note.six_marks.2</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>"It only counts you back."</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>"세면, 터널도 너를 센다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>note.wall_of_marks.title</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>A wall of marks</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>흔적으로 가득한 벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>note.wall_of_marks.0</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Ten scratches. Then more, far older than yours.</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>긁힘 열 개. 그 너머로 훨씬 오래된 자국들.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>note.wall_of_marks.1</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Some are in other hands.</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>일부는 다른 사람의 손길이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>note.wall_of_marks.2</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>You are not the first to wake down here.</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>여기서 눈을 뜬 사람은 당신이 처음이 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>credits.title</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>NO HOPE</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>NO HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>credits.game_by</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Game and art by PaleRook</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>게임과 그림: PaleRook</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>credits.fonts</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Fonts</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>글꼴</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>credits.font_galmuri</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Galmuri by Lee Minseo (OFL-1.1)</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Galmuri - Lee Minseo (OFL-1.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>credits.font_pixel</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Retro Gaming pixel font</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Retro Gaming 픽셀 글꼴</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>credits.tools</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>도구</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>credits.tool_gamemaker</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Made with GameMaker</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>GameMaker로 제작</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>credits.sounds</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Sound and music</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>효과음과 음악</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>credits.creator</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>creator: {name}</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>제작자: {name}</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>credits.thanks</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Thank you for playing.</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>플레이해 주셔서 감사합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>credits.by</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>by PaleRook</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>PaleRook 제작</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C737"/>
+  <dimension ref="A1:C753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -12952,6 +12952,278 @@
         </is>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>combat.msg.windup.skill_vine_trap</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>{enemy} coils its vines!</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 덩굴을 감아 올립니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>combat.msg.windup.skill_ghost_cut</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>{enemy} raises its blade!</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 칼날을 치켜듭니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>combat.msg.windup.skill_ramming</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>{enemy} lowers its horns!</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 뿔을 낮춥니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>combat.msg.windup.skill_pale_hymn</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>{enemy} draws a deep breath!</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 숨을 크게 들이쉽니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>combat.msg.phase.mini_boss.1</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>{enemy} paws the ground, snorting!</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 콧김을 내뿜으며 땅을 긁습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>combat.msg.phase.mini_boss.2</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>{enemy} bellows in a blind rage!</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 분노에 눈이 멀어 포효합니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>combat.msg.phase.final_boss.1</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>{enemy} sings a second voice!</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 두 번째 목소리로 노래합니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>combat.msg.phase.final_boss.2</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>{enemy} howls in fury!</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>{enemy}이(가) 격노하여 울부짖습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>combat.msg.windup_broken</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>{enemy}'s {skill} is broken off!</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>{enemy}의 {skill}이(가) 끊겼습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>combat.foresee.windup</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>winding up {skill}</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>{skill}을(를) 준비 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>skill.name.skill_regrow</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Regrow</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>재생</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>skill.name.skill_snuff</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Snuff</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>꺼뜨리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>skill.name.skill_gore</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Gore</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>뿔치기</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>skill.name.skill_pale_hymn</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Pale Hymn</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>창백한 찬가</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>combat.msg.skill.use.skill_regrow</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>It regrows its wounds!</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>상처가 아물어 갑니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>combat.msg.skill.use.skill_snuff</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Your enchantments are snuffed out!</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>당신의 강화 효과가 꺼졌습니다!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C846"/>
+  <dimension ref="A1:C937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -14805,6 +14805,1553 @@
         </is>
       </c>
     </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>elite.tag</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>정예</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>item.msg.throw_in_battle</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Throw it at an enemy in battle.</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>전투 중 적에게 던지세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>throw.msg.damage</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>{dmg} damage.</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>{dmg}의 피해.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>throw.msg.burn</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>It burns for {n} a turn.</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>매 턴 {n}의 화상을 입습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>throw.msg.poison</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>{n} stacks of poison.</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>독 {n}중첩.</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>throw.msg.evade</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>You will dodge the next attack.</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>다음 공격을 피합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>throw.msg.escape</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>You slip away in the smoke!</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>연기 속으로 빠져나갔습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>throw.msg.thrown</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>You throw the {item}!</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>{item}을(를) 던졌다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>item.sent.30</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Throw it for {power} power of damage; it burns for {turns} turns. Costs your turn.</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>위력 {power}의 피해를 주고 {turns}턴 동안 불탑니다. 턴을 소모합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>item.sent.31</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Throw it to poison the enemy with {n} stacks. Costs your turn.</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>적을 독 {n}중첩으로 중독시킵니다. 턴을 소모합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>item.sent.32</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Throw it for {power} power of damage and a stun that pushes the enemy back. Costs your turn.</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>위력 {power}의 피해를 주고 기절시켜 적을 뒤로 밉니다. 턴을 소모합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>item.sent.33</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Throw it to dodge the next attack ({turns} turns); a Perfect throw lets you slip away. Costs your turn.</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>다음 공격을 피합니다({turns}턴). 완벽하게 던지면 도망칩니다. 턴을 소모합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>item.sent.throw</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Throw it at the enemy. Costs your turn.</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>적에게 던집니다. 턴을 소모합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>item.sent.accessory_stat</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Wear it for {bonus}.</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>착용하면 {bonus}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>item.sent.accessory_passive</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Wear it: {line}.</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>착용: {line}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>item.sent.accessory</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>A ring or charm worn in the accessory slot.</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>장신구 칸에 착용하는 반지나 부적입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>item.sent.heal</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Restores {min} to {max} HP.</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>HP를 {min}에서 {max}만큼 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>item.sent.mp</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Restores {min} to {max} MP.</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>MP를 {min}에서 {max}만큼 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>item.sent.cure</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Cures {status}.</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>{status}을(를) 치료합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>item.sent.weapon</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>A weapon with {power} power.</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>위력 {power}의 무기입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>item.sent.armor</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Armor: {bonus}.</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>방어구: {bonus}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>shop.lbl.power</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>위력</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>shop.lbl.burn</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>shop.lbl.poison</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>독</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>shop.lbl.stun</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>기절</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>shop.val.pushback</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Push back</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>뒤로 밀기</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>shop.lbl.evade</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>shop.val.turns</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>{n} turns</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>{n}턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>shop.lbl.perfect</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Perfect</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>완벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>shop.val.escape</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>도망</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>shop.lbl.nobody</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Nobody</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>무명</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>shop.lbl.carry</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Carry up to</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>최대 소지</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>shop.lbl.damage_taken</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Damage taken</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>받는 피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>shop.lbl.mp</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>shop.val.mp_every</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>+{n} every {k} turns</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>+{n} ({k}턴마다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>shop.lbl.gold</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>shop.lbl.hp</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>shop.lbl.cures</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Cures</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>치료</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>shop.lbl.stat</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Uses</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>능력치</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>shop.lbl.bonus</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>combat.msg.gold_gain</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>(+{gold} gold)</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>(+{gold} 골드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>merchant.name</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>상인</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>elite.name.armored</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Armored</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>철갑</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>elite.name.venomous</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Venomous</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>맹독</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>elite.name.swift</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>신속</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>elite.name.brutal</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Brutal</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>흉포</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>elite.name.regenerating</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Regenerating</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>재생</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>elite.line.armored</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Armored: +{n} DEF.</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>철갑: 방어 +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>elite.line.venomous</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Venomous: its hits poison you for {n} stacks.</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>맹독: 공격이 {n}중첩의 독을 겁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>elite.line.swift</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Swift: +{n} SPD.</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>신속: 속도 +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>elite.line.brutal</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Brutal: +{n} ATK.</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>흉포: 공격 +{n}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>elite.line.regenerating</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Regenerating: heals {pct}% of its HP each turn.</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>재생: 매 턴 HP의 {pct}%를 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>menu.tooltip.item.type.accessory</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>장신구</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>menu.gold</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Gold: {n}</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>골드: {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>shop.sold_out</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Sold out</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>품절</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>shop.lbl.have</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>You have</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>shop.lbl.in_stock</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>In stock</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>shop.lbl.sells_for</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Sells for</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>shop.worn</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Worn</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>착용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>shop.nothing_to_sell</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Nothing to sell</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>팔 것이 없습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>shop.gold</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Gold {n}</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>골드 {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>shop.buy</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>shop.sell</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>판매</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>shop.leave</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>나가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>shop.title</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>상인</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>shop.msg.gold</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Not enough gold.</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>골드가 부족합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>shop.msg.sold_out</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Sold out.</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>품절입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>shop.msg.full</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>You cannot carry more of those.</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>더 이상 가질 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>shop.msg.owned</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>You already have that.</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>이미 가지고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>shop.msg.slots</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>All your skill slots are full.</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>스킬 칸이 가득 찼습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>shop.msg.equipped</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Take it off first.</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>먼저 벗으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>shop.msg.cant</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Cannot do that.</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>shop.msg.bought</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Bought {name} for {price}.</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>{name}을(를) {price}에 샀습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>shop.msg.sold</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Sold {name} for {price}.</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>{name}을(를) {price}에 팔았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>item.name.30</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Firebomb</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>화염병</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>item.name.31</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Poison Pot</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>독 항아리</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>item.name.32</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Ice Flask</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>얼음 병</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>item.name.33</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Smoke Bomb</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>연막탄</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>item.name.40</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Copper Ring</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>구리 반지</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>item.name.41</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Guard Ring</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>수호 반지</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>item.name.42</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Swift Charm</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>신속의 부적</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>item.name.43</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Sage Charm</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>현자의 부적</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>item.name.44</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Stone Charm</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>돌 부적</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>item.name.45</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Spring Ring</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>샘물 반지</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>item.name.46</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Lucky Charm</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>행운의 부적</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>item.passive.name.44</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Hardened</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>단단함</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>item.passive.desc.44</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Take 10% less damage</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>받는 피해 10% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>item.passive.name.45</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>샘물</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>item.passive.desc.45</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>+1 MP every 3 turns</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>3턴마다 MP +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>item.passive.name.46</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Lucky</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>행운</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>item.passive.desc.46</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Find 15% more gold</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>골드를 15% 더 얻음</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>뒤쪽에</t>
+          <t>뒤로</t>
         </is>
       </c>
     </row>
@@ -11991,12 +11991,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Planned: more forgiving timing on button prompts.</t>
+          <t>Wider bar zones and more time on arrow skills.</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>예정: 버튼 입력 타이밍 판정을 더 너그럽게 합니다.</t>
+          <t>막대 판정 구간이 넓어지고 화살표 기술의 시간이 늘어납니다.</t>
         </is>
       </c>
     </row>
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Left / Right to choose, confirm to take it</t>
+          <t>{left}{right} Choose   {confirm} Take</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>좌/우로 고르고, 확인으로 받는다</t>
+          <t>{left}{right} 고르기   {confirm} 받기</t>
         </is>
       </c>
     </row>
@@ -16179,6 +16179,1094 @@
       <c r="C927" t="inlineStr">
         <is>
           <t>PaleRook 제작</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>tutorial.timeline.title</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Turn order</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>턴 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>tutorial.timeline.body</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>The strip at the top shows who acts next. Faster fighters act more often, and some skills push an enemy back a turn.</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>위쪽 띠는 다음에 행동할 상대를 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 어떤 기술은 적을 한 턴 뒤로 밀어냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>tutorial.bar.title</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>The sliding bar</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>움직이는 막대</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>tutorial.bar.body</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>A cursor slides along the bar. Press {confirm} when it is over the bright zone. The closer to the middle, the harder you hit.</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>커서가 막대를 따라 움직입니다. 밝은 구간 위에 왔을 때 {confirm}을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>tutorial.arrows.title</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Arrow skills</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>화살표 기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>tutorial.arrows.body</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Skills show a row of arrows. Press {up}{down}{left}{right} in that order before the time bar runs out. A wrong press costs time.</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>기술을 쓰면 화살표 줄이 나옵니다. 시간 막대가 다 줄기 전에 {up}{down}{left}{right}으로 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>tutorial.defence.title</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Defending</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>막기</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>tutorial.defence.body</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>When an enemy winds up a big attack, a bar appears. Press {confirm} on the bright zone to take less damage and shake off its effects.</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>적이 큰 공격을 준비하면 막대가 나타납니다. 밝은 구간에서 {confirm}을(를) 누르면 피해가 줄고 부가 효과도 털어냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>tutorial.stagger.title</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Stagger and BREAK</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>경직과 BREAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>tutorial.stagger.body</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Good hits fill the enemy's stagger meter. When it is full the enemy is BROKEN: it loses a turn and takes +50% damage.</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>좋은 공격은 적의 경직 게이지를 채웁니다. 가득 차면 적이 BREAK 상태가 되어 한 턴을 잃고 피해를 50% 더 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>tutorial.cards.title</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Cards</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>카드</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>tutorial.cards.body</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Level-ups and skill chests offer 3 cards: a new skill, an upgrade or a passive. Take one, or skip for a little gold.</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>레벨업과 기술 상자는 카드 3장을 보여 줍니다. 새 기술, 강화, 패시브 중 하나를 고르거나, 건너뛰고 약간의 골드를 받으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>tutorial.shop.title</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>The shop</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>tutorial.shop.body</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>The merchant sells potions and gear. Gold is kept for the whole run, and the stock changes with every run.</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>상인은 물약과 장비를 팝니다. 골드는 한 번의 도전 동안 유지되고, 상품은 도전마다 바뀝니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>tutorial.throwables.title</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Throwables</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>투척 도구</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>tutorial.throwables.body</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Throwable items hurt an enemy straight from the item menu. Each one is used up when thrown, so save them for hard fights.</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>투척 도구는 아이템 메뉴에서 바로 적에게 피해를 줍니다. 던지면 사라지니 어려운 싸움을 위해 아껴 두세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>tutorial.bed.title</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>tutorial.bed.body</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Each bed can be used once per run. Rest to restore all your HP and MP, or use it to upgrade one of your skills.</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>침대는 도전마다 한 번씩만 쓸 수 있습니다. 쉬어서 HP와 MP를 모두 채우거나, 기술 하나를 강화하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>tutorial.elite.title</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Elites</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>정예</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>tutorial.elite.body</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Marked enemies are Elites. They are tougher than normal ones, but their rewards are better.</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>표시가 붙은 적은 정예입니다. 일반 적보다 강하지만 보상이 더 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>tutorial.status.title</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>상태 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>tutorial.status.body</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Poison, Burning, Bleeding and Stun last a few turns. The icons under a name show which ones a fighter has.</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>독, 화상, 출혈, 기절은 몇 턴 동안 이어집니다. 이름 아래 아이콘이 걸려 있는 상태를 보여 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>tutorial.footer</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>{confirm} Continue</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>{confirm} 계속</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>tutorial.more</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>+{n} more</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>+{n}개 더</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>help.title</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>도움말</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>pause.option.help</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>도움말</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>bed.title</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Bed</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>bed.option.heal</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>쉬기</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>bed.option.upgrade</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Upgrade a skill</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>기술 강화</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>bed.option.leave</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>떠나기</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>bed.help.heal</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Sleep a while and wake with all your HP and MP.</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>잠시 자고 나면 HP와 MP가 가득 찹니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>bed.help.upgrade</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Think over one of your skills and make it better for good.</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>기술 하나를 곰곰이 되짚어 영구히 더 강하게 만듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>bed.help.upgrade_none</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>None of your skills can be upgraded any more.</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>더 강화할 수 있는 기술이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>bed.help.leave</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Walk away. The bed stays free for later.</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>그냥 떠납니다. 침대는 나중을 위해 비어 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>bed.help.back</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Go back without choosing.</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>고르지 않고 돌아갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>bed.lbl.hp</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>bed.lbl.mp</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>bed.upgrade_title</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Upgrade which skill?</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>어떤 기술을 강화할까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>bed.used</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>You have rested here already. The bed is still warm.</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>이미 여기서 쉬었습니다. 침대는 아직 따뜻합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>bed.msg.heal</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>You sleep a while. HP and MP are full again.</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>잠시 잠들었습니다. HP와 MP가 다시 가득 찼습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>bed.msg.upgrade</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>{skill} is better now.</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>{skill}이(가) 더 강해졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>settings.row.controls</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>settings.help.controls</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Change the keyboard keys. The controller stays as it is.</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>키보드 키를 바꿉니다. 컨트롤러는 그대로입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>controls.title</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>조작</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>controls.row.confirm</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>controls.row.back</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>뒤로</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>controls.row.up</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>위</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>controls.row.down</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>아래</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>controls.row.left</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>왼쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>controls.row.right</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>controls.row.run</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>달리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>controls.row.tab_prev</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Previous tab</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>이전 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>controls.row.tab_next</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Next tab</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>다음 탭</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>controls.row.interact</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Interact</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>상호작용</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>controls.reset</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Reset to defaults</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>기본값으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>controls.press_key</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Press a key...</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>키를 누르세요...</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>controls.help.row</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Confirm, then press the new key. If another action already uses it, the two swap. Esc cancels.</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>확인을 누른 뒤 새 키를 누르세요. 다른 동작이 이미 쓰는 키면 둘이 서로 바뀝니다. Esc로 취소합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>controls.help.reset</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Puts every keyboard key back to how it was. The controller is never changed.</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>키보드 키를 모두 처음대로 되돌립니다. 컨트롤러는 바뀌지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>controls.waiting</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Press the new key for {action}. Esc cancels.</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>{action}에 쓸 새 키를 누르세요. Esc로 취소합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>controls.set</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Key changed. Apply saves it.</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>키가 바뀌었습니다. 적용을 누르면 저장됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>controls.swapped</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>{other} had that key, so the two swapped.</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>{other}이(가) 그 키를 쓰고 있어 서로 바꿨습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>controls.reserved</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>That key is reserved.</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>그 키는 따로 쓰이고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>controls.unusable</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>That key cannot be used.</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>그 키는 쓸 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>controls.reset_done</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Keys are back to the defaults. Apply saves them.</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>키가 기본값으로 돌아갔습니다. 적용을 누르면 저장됩니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>아이템</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>달리다</t>
+          <t>도망</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>기술</t>
         </is>
       </c>
     </row>
@@ -16451,6 +16451,312 @@
       <c r="C943" t="inlineStr">
         <is>
           <t>당신의 강화 효과가 꺼졌습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>battle.action.guard</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>GUARD</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>방어</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>battle.hud.hp</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>battle.hud.mp</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>battle.hud.level</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Lv {n}</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Lv {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>battle.menu.mp</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>{mp} MP</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>{mp} MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>battle.det.hits</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>타수</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>battle.det.hp</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>battle.det.mp</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>battle.item.other</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>A useful item.</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>쓸모 있는 물건입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>battle.item.heal</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Restores your HP.</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>HP를 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>battle.item.mp</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Restores your MP.</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>MP를 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>battle.item.cure</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Cures {status}.</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>{status} 상태를 치료합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>battle.chip.steadfast</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Steadfast</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>버티기</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>battle.chip.steadfast.line</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Cannot be stunned.</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>기절하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>battle.chip.break.line</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Takes +50% damage until its next turn.</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>다음 차례까지 받는 피해가 50% 늘어납니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>combat.msg.guard</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>You brace yourself.</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>당신은 몸을 웅크립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>status.name.status_brace</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Braced</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>방어 태세</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>status.desc.status_brace</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Braced for the next hit: it deals {pct}% less damage.</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>다음 공격에 대비합니다. 피해가 {pct}% 줄어듭니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C927"/>
+  <dimension ref="A1:C1018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -8302,12 +8302,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Characters per second</t>
+          <t>Chars per sec</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>초당 글자 수</t>
+          <t>초당 글자</t>
         </is>
       </c>
     </row>
@@ -16179,6 +16179,1553 @@
       <c r="C927" t="inlineStr">
         <is>
           <t>속박 사격이 적을 기절시켰습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>pause.help.abandon</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Ends this run now. It counts as a death, but you keep the echo.</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>지금 도전을 끝냅니다. 죽음으로 기록되지만 메아리는 그대로 가져갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>pause.help.abandon_armed</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Confirm once more to end this run now. Back or another row cancels.</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>한 번 더 확인하면 지금 도전이 끝납니다. 뒤로 가기나 다른 항목을 고르면 취소됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>pause.help.help</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Every hint the game has: the ones you have seen and the ones still to come.</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>게임이 알려 주는 모든 도움말입니다. 본 것도, 앞으로 볼 것도 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>pause.help.quit</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Saves the run and goes to the title. Continue picks it up again.</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>도전을 저장하고 타이틀로 갑니다. 이어하기로 다시 시작할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>pause.help.resume</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Back to the game.</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>게임으로 돌아갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>pause.help.settings</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Sound, text, window, language and keys.</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>소리, 글자, 창, 언어, 키를 바꿉니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>pause.option.quit</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Quit to title</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>타이틀로 나가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>pause.title</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Paused</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>일시 정지</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>tab.bestiary.attack</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>tab.bestiary.boss</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>A boss.</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>보스입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>tab.bestiary.moves</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Moves: {list}.</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>행동: {list}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>tab.bestiary.unknown</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>You have not met this one yet.</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>아직 만난 적 없는 적입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>tab.codex</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>도감</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>tab.codex.bestiary</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Bestiary</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>적 도감</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>tab.codex.bestiary_help</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>The enemies you have met: their numbers and their moves.</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>만난 적들의 능력치와 행동입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>tab.codex.bestiary_title</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Bestiary {n}/{max}</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>적 도감 {n}/{max}</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>tab.codex.history</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Run history</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>도전 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>tab.codex.history_help</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Every run you have finished, newest first.</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>끝낸 도전이 최근 순서로 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>tab.codex.notes</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>쪽지</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>tab.codex.notes_help</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>The notes you have read in the tunnel.</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>터널에서 읽은 쪽지입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>tab.codex.notes_title</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Notes {n}/{max}</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>쪽지 {n}/{max}</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>tab.codex.unlocks</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Unlocks</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>tab.codex.unlocks_help</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>What winning has opened up for later runs.</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>승리로 이후 도전에 열린 것들입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>tab.gear</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Gear</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>tab.gear.bag</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>가방</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>tab.gear.empty</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Nothing worn</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>착용 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>tab.gear.empty_help</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Nothing is worn in this slot.</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>이 칸에는 아무것도 착용하지 않았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>tab.gear.no_accessory</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>No accessory</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>장신구 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>tab.gear.no_armor</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>No armor</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>방어구 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>tab.gear.no_weapon</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>No weapon</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>무기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>tab.gear.replaces</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Replaces {item}.</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>{item}을(를) 대체합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>tab.gear.worn</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Worn</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>착용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>tab.hint.back</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>{back} Back</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>{back} 뒤로</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>tab.hint.change</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>{left}{right} Change</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>{left}{right} 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>tab.hint.close</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>{back} Close</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>{back} 닫기</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>tab.hint.equip</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>{confirm} Equip</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>{confirm} 착용</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>tab.hint.open</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>{confirm} Open</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>{confirm} 열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>tab.hint.select</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>{confirm} Select</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>{confirm} 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>tab.hint.takeoff</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>{confirm} Take off</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>{confirm} 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>tab.hint.use</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>{confirm} Use</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>{confirm} 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>tab.hist.abandoned</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>You gave this run up on floor {n}.</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>{n}층에서 도전을 포기했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>tab.hist.died</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>You fell on floor {n}.</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>{n}층에서 쓰러졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>tab.hist.died_to</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Floor {n}: felled by {name}.</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>{n}층: {name}에게 쓰러졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>tab.hist.row</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>{cls} Lv {n}</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>{cls} Lv {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>tab.hist.won</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>You climbed out of the tunnel.</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>터널을 빠져나왔습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>tab.items</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>tab.items.key</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>An item you keep for the way ahead.</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>앞으로의 길을 위해 간직하는 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>tab.items.none</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Nothing in your bag</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>소지품이 없습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>tab.items.none_help</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Potions, throwables and keys you find show up here.</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>찾은 물약, 투척 아이템, 열쇠가 여기에 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>tab.lbl.base</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>tab.lbl.best_floor</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Best floor</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>최고 층</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>tab.lbl.effects</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Effects</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>tab.lbl.elite</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>정예</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>tab.lbl.falls</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Falls</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>추락</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>tab.lbl.floor</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>층</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>tab.lbl.gear</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Gear</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>tab.lbl.gold</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>골드</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>tab.lbl.hp</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>tab.lbl.kills</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Foes beaten</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>처치한 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>tab.lbl.level</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>tab.lbl.met</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>만난 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>tab.lbl.seed</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>시드</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>tab.lbl.seed_small</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Seed {n}</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>시드 {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>tab.lbl.total</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>tab.lbl.upgrade</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Upgrade</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>강화</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>tab.lbl.wins</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>승리</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>tab.lbl.xp</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>XP</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>경험치</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>tab.notes.unknown</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>A note you have not found yet. Look at the walls.</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>아직 찾지 못한 쪽지입니다. 벽을 살펴보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>tab.settings</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>tab.skills</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Skills</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>스킬</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>tab.skills.none</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>No skills yet</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>스킬 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>tab.skills.none_help</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Cards and chests teach skills. They appear here with the arrows to press.</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>카드와 상자에서 스킬을 얻습니다. 누를 화살표와 함께 여기에 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>tab.skills.passives</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>패시브</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>tab.status</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>tab.title.codex</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>도감</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>tab.title.gear</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Gear</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>tab.title.items</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>tab.title.skills</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Skills {n}/{max}</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>스킬 {n}/{max}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>tab.title.status</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>능력치</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>tab.unlock.nobody</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Nobody</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>무명</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>tab.unlock.nobody_off</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Win a run to unlock a fighter with no class.</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>승리하면 직업이 없는 전사가 해금됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>tab.unlock.nobody_on</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>A fighter with no class. Throws {m}x as hard and carries {cap} of each throwable.</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>직업이 없는 전사입니다. 투척 아이템을 {m}배 강하게 던지고 종류마다 {cap}개를 가질 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>tab.val.abandoned</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Gave up</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>포기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>tab.val.applied</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>적용됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>tab.val.floor</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Floor {n}</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>{n}층</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>tab.val.locked</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>잠김</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>tab.val.max</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>MAX</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>최대</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>tab.val.none</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>tab.val.seen</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Seen</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>목격</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>tab.val.unlocked</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>해금됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>tab.val.won</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>승리</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1018"/>
+  <dimension ref="A1:C1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -8727,12 +8727,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Critical chance +{pct}%.</t>
+          <t>1 in every {n} hits is a critical.</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>치명타 확률 +{pct}%.</t>
+          <t>{n}번 공격마다 1번은 치명타입니다.</t>
         </is>
       </c>
     </row>
@@ -17726,6 +17726,57 @@
       <c r="C1018" t="inlineStr">
         <is>
           <t>승리</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>status.desc.status_crit_up_many</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>In every {n} hits, {reds} are criticals.</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>{n}번 공격 중 {reds}번은 치명타입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>battle.action.run_no</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>pause.help.in_battle</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Not available during a battle.</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>전투 중에는 사용할 수 없습니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Restore HP {min}-{max}</t>
+          <t>Restore HP {n}</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>HP 회복 {min}-{max}</t>
+          <t>HP {n} 회복</t>
         </is>
       </c>
     </row>
@@ -6109,12 +6109,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Restore MP {min}-{max}</t>
+          <t>Restore MP {n}</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>MP 회복 {min}-{max}</t>
+          <t>MP {n} 회복</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8761,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Recover {lo}-{hi} MP each turn.</t>
+          <t>Recover {n} MP each turn.</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>매 턴 MP를 {lo}-{hi} 회복합니다.</t>
+          <t>매 턴 MP를 {n} 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -13181,12 +13181,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Restores {min} to {max} HP.</t>
+          <t>Restores {n} HP.</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>HP를 {min}에서 {max}만큼 회복합니다.</t>
+          <t>HP를 {n}만큼 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -13198,12 +13198,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Restores {min} to {max} MP.</t>
+          <t>Restores {n} MP.</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>MP를 {min}에서 {max}만큼 회복합니다.</t>
+          <t>MP를 {n}만큼 회복합니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1021"/>
+  <dimension ref="A1:C1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17780,6 +17780,74 @@
         </is>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>title.splash.press_key</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Press any key</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>아무 키나 누르세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>title.splash.press_button</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Press any button</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>아무 버튼이나 누르세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>title.card.cant</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Can't continue</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>이어할 수 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>title.card.time</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>플레이 시간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1021"/>
+  <dimension ref="A1:C1023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17780,6 +17780,40 @@
         </is>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>dialogue.sys_class_chest_guard.0</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Wait, there was a chest back there. I think I should open it...</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>잠깐, 저 뒤에 상자가 있었어. 열어 봐야겠어...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>dialogue.sys_class_chest_guard.1</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>...there might be something I can use to protect myself.</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>...나를 지킬 만한 뭔가가 들어 있을지도 몰라.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1027"/>
+  <dimension ref="A1:C1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17882,6 +17882,40 @@
         </is>
       </c>
     </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>settings.row.rumble</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Rumble</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>진동</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>settings.help.rumble</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Short controller vibration on Perfect hits, BREAK, big hits and defeat.</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>완벽한 공격, 브레이크, 큰 피해, 쓰러질 때 컨트롤러가 짧게 진동합니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1027"/>
+  <dimension ref="A1:C1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17882,6 +17882,23 @@
         </is>
       </c>
     </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>echo.pick.title</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Keep one echo of the last fall</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>지난 추락의 메아리 하나를 간직합니다</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1027"/>
+  <dimension ref="A1:C1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17882,6 +17882,108 @@
         </is>
       </c>
     </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>battle.det.damage</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>battle.det.perfect</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Perfect</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>완벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>battle.preview.damage</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Damage {n}</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>피해 {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>battle.preview.perfect</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Perfect {n}</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>완벽 {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>battle.preview.hits</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>{n} x{hits}</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>{n} x{hits}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>battle.speed.mark</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1030"/>
+  <dimension ref="A1:C1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17933,6 +17933,108 @@
         </is>
       </c>
     </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>stat.perfect</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Perfect rate</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>퍼펙트 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>stat.crits</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Crits landed</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>치명타 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>stat.dmg_dealt</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Damage dealt</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>준 피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>stat.dmg_taken</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Damage taken</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>받은 피해</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>stat.fights_won</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Fights won</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>승리한 전투</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>stat.time</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Run time</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>플레이 시간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1036"/>
+  <dimension ref="A1:C1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -18035,6 +18035,108 @@
         </is>
       </c>
     </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>levelup.gain</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>{stat} +{n}</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>{stat} +{n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>levelup.growth</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>{name} growth: {gains}</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>{name} 성장: {gains}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>cards.stat.maxhp</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Max HP +{n}</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>최대 HP +{n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>cards.stat.maxmp</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Max MP +{n}</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>최대 MP +{n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>cards.stat.maxhp.desc</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Raises your max HP by {n} and heals {n} HP.</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>최대 HP가 {n} 오르고 HP를 {n} 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>cards.stat.maxmp.desc</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Raises your max MP by {n} and restores {n} MP.</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>최대 MP가 {n} 오르고 MP를 {n} 회복합니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1036"/>
+  <dimension ref="A1:C1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -8455,12 +8455,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Windowed, borderless fullscreen, or exclusive fullscreen.</t>
+          <t>Windowed, borderless fullscreen, or exclusive fullscreen. You are asked to keep a change.</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>창 모드, 테두리 없는 전체 화면, 전용 전체 화면 중에서 고릅니다.</t>
+          <t>창 모드, 테두리 없는 전체 화면, 전용 전체 화면 중에서 고릅니다. 바꾸면 유지할지 물어봅니다.</t>
         </is>
       </c>
     </row>
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>How many times the picture is enlarged in a window. Only used when windowed.</t>
+          <t>How many times the picture is enlarged in a window. Only used when windowed. You are asked to keep a change.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>창 모드에서 화면을 몇 배로 키울지 정합니다. 창 모드에서만 쓰입니다.</t>
+          <t>창 모드에서 화면을 몇 배로 키울지 정합니다. 창 모드에서만 쓰입니다. 바꾸면 유지할지 물어봅니다.</t>
         </is>
       </c>
     </row>
@@ -15459,12 +15459,12 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Key changed. Apply saves it.</t>
+          <t>Key changed.</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>키가 바뀌었습니다. 적용을 누르면 저장됩니다.</t>
+          <t>키가 바뀌었습니다.</t>
         </is>
       </c>
     </row>
@@ -15527,12 +15527,12 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Keys are back to the defaults. Apply saves them.</t>
+          <t>Keys are back to the defaults.</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>키가 기본값으로 돌아갔습니다. 적용을 누르면 저장됩니다.</t>
+          <t>키가 기본값으로 돌아갔습니다.</t>
         </is>
       </c>
     </row>
@@ -18032,6 +18032,108 @@
       <c r="C1036" t="inlineStr">
         <is>
           <t>x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>tab.system</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>tab.title.system</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>tab.system.quit_battle_help</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Goes back to the title. Continue puts you back just before this fight.</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>타이틀로 나갑니다. 이어하기를 하면 이 전투 직전부터 다시 시작합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>settings.keep.title</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Keep this setting?</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>이 설정을 유지할까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>settings.keep.body</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>It goes back by itself in {n} s.</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>{n}초 뒤에 자동으로 원래대로 돌아갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>settings.keep.hint</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>{confirm} Keep   {back} Revert</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>{confirm} 유지   {back} 되돌리기</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1036"/>
+  <dimension ref="A1:C1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -17244,12 +17244,12 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>Seed {n}</t>
+          <t>Seed: {n}</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>시드 {n}</t>
+          <t>시드: {n}</t>
         </is>
       </c>
     </row>
@@ -18032,6 +18032,159 @@
       <c r="C1036" t="inlineStr">
         <is>
           <t>x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>seed.choice.title</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Choose a seed</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>시드 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>seed.choice.random</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Random seed</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>무작위 시드</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>seed.choice.enter</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Enter seed</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>시드 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>seed.entry.title</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Enter seed</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>시드 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>seed.entry.info</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Up to 9 digits. Same seed, same run.</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>최대 9자리. 같은 시드, 같은 모험.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>seed.entry.need</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Enter a seed above zero.</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>0보다 큰 시드를 입력하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>seed.entry.hint</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>{up}{down} Digit   {left}{right} Move</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>{up}{down} 숫자   {left}{right} 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>seed.entry.hint2</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>{confirm} Start</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>{confirm} 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>seed.entry.hint3</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>{back} Back   {tab_prev} Delete</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>{back} 뒤로   {tab_prev} 지우기</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1042"/>
+  <dimension ref="A1:C1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -16513,12 +16513,12 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>The notes you have read in the tunnel.</t>
+          <t>The notes you have found in the tunnel.</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>터널에서 읽은 쪽지입니다.</t>
+          <t>터널에서 찾은 쪽지입니다.</t>
         </is>
       </c>
     </row>
@@ -16530,12 +16530,12 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>Notes {n}/{max}</t>
+          <t>Notes found {n}/{max}</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>쪽지 {n}/{max}</t>
+          <t>찾은 쪽지 {n}/{max}</t>
         </is>
       </c>
     </row>
@@ -18134,6 +18134,57 @@
       <c r="C1042" t="inlineStr">
         <is>
           <t>{confirm} 유지   {back} 되돌리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>tab.hint.read</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>{confirm} Read</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>{confirm} 읽기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>tab.hint.scroll</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>{up}{down} Scroll</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>{up}{down} 넘기기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>note.found</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Note found: {title}</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>쪽지를 찾았다: {title}</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -10269,4580 +10269,4580 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>class.lbl.five</t>
+          <t>class.lbl.none</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>5 to find</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>찾을 스킬 5개</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>class.lbl.none</t>
+          <t>class.line.archer</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>A scout of the dark tunnels. Quick and sharp: poison and double shots.</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>어두운 터널의 척후병. 빠르고 날카롭습니다. 독과 연속 사격.</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>class.line.archer</t>
+          <t>class.line.knight</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Fast and sharp. High speed, poison and double shots to find.</t>
+          <t>Guard of the fallen keep. Hits hard, takes hits harder. Stands firm.</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>빠르고 날카롭다. 높은 속도, 독과 연속 사격을 찾아보자.</t>
+          <t>무너진 보루의 수호병. 강하게 치고 더 단단히 버팁니다.</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>class.line.knight</t>
+          <t>class.line.mage</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>A sturdy fighter. Strong attack and defense, five skills to find.</t>
+          <t>A scholar who heard the dark. Frail, but great magic and mana.</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>듬직한 전사. 강한 공격과 방어, 찾아야 할 스킬 5개.</t>
+          <t>어둠의 소리를 들은 학자. 약하지만 마법과 마나가 대단합니다.</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>class.line.mage</t>
+          <t>class.line.nobody</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>A spell caster. Great magic and MP, five skills to find.</t>
+          <t>No name, no past, no skills. Only blade, passives and items.</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>주문 시전자. 뛰어난 마법과 MP, 찾아야 할 스킬 5개.</t>
+          <t>이름도 과거도 스킬도 없습니다. 칼과 패시브와 아이템뿐.</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>class.line.nobody</t>
+          <t>class.nobody.locked</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>No skills at all. Fight with your blade, your passives and your items.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>스킬이 전혀 없다. 칼, 패시브, 아이템으로 싸운다.</t>
+          <t>잠김</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>class.nobody.locked</t>
+          <t>class.nobody.locked_hint</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Win a run to unlock this path.</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>한 번 승리하면 이 길이 열립니다.</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>class.nobody.locked_hint</t>
+          <t>class.select.become</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Win a run to unlock this path.</t>
+          <t>Become {cls}?</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>한 번 승리하면 이 길이 열립니다.</t>
+          <t>{cls}의 길을 걸을까요?</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>class.select.become</t>
+          <t>menu.common.yes</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Become {cls}?</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>{cls}의 길을 걸을까요?</t>
+          <t>예</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>menu.common.yes</t>
+          <t>menu.common.no</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>아니요</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>menu.common.no</t>
+          <t>card.pas.quick_feet.name</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Quick Feet</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>아니요</t>
+          <t>빠른 발</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>card.pas.quick_feet.name</t>
+          <t>card.pas.quick_feet.line</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Quick Feet</t>
+          <t>Light on your feet: +{n} SPD for good.</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>빠른 발</t>
+          <t>가벼운 발걸음: 영구히 SPD +{n}.</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>card.pas.quick_feet.line</t>
+          <t>card.pas.venom_coat.name</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Light on your feet: +{n} SPD for good.</t>
+          <t>Venom Coat</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>가벼운 발걸음: 영구히 SPD +{n}.</t>
+          <t>독 바르기</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>card.pas.venom_coat.name</t>
+          <t>card.pas.venom_coat.line</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Venom Coat</t>
+          <t>Poison you apply adds {n} extra stack.</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>독 바르기</t>
+          <t>내가 거는 독이 {n}중첩 더 쌓인다.</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>card.pas.venom_coat.line</t>
+          <t>card.pas.field_medic.name</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Poison you apply adds {n} extra stack.</t>
+          <t>Field Medic</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>내가 거는 독이 {n}중첩 더 쌓인다.</t>
+          <t>야전 의무병</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>card.pas.field_medic.name</t>
+          <t>card.pas.field_medic.line</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Field Medic</t>
+          <t>Restore {n} HP after each fight you win.</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>야전 의무병</t>
+          <t>전투에서 이길 때마다 HP를 {n} 회복한다.</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>card.pas.field_medic.line</t>
+          <t>card.pas.steady_hands.name</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Restore {n} HP after each fight you win.</t>
+          <t>Steady Hands</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>전투에서 이길 때마다 HP를 {n} 회복한다.</t>
+          <t>흔들림 없는 손</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>card.pas.steady_hands.name</t>
+          <t>card.pas.steady_hands.line</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Steady Hands</t>
+          <t>Perfect zones are {n}% wider.</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>흔들림 없는 손</t>
+          <t>완벽 구간이 {n}% 넓어진다.</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>card.pas.steady_hands.line</t>
+          <t>card.pas.coin_sense.name</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Perfect zones are {n}% wider.</t>
+          <t>Coin Sense</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>완벽 구간이 {n}% 넓어진다.</t>
+          <t>돈 냄새</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>card.pas.coin_sense.name</t>
+          <t>card.pas.coin_sense.line</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Coin Sense</t>
+          <t>Find {n}% more gold.</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>돈 냄새</t>
+          <t>골드를 {n}% 더 얻는다.</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>card.pas.coin_sense.line</t>
+          <t>card.pas.mana_spring.name</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Find {n}% more gold.</t>
+          <t>Mana Spring</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>골드를 {n}% 더 얻는다.</t>
+          <t>마나의 샘</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>card.pas.mana_spring.name</t>
+          <t>card.pas.mana_spring.line</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Mana Spring</t>
+          <t>Regain {n} MP at the start of each of your turns.</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>마나의 샘</t>
+          <t>내 턴이 시작될 때마다 MP를 {n} 회복한다.</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>card.pas.mana_spring.line</t>
+          <t>card.pas.potion_lore.name</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Regain {n} MP at the start of each of your turns.</t>
+          <t>Potion Lore</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>내 턴이 시작될 때마다 MP를 {n} 회복한다.</t>
+          <t>물약 지식</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>card.pas.potion_lore.name</t>
+          <t>card.pas.potion_lore.line</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Potion Lore</t>
+          <t>Potions work {n}% better.</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>물약 지식</t>
+          <t>물약의 효과가 {n}% 커진다.</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>card.pas.potion_lore.line</t>
+          <t>card.pas.opening_blow.name</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Potions work {n}% better.</t>
+          <t>Opening Blow</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>물약의 효과가 {n}% 커진다.</t>
+          <t>선제 일격</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>card.pas.opening_blow.name</t>
+          <t>card.pas.opening_blow.line</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Opening Blow</t>
+          <t>Enemies start each fight with {n} stagger.</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>선제 일격</t>
+          <t>전투가 시작될 때 적의 경직이 {n} 쌓여 있다.</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>card.pas.opening_blow.line</t>
+          <t>card.pas.k_iron_hide.name</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Enemies start each fight with {n} stagger.</t>
+          <t>Iron Hide</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>전투가 시작될 때 적의 경직이 {n} 쌓여 있다.</t>
+          <t>강철 가죽</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>card.pas.k_iron_hide.name</t>
+          <t>card.pas.k_iron_hide.line</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Iron Hide</t>
+          <t>Thicker hide: +{n} DEF for good.</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>강철 가죽</t>
+          <t>두꺼운 가죽: 영구히 DEF +{n}.</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>card.pas.k_iron_hide.line</t>
+          <t>card.pas.k_bulwark.name</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Thicker hide: +{n} DEF for good.</t>
+          <t>Bulwark</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>두꺼운 가죽: 영구히 DEF +{n}.</t>
+          <t>방벽</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>card.pas.k_bulwark.name</t>
+          <t>card.pas.k_bulwark.line</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Bulwark</t>
+          <t>Guard on yourself lasts {n} turns longer.</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>방벽</t>
+          <t>나에게 건 방어 효과가 {n}턴 더 오래간다.</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>card.pas.k_bulwark.line</t>
+          <t>card.pas.k_heavy_hands.name</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Guard on yourself lasts {n} turns longer.</t>
+          <t>Heavy Hands</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>나에게 건 방어 효과가 {n}턴 더 오래간다.</t>
+          <t>묵직한 손</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>card.pas.k_heavy_hands.name</t>
+          <t>card.pas.k_heavy_hands.line</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Heavy Hands</t>
+          <t>A harder swing: +{n} ATK for good.</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>묵직한 손</t>
+          <t>더 묵직한 일격: 영구히 ATK +{n}.</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>card.pas.k_heavy_hands.line</t>
+          <t>card.pas.a_fleet_foot.name</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>A harder swing: +{n} ATK for good.</t>
+          <t>Fleet Foot</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>더 묵직한 일격: 영구히 ATK +{n}.</t>
+          <t>날랜 발</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>card.pas.a_fleet_foot.name</t>
+          <t>card.pas.a_fleet_foot.line</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Fleet Foot</t>
+          <t>Quicker than the wind: +{n} SPD for good.</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>날랜 발</t>
+          <t>바람보다 빠르게: 영구히 SPD +{n}.</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>card.pas.a_fleet_foot.line</t>
+          <t>card.pas.a_barbed.name</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Quicker than the wind: +{n} SPD for good.</t>
+          <t>Barbed Arrows</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>바람보다 빠르게: 영구히 SPD +{n}.</t>
+          <t>가시 화살</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>card.pas.a_barbed.name</t>
+          <t>card.pas.a_barbed.line</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Barbed Arrows</t>
+          <t>Your damage skills hit for {n} more power.</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>가시 화살</t>
+          <t>내 공격 스킬의 위력이 {n} 높아진다.</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>card.pas.a_barbed.line</t>
+          <t>card.pas.a_second_wind.name</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Your damage skills hit for {n} more power.</t>
+          <t>Second Wind</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>내 공격 스킬의 위력이 {n} 높아진다.</t>
+          <t>두 번째 숨</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>card.pas.a_second_wind.name</t>
+          <t>card.pas.a_second_wind.line</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Second Wind</t>
+          <t>Regain {n} MP after each fight you win.</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>두 번째 숨</t>
+          <t>전투에서 이길 때마다 MP를 {n} 회복한다.</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>card.pas.a_second_wind.line</t>
+          <t>card.pas.m_arcane_well.name</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Regain {n} MP after each fight you win.</t>
+          <t>Arcane Well</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>전투에서 이길 때마다 MP를 {n} 회복한다.</t>
+          <t>비전의 샘</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>card.pas.m_arcane_well.name</t>
+          <t>card.pas.m_arcane_well.line</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Arcane Well</t>
+          <t>A deeper well: +{n} MAG for good.</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>비전의 샘</t>
+          <t>더 깊은 샘: 영구히 MAG +{n}.</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>card.pas.m_arcane_well.line</t>
+          <t>card.pas.m_spellweave.name</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>A deeper well: +{n} MAG for good.</t>
+          <t>Spellweave</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>더 깊은 샘: 영구히 MAG +{n}.</t>
+          <t>주문 엮기</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>card.pas.m_spellweave.name</t>
+          <t>card.pas.m_spellweave.line</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Spellweave</t>
+          <t>Your skills cost {n} MP less (never below 1).</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>주문 엮기</t>
+          <t>스킬의 MP 소모가 {n} 줄어든다 (최소 1).</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>card.pas.m_spellweave.line</t>
+          <t>card.pas.m_cold_focus.name</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Your skills cost {n} MP less (never below 1).</t>
+          <t>Cold Focus</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>스킬의 MP 소모가 {n} 줄어든다 (최소 1).</t>
+          <t>차가운 집중</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>card.pas.m_cold_focus.name</t>
+          <t>card.pas.m_cold_focus.line</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Cold Focus</t>
+          <t>Statuses you inflict last {n} turn longer.</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>차가운 집중</t>
+          <t>내가 거는 상태 이상이 {n}턴 더 오래간다.</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>card.pas.m_cold_focus.line</t>
+          <t>card.pas.n_tonic.name</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Statuses you inflict last {n} turn longer.</t>
+          <t>Tonic Blend</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>내가 거는 상태 이상이 {n}턴 더 오래간다.</t>
+          <t>강장제 배합</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>card.pas.n_tonic.name</t>
+          <t>card.pas.n_tonic.line</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Tonic Blend</t>
+          <t>Healing potions also restore {n} MP.</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>강장제 배합</t>
+          <t>회복 물약이 MP도 {n} 회복시킨다.</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>card.pas.n_tonic.line</t>
+          <t>card.pas.n_apothecary.name</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Healing potions also restore {n} MP.</t>
+          <t>Apothecary</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>회복 물약이 MP도 {n} 회복시킨다.</t>
+          <t>약제사</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>card.pas.n_apothecary.name</t>
+          <t>card.pas.n_apothecary.line</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Apothecary</t>
+          <t>Potions work {n}% better.</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>약제사</t>
+          <t>물약의 효과가 {n}% 커진다.</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>card.pas.n_apothecary.line</t>
+          <t>card.pas.n_scrounger.name</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Potions work {n}% better.</t>
+          <t>Scrounger</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>물약의 효과가 {n}% 커진다.</t>
+          <t>주워 모으는 자</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>card.pas.n_scrounger.name</t>
+          <t>card.pas.n_scrounger.line</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Scrounger</t>
+          <t>{n}% chance to find a potion after each fight you win.</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>주워 모으는 자</t>
+          <t>전투에서 이길 때마다 {n}% 확률로 물약을 줍는다.</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>card.pas.n_scrounger.line</t>
+          <t>card.fb.rest.name</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>{n}% chance to find a potion after each fight you win.</t>
+          <t>Second Breath</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>전투에서 이길 때마다 {n}% 확률로 물약을 줍는다.</t>
+          <t>숨 고르기</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>card.fb.rest.name</t>
+          <t>card.fb.rest.line</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Second Breath</t>
+          <t>Restore {n}% of your HP and MP now.</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>숨 고르기</t>
+          <t>지금 HP와 MP를 {n}% 회복한다.</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>card.fb.rest.line</t>
+          <t>card.fb.gold.name</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Restore {n}% of your HP and MP now.</t>
+          <t>Coin Purse</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>지금 HP와 MP를 {n}% 회복한다.</t>
+          <t>동전 주머니</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>card.fb.gold.name</t>
+          <t>card.fb.gold.line</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Coin Purse</t>
+          <t>Take {n} gold.</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>동전 주머니</t>
+          <t>골드 {n}을 얻는다.</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>card.fb.gold.line</t>
+          <t>card.fb.focus.name</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Take {n} gold.</t>
+          <t>Whetstone</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>골드 {n}을 얻는다.</t>
+          <t>숫돌</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>card.fb.focus.name</t>
+          <t>card.fb.focus.line</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Whetstone</t>
+          <t>Your main stat grows by {n} for good.</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>숫돌</t>
+          <t>주력 능력치가 영구히 {n} 오른다.</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>card.fb.focus.line</t>
+          <t>death.t1.0</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Your main stat grows by {n} for good.</t>
+          <t>The dark takes you. Quietly.</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>주력 능력치가 영구히 {n} 오른다.</t>
+          <t>어둠이 당신을 조용히 데려간다.</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>death.t1.0</t>
+          <t>death.t1.1</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>The dark takes you. Quietly.</t>
+          <t>So this is how it ends.</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>어둠이 당신을 조용히 데려간다.</t>
+          <t>결국 이렇게 끝나는구나.</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>death.t1.1</t>
+          <t>death.t1.2</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>So this is how it ends.</t>
+          <t>The floor gives way beneath you.</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>결국 이렇게 끝나는구나.</t>
+          <t>발밑의 바닥이 꺼진다.</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>death.t1.2</t>
+          <t>death.t2.0</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>The floor gives way beneath you.</t>
+          <t>You were sure that was the end.</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>발밑의 바닥이 꺼진다.</t>
+          <t>분명 이게 끝이라고 생각했다.</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>death.t2.0</t>
+          <t>death.t2.1</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>You were sure that was the end.</t>
+          <t>The tunnel is not finished with you.</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>분명 이게 끝이라고 생각했다.</t>
+          <t>터널은 아직 당신을 놓아주지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>death.t2.1</t>
+          <t>death.t2.2</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>The tunnel is not finished with you.</t>
+          <t>Cold stone. A fall. Again.</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>터널은 아직 당신을 놓아주지 않는다.</t>
+          <t>차가운 돌. 추락. 또다시.</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>death.t2.2</t>
+          <t>death.t3.0</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Cold stone. A fall. Again.</t>
+          <t>You know this fall by heart now.</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>차가운 돌. 추락. 또다시.</t>
+          <t>이 추락은 이제 눈 감고도 안다.</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>death.t3.0</t>
+          <t>death.t3.1</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>You know this fall by heart now.</t>
+          <t>How many times has it been?</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>이 추락은 이제 눈 감고도 안다.</t>
+          <t>벌써 몇 번째일까?</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>death.t3.1</t>
+          <t>death.t3.2</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>How many times has it been?</t>
+          <t>Dying is starting to feel like routine.</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>벌써 몇 번째일까?</t>
+          <t>죽는 일이 일상처럼 느껴지기 시작한다.</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>death.t3.2</t>
+          <t>death.t4.0</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Dying is starting to feel like routine.</t>
+          <t>You stopped counting. The walls didn't.</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>죽는 일이 일상처럼 느껴지기 시작한다.</t>
+          <t>세는 건 그만뒀다. 벽은 아니었다.</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>death.t4.0</t>
+          <t>death.t4.1</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>You stopped counting. The walls didn't.</t>
+          <t>{killer}. You don't even flinch anymore.</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>세는 건 그만뒀다. 벽은 아니었다.</t>
+          <t>{killer}. 이제 놀라지도 않는다.</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>death.t4.1</t>
+          <t>death.t4.2</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>{killer}. You don't even flinch anymore.</t>
+          <t>Nobody is coming. Nobody ever did.</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>{killer}. 이제 놀라지도 않는다.</t>
+          <t>아무도 오지 않는다. 한 번도 온 적 없다.</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>death.t4.2</t>
+          <t>death.t5.0</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Nobody is coming. Nobody ever did.</t>
+          <t>Even wanting to leave has gone quiet.</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>아무도 오지 않는다. 한 번도 온 적 없다.</t>
+          <t>떠나고 싶다는 마음마저 조용해졌다.</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>death.t5.0</t>
+          <t>death.t5.1</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Even wanting to leave has gone quiet.</t>
+          <t>{killer}. Of course it was.</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>떠나고 싶다는 마음마저 조용해졌다.</t>
+          <t>{killer}. 역시 그랬다.</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>death.t5.1</t>
+          <t>death.t5.2</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>{killer}. Of course it was.</t>
+          <t>Down here, at least, you know what to expect.</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>{killer}. 역시 그랬다.</t>
+          <t>적어도 여기서는 무엇이 올지 안다.</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>death.t5.2</t>
+          <t>death.killer.enemy_slime</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Down here, at least, you know what to expect.</t>
+          <t>A slime. You were beaten by a slime.</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>적어도 여기서는 무엇이 올지 안다.</t>
+          <t>슬라임. 고작 슬라임에게 당했다.</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>death.killer.enemy_slime</t>
+          <t>death.killer.enemy_direwolf</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>A slime. You were beaten by a slime.</t>
+          <t>The wolf was faster than your fear.</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>슬라임. 고작 슬라임에게 당했다.</t>
+          <t>늑대는 당신의 두려움보다 빨랐다.</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>death.killer.enemy_direwolf</t>
+          <t>death.killer.enemy_ghostsword</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>The wolf was faster than your fear.</t>
+          <t>A blade with no hand to hold it.</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>늑대는 당신의 두려움보다 빨랐다.</t>
+          <t>손도 없이 휘둘러지는 검.</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>death.killer.enemy_ghostsword</t>
+          <t>death.killer.enemy_spider</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>A blade with no hand to hold it.</t>
+          <t>Eight eyes. The last thing you saw.</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>손도 없이 휘둘러지는 검.</t>
+          <t>여덟 개의 눈. 마지막으로 본 것.</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>death.killer.enemy_spider</t>
+          <t>death.killer.enemy_madwhisp</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Eight eyes. The last thing you saw.</t>
+          <t>The glow led you here. It always does.</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>여덟 개의 눈. 마지막으로 본 것.</t>
+          <t>그 빛이 여기까지 이끌었다. 언제나 그렇다.</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>death.killer.enemy_madwhisp</t>
+          <t>death.killer.enemy_snake</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>The glow led you here. It always does.</t>
+          <t>A hiss. Then nothing.</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>그 빛이 여기까지 이끌었다. 언제나 그렇다.</t>
+          <t>쉬익. 그리고 아무것도 없다.</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>death.killer.enemy_snake</t>
+          <t>death.killer.enemy_killer_plant</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>A hiss. Then nothing.</t>
+          <t>Even the plants here want you gone.</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>쉬익. 그리고 아무것도 없다.</t>
+          <t>여기선 식물조차 당신을 죽이려 든다.</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>death.killer.enemy_killer_plant</t>
+          <t>death.killer.enemy_stranger</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Even the plants here want you gone.</t>
+          <t>The stranger smiled the whole time.</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>여기선 식물조차 당신을 죽이려 든다.</t>
+          <t>낯선 이는 내내 웃고 있었다.</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>death.killer.enemy_stranger</t>
+          <t>death.killer.enemy_mini_boss</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>The stranger smiled the whole time.</t>
+          <t>{killer} did not even slow down.</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>낯선 이는 내내 웃고 있었다.</t>
+          <t>{killer}은(는) 속도조차 늦추지 않았다.</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>death.killer.enemy_mini_boss</t>
+          <t>death.killer.enemy_final_boss</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>{killer} did not even slow down.</t>
+          <t>The choir sings. You were its last note.</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>{killer}은(는) 속도조차 늦추지 않았다.</t>
+          <t>성가대가 노래한다. 당신은 그 마지막 음이었다.</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>death.killer.enemy_final_boss</t>
+          <t>death.killer.status_poison</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>The choir sings. You were its last note.</t>
+          <t>The poison finished what the fight began.</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>성가대가 노래한다. 당신은 그 마지막 음이었다.</t>
+          <t>독이 싸움이 남긴 일을 끝냈다.</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>death.killer.status_poison</t>
+          <t>death.killer.status_burn</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>The poison finished what the fight began.</t>
+          <t>The fire was warm, at least.</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>독이 싸움이 남긴 일을 끝냈다.</t>
+          <t>적어도 불은 따뜻했다.</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>death.killer.status_burn</t>
+          <t>death.killer.status_bleed</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>The fire was warm, at least.</t>
+          <t>You bled out, counting the drops.</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>적어도 불은 따뜻했다.</t>
+          <t>방울을 세며 피를 흘렸다.</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>death.killer.status_bleed</t>
+          <t>death.killer.abandoned</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>You bled out, counting the drops.</t>
+          <t>You let go. The tunnel did not mind.</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>방울을 세며 피를 흘렸다.</t>
+          <t>당신은 손을 놓았다. 터널은 개의치 않았다.</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>death.killer.abandoned</t>
+          <t>death.killer.unknown_name</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>You let go. The tunnel did not mind.</t>
+          <t>Something</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>당신은 손을 놓았다. 터널은 개의치 않았다.</t>
+          <t>무언가</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>death.killer.unknown_name</t>
+          <t>wake.t1</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Something</t>
+          <t>You wake where you first fell. Alive.</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>무언가</t>
+          <t>처음 떨어진 곳에서 눈을 뜬다. 살아 있다.</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>wake.t1</t>
+          <t>wake.t2</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>You wake where you first fell. Alive.</t>
+          <t>The same stone. The same cold. You wake again.</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>처음 떨어진 곳에서 눈을 뜬다. 살아 있다.</t>
+          <t>같은 돌바닥. 같은 냉기. 다시 눈을 뜬다.</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>wake.t2</t>
+          <t>wake.t3</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>The same stone. The same cold. You wake again.</t>
+          <t>You wake at the entrance. It almost feels like home.</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>같은 돌바닥. 같은 냉기. 다시 눈을 뜬다.</t>
+          <t>입구에서 눈을 뜬다. 어쩐지 집처럼 느껴진다.</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>wake.t3</t>
+          <t>wake.t4</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>You wake at the entrance. It almost feels like home.</t>
+          <t>You wake. You no longer ask why.</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>입구에서 눈을 뜬다. 어쩐지 집처럼 느껴진다.</t>
+          <t>눈을 뜬다. 더는 이유를 묻지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>wake.t4</t>
+          <t>runflow.sum.floor</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>You wake. You no longer ask why.</t>
+          <t>Floor reached</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>눈을 뜬다. 더는 이유를 묻지 않는다.</t>
+          <t>도달한 층</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>runflow.sum.floor</t>
+          <t>runflow.sum.class</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Floor reached</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>도달한 층</t>
+          <t>직업</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>runflow.sum.class</t>
+          <t>runflow.sum.level</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>직업</t>
+          <t>레벨</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>runflow.sum.level</t>
+          <t>runflow.sum.kills</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Foes beaten</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>레벨</t>
+          <t>쓰러뜨린 적</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>runflow.sum.kills</t>
+          <t>runflow.sum.falls</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Foes beaten</t>
+          <t>Falls so far</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>쓰러뜨린 적</t>
+          <t>지금까지 추락</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>runflow.sum.falls</t>
+          <t>note.map_page.title</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Falls so far</t>
+          <t>Torn survey page</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>지금까지 추락</t>
+          <t>찢어진 측량 기록</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>note.map_page.title</t>
+          <t>note.map_page.0</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Torn survey page</t>
+          <t>A page torn from a survey book. Your handwriting.</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>찢어진 측량 기록</t>
+          <t>측량 수첩에서 뜯긴 한 장. 당신의 필체다.</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>note.map_page.0</t>
+          <t>note.map_page.1</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>A page torn from a survey book. Your handwriting.</t>
+          <t>"No tunnel here. Not on any map I ever drew."</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>측량 수첩에서 뜯긴 한 장. 당신의 필체다.</t>
+          <t>"이곳에 터널은 없다. 내가 그린 어떤 지도에도."</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>note.map_page.1</t>
+          <t>note.map_page.2</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>"No tunnel here. Not on any map I ever drew."</t>
+          <t>The ink still looks wet. You don't remember writing it.</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>"이곳에 터널은 없다. 내가 그린 어떤 지도에도."</t>
+          <t>잉크가 아직 젖어 있다. 쓴 기억은 없다.</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>note.map_page.2</t>
+          <t>note.wall_breath.title</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>The ink still looks wet. You don't remember writing it.</t>
+          <t>Wall scratches</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>잉크가 아직 젖어 있다. 쓴 기억은 없다.</t>
+          <t>벽의 긁힌 자국</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>note.wall_breath.title</t>
+          <t>note.wall_breath.0</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Wall scratches</t>
+          <t>Scratched deep into the stone, slowly and carefully:</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>벽의 긁힌 자국</t>
+          <t>돌에 깊이, 천천히, 조심스럽게 새겨져 있다.</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>note.wall_breath.0</t>
+          <t>note.wall_breath.1</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Scratched deep into the stone, slowly and carefully:</t>
+          <t>"It breathes. Hold still and you can feel it."</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>돌에 깊이, 천천히, 조심스럽게 새겨져 있다.</t>
+          <t>"숨을 쉰다. 가만히 있으면 느껴진다."</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>note.wall_breath.1</t>
+          <t>note.wall_breath.2</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>"It breathes. Hold still and you can feel it."</t>
+          <t>"Every step goes deeper. None of them go back."</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>"숨을 쉰다. 가만히 있으면 느껴진다."</t>
+          <t>"한 걸음마다 더 깊어진다. 돌아가는 길은 없다."</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>note.wall_breath.2</t>
+          <t>note.lost_others.title</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>"Every step goes deeper. None of them go back."</t>
+          <t>Unfinished letter</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>"한 걸음마다 더 깊어진다. 돌아가는 길은 없다."</t>
+          <t>쓰다 만 편지</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>note.lost_others.title</t>
+          <t>note.lost_others.0</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Unfinished letter</t>
+          <t>A letter that stops in the middle of a sentence.</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>쓰다 만 편지</t>
+          <t>문장 중간에서 끊긴 편지.</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>note.lost_others.0</t>
+          <t>note.lost_others.1</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>A letter that stops in the middle of a sentence.</t>
+          <t>"The others went ahead. Or I did. I can't tell anymore."</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>문장 중간에서 끊긴 편지.</t>
+          <t>"다른 이들이 먼저 갔다. 아니면 내가. 이제 모르겠다."</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>note.lost_others.1</t>
+          <t>note.lost_others.2</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>"The others went ahead. Or I did. I can't tell anymore."</t>
+          <t>"I keep calling for them. Only the walls answer."</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>"다른 이들이 먼저 갔다. 아니면 내가. 이제 모르겠다."</t>
+          <t>"계속 불러보지만 벽만 대답한다."</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>note.lost_others.2</t>
+          <t>note.carved_arrow.title</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>"I keep calling for them. Only the walls answer."</t>
+          <t>Carved arrow</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>"계속 불러보지만 벽만 대답한다."</t>
+          <t>새겨진 화살표</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>note.carved_arrow.title</t>
+          <t>note.carved_arrow.0</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Carved arrow</t>
+          <t>An arrow is carved here, pointing up.</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>새겨진 화살표</t>
+          <t>위쪽을 가리키는 화살표가 새겨져 있다.</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>note.carved_arrow.0</t>
+          <t>note.carved_arrow.1</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>An arrow is carved here, pointing up.</t>
+          <t>Someone crossed it out. Beneath it, one word:</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>위쪽을 가리키는 화살표가 새겨져 있다.</t>
+          <t>누군가 그 위에 줄을 긋고, 아래에 한 단어를 남겼다.</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>note.carved_arrow.1</t>
+          <t>note.carved_arrow.2</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Someone crossed it out. Beneath it, one word:</t>
+          <t>"Don't."</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>누군가 그 위에 줄을 긋고, 아래에 한 단어를 남겼다.</t>
+          <t>"가지 마."</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>note.carved_arrow.2</t>
+          <t>note.three_marks.title</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>"Don't."</t>
+          <t>Three marks</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>"가지 마."</t>
+          <t>세 줄의 흔적</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>note.three_marks.title</t>
+          <t>note.three_marks.0</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Three marks</t>
+          <t>Three short scratches in the stone.</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>세 줄의 흔적</t>
+          <t>돌에 짧은 긁힘이 세 개 있다.</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>note.three_marks.0</t>
+          <t>note.three_marks.1</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Three short scratches in the stone.</t>
+          <t>You made these. You don't remember making them.</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>돌에 짧은 긁힘이 세 개 있다.</t>
+          <t>당신이 새긴 것이다. 새긴 기억은 없다.</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>note.three_marks.1</t>
+          <t>note.mapmaker_scrap.title</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>You made these. You don't remember making them.</t>
+          <t>Mapmaker's scrap</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>당신이 새긴 것이다. 새긴 기억은 없다.</t>
+          <t>지도 제작자의 쪽지</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>note.mapmaker_scrap.title</t>
+          <t>note.mapmaker_scrap.0</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Mapmaker's scrap</t>
+          <t>A scrap of paper in your own hand:</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>지도 제작자의 쪽지</t>
+          <t>당신의 필체로 쓰인 쪽지.</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>note.mapmaker_scrap.0</t>
+          <t>note.mapmaker_scrap.1</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>A scrap of paper in your own hand:</t>
+          <t>"The fall was no accident. It wanted a mapmaker."</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>당신의 필체로 쓰인 쪽지.</t>
+          <t>"추락은 사고가 아니었다. 터널은 지도 제작자를 원했다."</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>note.mapmaker_scrap.1</t>
+          <t>note.mapmaker_scrap.2</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>"The fall was no accident. It wanted a mapmaker."</t>
+          <t>"Someone who would map it, and come back to map it again."</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>"추락은 사고가 아니었다. 터널은 지도 제작자를 원했다."</t>
+          <t>"그리고 돌아와서 다시 지도를 그릴 사람을."</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>note.mapmaker_scrap.2</t>
+          <t>note.six_marks.title</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>"Someone who would map it, and come back to map it again."</t>
+          <t>Six marks</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>"그리고 돌아와서 다시 지도를 그릴 사람을."</t>
+          <t>여섯 줄의 흔적</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>note.six_marks.title</t>
+          <t>note.six_marks.0</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Six marks</t>
+          <t>Six scratches in a row, tidy as a ledger.</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>여섯 줄의 흔적</t>
+          <t>장부처럼 가지런한 긁힘 여섯 개.</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>note.six_marks.0</t>
+          <t>note.six_marks.1</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Six scratches in a row, tidy as a ledger.</t>
+          <t>Beside them, in a shakier hand: "Stop counting."</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>장부처럼 가지런한 긁힘 여섯 개.</t>
+          <t>그 옆에 떨리는 필체로: "세지 마."</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>note.six_marks.1</t>
+          <t>note.six_marks.2</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Beside them, in a shakier hand: "Stop counting."</t>
+          <t>"It only counts you back."</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>그 옆에 떨리는 필체로: "세지 마."</t>
+          <t>"세면, 터널도 너를 센다."</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>note.six_marks.2</t>
+          <t>note.wall_of_marks.title</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>"It only counts you back."</t>
+          <t>A wall of marks</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>"세면, 터널도 너를 센다."</t>
+          <t>흔적으로 가득한 벽</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>note.wall_of_marks.title</t>
+          <t>note.wall_of_marks.0</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>A wall of marks</t>
+          <t>Ten scratches. Then more, far older than yours.</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>흔적으로 가득한 벽</t>
+          <t>긁힘 열 개. 그 너머로 훨씬 오래된 자국들.</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>note.wall_of_marks.0</t>
+          <t>note.wall_of_marks.1</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Ten scratches. Then more, far older than yours.</t>
+          <t>Some are in other hands.</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>긁힘 열 개. 그 너머로 훨씬 오래된 자국들.</t>
+          <t>일부는 다른 사람의 손길이다.</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>note.wall_of_marks.1</t>
+          <t>note.wall_of_marks.2</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Some are in other hands.</t>
+          <t>You are not the first to wake down here.</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>일부는 다른 사람의 손길이다.</t>
+          <t>여기서 눈을 뜬 사람은 당신이 처음이 아니다.</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>note.wall_of_marks.2</t>
+          <t>credits.title</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>You are not the first to wake down here.</t>
+          <t>NO HOPE</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>여기서 눈을 뜬 사람은 당신이 처음이 아니다.</t>
+          <t>NO HOPE</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>credits.title</t>
+          <t>credits.game_by</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>NO HOPE</t>
+          <t>Game and art by PaleRook</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>NO HOPE</t>
+          <t>게임과 그림: PaleRook</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>credits.game_by</t>
+          <t>credits.fonts</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Game and art by PaleRook</t>
+          <t>Fonts</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>게임과 그림: PaleRook</t>
+          <t>글꼴</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>credits.fonts</t>
+          <t>credits.font_galmuri</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Fonts</t>
+          <t>Galmuri by Lee Minseo (OFL-1.1)</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>글꼴</t>
+          <t>Galmuri - Lee Minseo (OFL-1.1)</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>credits.font_galmuri</t>
+          <t>credits.font_pixel</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Galmuri by Lee Minseo (OFL-1.1)</t>
+          <t>Retro Gaming pixel font</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Galmuri - Lee Minseo (OFL-1.1)</t>
+          <t>Retro Gaming 픽셀 글꼴</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>credits.font_pixel</t>
+          <t>credits.tools</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Retro Gaming pixel font</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Retro Gaming 픽셀 글꼴</t>
+          <t>도구</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>credits.tools</t>
+          <t>credits.tool_gamemaker</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Made with GameMaker</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>도구</t>
+          <t>GameMaker로 제작</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>credits.tool_gamemaker</t>
+          <t>credits.sounds</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Made with GameMaker</t>
+          <t>Sound and music</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>GameMaker로 제작</t>
+          <t>효과음과 음악</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>credits.sounds</t>
+          <t>credits.creator</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Sound and music</t>
+          <t>creator: {name}</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>효과음과 음악</t>
+          <t>제작: {name}</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>credits.creator</t>
+          <t>credits.thanks</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>creator: {name}</t>
+          <t>Thank you for playing.</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>제작: {name}</t>
+          <t>플레이해 주셔서 감사합니다.</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>credits.thanks</t>
+          <t>credits.by</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Thank you for playing.</t>
+          <t>by PaleRook</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>플레이해 주셔서 감사합니다.</t>
+          <t>PaleRook 제작</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>credits.by</t>
+          <t>combat.msg.windup.skill_vine_trap</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>by PaleRook</t>
+          <t>{enemy} coils its vines!</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>PaleRook 제작</t>
+          <t>{enemy}이(가) 덩굴을 감아 올립니다!</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>combat.msg.windup.skill_vine_trap</t>
+          <t>combat.msg.windup.skill_ghost_cut</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>{enemy} coils its vines!</t>
+          <t>{enemy} raises its blade!</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 덩굴을 감아 올립니다!</t>
+          <t>{enemy}이(가) 칼날을 치켜듭니다!</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>combat.msg.windup.skill_ghost_cut</t>
+          <t>combat.msg.windup.skill_ramming</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>{enemy} raises its blade!</t>
+          <t>{enemy} lowers its horns!</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 칼날을 치켜듭니다!</t>
+          <t>{enemy}이(가) 뿔을 낮춥니다!</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>combat.msg.windup.skill_ramming</t>
+          <t>combat.msg.windup.skill_pale_hymn</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>{enemy} lowers its horns!</t>
+          <t>{enemy} draws a deep breath!</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 뿔을 낮춥니다!</t>
+          <t>{enemy}이(가) 숨을 크게 들이쉽니다!</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>combat.msg.windup.skill_pale_hymn</t>
+          <t>combat.msg.phase.mini_boss.1</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>{enemy} draws a deep breath!</t>
+          <t>{enemy} paws the ground, snorting!</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 숨을 크게 들이쉽니다!</t>
+          <t>{enemy}이(가) 콧김을 내뿜으며 땅을 긁습니다!</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>combat.msg.phase.mini_boss.1</t>
+          <t>combat.msg.phase.mini_boss.2</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>{enemy} paws the ground, snorting!</t>
+          <t>{enemy} bellows in a blind rage!</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 콧김을 내뿜으며 땅을 긁습니다!</t>
+          <t>{enemy}이(가) 분노에 눈이 멀어 포효합니다!</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>combat.msg.phase.mini_boss.2</t>
+          <t>combat.msg.phase.final_boss.1</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>{enemy} bellows in a blind rage!</t>
+          <t>{enemy} sings a second voice!</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 분노에 눈이 멀어 포효합니다!</t>
+          <t>{enemy}이(가) 두 번째 목소리로 노래합니다!</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>combat.msg.phase.final_boss.1</t>
+          <t>combat.msg.phase.final_boss.2</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>{enemy} sings a second voice!</t>
+          <t>{enemy} howls in fury!</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 두 번째 목소리로 노래합니다!</t>
+          <t>{enemy}이(가) 격노하여 울부짖습니다!</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>combat.msg.phase.final_boss.2</t>
+          <t>combat.msg.windup_broken</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>{enemy} howls in fury!</t>
+          <t>{enemy}'s {skill} is broken off!</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>{enemy}이(가) 격노하여 울부짖습니다!</t>
+          <t>{enemy}의 {skill}이(가) 끊겼습니다!</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>combat.msg.windup_broken</t>
+          <t>combat.foresee.windup</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>{enemy}'s {skill} is broken off!</t>
+          <t>winding up {skill}</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>{enemy}의 {skill}이(가) 끊겼습니다!</t>
+          <t>{skill}을(를) 준비 중</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>combat.foresee.windup</t>
+          <t>skill.name.skill_regrow</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>winding up {skill}</t>
+          <t>Regrow</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>{skill}을(를) 준비 중</t>
+          <t>다시 자라기</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>skill.name.skill_regrow</t>
+          <t>skill.name.skill_snuff</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Regrow</t>
+          <t>Snuff</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>다시 자라기</t>
+          <t>꺼뜨리기</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>skill.name.skill_snuff</t>
+          <t>skill.name.skill_gore</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Snuff</t>
+          <t>Gore</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>꺼뜨리기</t>
+          <t>들이받기</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>skill.name.skill_gore</t>
+          <t>skill.name.skill_pale_hymn</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Gore</t>
+          <t>Pale Hymn</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>들이받기</t>
+          <t>창백한 찬가</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>skill.name.skill_pale_hymn</t>
+          <t>combat.msg.skill.use.skill_regrow</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Pale Hymn</t>
+          <t>It regrows its wounds!</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>창백한 찬가</t>
+          <t>상처가 아물어 갑니다!</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>combat.msg.skill.use.skill_regrow</t>
+          <t>combat.msg.skill.use.skill_snuff</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>It regrows its wounds!</t>
+          <t>Your enchantments are snuffed out!</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>상처가 아물어 갑니다!</t>
+          <t>당신의 강화 효과가 꺼졌습니다!</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>combat.msg.skill.use.skill_snuff</t>
+          <t>elite.tag</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Your enchantments are snuffed out!</t>
+          <t>ELITE</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>당신의 강화 효과가 꺼졌습니다!</t>
+          <t>정예</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>elite.tag</t>
+          <t>item.msg.throw_in_battle</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>ELITE</t>
+          <t>Throw it at an enemy in battle.</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>정예</t>
+          <t>전투 중 적에게 던지세요.</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>item.msg.throw_in_battle</t>
+          <t>throw.msg.damage</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Throw it at an enemy in battle.</t>
+          <t>{dmg} damage.</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>전투 중 적에게 던지세요.</t>
+          <t>{dmg}의 피해.</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>throw.msg.damage</t>
+          <t>throw.msg.burn</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>{dmg} damage.</t>
+          <t>It burns for {n} each turn.</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>{dmg}의 피해.</t>
+          <t>매 턴 {n}의 화상을 입습니다.</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>throw.msg.burn</t>
+          <t>throw.msg.poison</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>It burns for {n} each turn.</t>
+          <t>{n} stacks of poison.</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>매 턴 {n}의 화상을 입습니다.</t>
+          <t>독 {n}중첩.</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>throw.msg.poison</t>
+          <t>throw.msg.evade</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>{n} stacks of poison.</t>
+          <t>You will dodge the next attack.</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>독 {n}중첩.</t>
+          <t>다음 공격을 피합니다.</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>throw.msg.evade</t>
+          <t>throw.msg.escape</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>You will dodge the next attack.</t>
+          <t>You slip away in the smoke!</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>다음 공격을 피합니다.</t>
+          <t>연기 속으로 빠져나갔습니다!</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>throw.msg.escape</t>
+          <t>throw.msg.thrown</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>You slip away in the smoke!</t>
+          <t>You throw the {item}!</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>연기 속으로 빠져나갔습니다!</t>
+          <t>{item}을(를) 던졌습니다!</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>throw.msg.thrown</t>
+          <t>item.sent.30</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>You throw the {item}!</t>
+          <t>Throw it for {power} power of damage; it burns for {turns} turns. Costs your turn.</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>{item}을(를) 던졌습니다!</t>
+          <t>위력 {power}의 피해를 주고 {turns}턴 동안 불탑니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>item.sent.30</t>
+          <t>item.sent.31</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Throw it for {power} power of damage; it burns for {turns} turns. Costs your turn.</t>
+          <t>Throw it to poison the enemy with {n} stacks. Costs your turn.</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>위력 {power}의 피해를 주고 {turns}턴 동안 불탑니다. 턴을 소모합니다.</t>
+          <t>적에게 독 {n}중첩을 겁니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>item.sent.31</t>
+          <t>item.sent.32</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Throw it to poison the enemy with {n} stacks. Costs your turn.</t>
+          <t>Throw it for {power} power of damage and a stun that pushes the enemy back. Costs your turn.</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>적에게 독 {n}중첩을 겁니다. 턴을 소모합니다.</t>
+          <t>위력 {power}의 피해를 주고 기절시켜 적을 뒤로 밉니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>item.sent.32</t>
+          <t>item.sent.33</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Throw it for {power} power of damage and a stun that pushes the enemy back. Costs your turn.</t>
+          <t>Throw it to dodge the next attack ({turns} turns); a Perfect throw lets you slip away. Costs your turn.</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>위력 {power}의 피해를 주고 기절시켜 적을 뒤로 밉니다. 턴을 소모합니다.</t>
+          <t>다음 공격을 피합니다({turns}턴). 완벽하게 던지면 도망칩니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>item.sent.33</t>
+          <t>item.sent.throw</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Throw it to dodge the next attack ({turns} turns); a Perfect throw lets you slip away. Costs your turn.</t>
+          <t>Throw it at the enemy. Costs your turn.</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>다음 공격을 피합니다({turns}턴). 완벽하게 던지면 도망칩니다. 턴을 소모합니다.</t>
+          <t>적에게 던집니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>item.sent.throw</t>
+          <t>item.sent.accessory_stat</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Throw it at the enemy. Costs your turn.</t>
+          <t>Wear it for {bonus}.</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>적에게 던집니다. 턴을 소모합니다.</t>
+          <t>착용 효과: {bonus}.</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>item.sent.accessory_stat</t>
+          <t>item.sent.accessory_passive</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Wear it for {bonus}.</t>
+          <t>Wear it: {line}.</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>착용 효과: {bonus}.</t>
+          <t>착용 효과: {line}.</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>item.sent.accessory_passive</t>
+          <t>item.sent.accessory</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Wear it: {line}.</t>
+          <t>A ring or charm worn in the accessory slot.</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>착용 효과: {line}.</t>
+          <t>장신구 칸에 착용하는 반지나 부적입니다.</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>item.sent.accessory</t>
+          <t>item.sent.heal</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>A ring or charm worn in the accessory slot.</t>
+          <t>Restores {n} HP.</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>장신구 칸에 착용하는 반지나 부적입니다.</t>
+          <t>HP를 {n}만큼 회복합니다.</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>item.sent.heal</t>
+          <t>item.sent.mp</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Restores {n} HP.</t>
+          <t>Restores {n} MP.</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>HP를 {n}만큼 회복합니다.</t>
+          <t>MP를 {n}만큼 회복합니다.</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>item.sent.mp</t>
+          <t>item.sent.cure</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Restores {n} MP.</t>
+          <t>Cures {status}.</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>MP를 {n}만큼 회복합니다.</t>
+          <t>{status} 상태를 치료합니다.</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>item.sent.cure</t>
+          <t>item.sent.weapon</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Cures {status}.</t>
+          <t>A weapon with {power} power.</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>{status} 상태를 치료합니다.</t>
+          <t>위력 {power}의 무기입니다.</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>item.sent.weapon</t>
+          <t>item.sent.armor</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>A weapon with {power} power.</t>
+          <t>Armor: {bonus}.</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>위력 {power}의 무기입니다.</t>
+          <t>방어구: {bonus}.</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>item.sent.armor</t>
+          <t>shop.lbl.power</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Armor: {bonus}.</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>방어구: {bonus}.</t>
+          <t>위력</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>shop.lbl.power</t>
+          <t>shop.lbl.burn</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>위력</t>
+          <t>화상</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>shop.lbl.burn</t>
+          <t>shop.lbl.poison</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Burn</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>화상</t>
+          <t>독</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>shop.lbl.poison</t>
+          <t>shop.lbl.stun</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Stun</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>독</t>
+          <t>기절</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>shop.lbl.stun</t>
+          <t>shop.val.pushback</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Stun</t>
+          <t>Push back</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>기절</t>
+          <t>밀치기</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>shop.val.pushback</t>
+          <t>shop.lbl.evade</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Push back</t>
+          <t>Dodge</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>밀치기</t>
+          <t>회피</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>shop.lbl.evade</t>
+          <t>shop.val.turns</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>{n} turns</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>회피</t>
+          <t>{n}턴</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>shop.val.turns</t>
+          <t>shop.lbl.perfect</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>{n} turns</t>
+          <t>Perfect</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>{n}턴</t>
+          <t>완벽</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>shop.lbl.perfect</t>
+          <t>shop.val.escape</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Perfect</t>
+          <t>Escape</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>완벽</t>
+          <t>도망</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>shop.val.escape</t>
+          <t>shop.lbl.nobody</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Escape</t>
+          <t>Nobody</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>도망</t>
+          <t>무명</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>shop.lbl.nobody</t>
+          <t>shop.lbl.carry</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Nobody</t>
+          <t>Carry up to</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>무명</t>
+          <t>최대 소지</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>shop.lbl.carry</t>
+          <t>shop.lbl.damage_taken</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Carry up to</t>
+          <t>Damage taken</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>최대 소지</t>
+          <t>받는 피해</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>shop.lbl.damage_taken</t>
+          <t>shop.lbl.mp</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Damage taken</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>받는 피해</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>shop.lbl.mp</t>
+          <t>shop.val.mp_every</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>+{n} every {k} turns</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>+{n} ({k}턴마다)</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>shop.val.mp_every</t>
+          <t>shop.lbl.gold</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>+{n} every {k} turns</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>+{n} ({k}턴마다)</t>
+          <t>골드</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>shop.lbl.gold</t>
+          <t>shop.lbl.hp</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>shop.lbl.hp</t>
+          <t>shop.lbl.cures</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Cures</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>치료</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>shop.lbl.cures</t>
+          <t>shop.lbl.stat</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Cures</t>
+          <t>Uses</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>치료</t>
+          <t>기준 능력치</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>shop.lbl.stat</t>
+          <t>shop.lbl.bonus</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Uses</t>
+          <t>Bonus</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>기준 능력치</t>
+          <t>보너스</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>shop.lbl.bonus</t>
+          <t>combat.msg.gold_gain</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>(+{gold} gold)</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>보너스</t>
+          <t>(+{gold} 골드)</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>combat.msg.gold_gain</t>
+          <t>merchant.name</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>(+{gold} gold)</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>(+{gold} 골드)</t>
+          <t>상인</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>merchant.name</t>
+          <t>elite.name.armored</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Armored</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>상인</t>
+          <t>철갑</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>elite.name.armored</t>
+          <t>elite.name.venomous</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Armored</t>
+          <t>Venomous</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>철갑</t>
+          <t>맹독</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>elite.name.venomous</t>
+          <t>elite.name.swift</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Venomous</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>맹독</t>
+          <t>신속</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>elite.name.swift</t>
+          <t>elite.name.brutal</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Brutal</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>신속</t>
+          <t>흉포</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>elite.name.brutal</t>
+          <t>elite.name.regenerating</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Brutal</t>
+          <t>Regenerating</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>흉포</t>
+          <t>재생</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>elite.name.regenerating</t>
+          <t>elite.line.armored</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Regenerating</t>
+          <t>Armored: +{n} DEF.</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>재생</t>
+          <t>철갑: DEF +{n}.</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>elite.line.armored</t>
+          <t>elite.line.venomous</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Armored: +{n} DEF.</t>
+          <t>Venomous: its hits poison you for {n} stacks.</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>철갑: DEF +{n}.</t>
+          <t>맹독: 공격이 {n}중첩의 독을 겁니다.</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>elite.line.venomous</t>
+          <t>elite.line.swift</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Venomous: its hits poison you for {n} stacks.</t>
+          <t>Swift: +{n} SPD.</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>맹독: 공격이 {n}중첩의 독을 겁니다.</t>
+          <t>신속: SPD +{n}.</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>elite.line.swift</t>
+          <t>elite.line.brutal</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Swift: +{n} SPD.</t>
+          <t>Brutal: +{n} ATK.</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>신속: SPD +{n}.</t>
+          <t>흉포: ATK +{n}.</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>elite.line.brutal</t>
+          <t>elite.line.regenerating</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Brutal: +{n} ATK.</t>
+          <t>Regenerating: heals {pct}% of its HP each turn.</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>흉포: ATK +{n}.</t>
+          <t>재생: 매 턴 HP의 {pct}%를 회복합니다.</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>elite.line.regenerating</t>
+          <t>menu.tooltip.item.type.accessory</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Regenerating: heals {pct}% of its HP each turn.</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>재생: 매 턴 HP의 {pct}%를 회복합니다.</t>
+          <t>장신구</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>menu.tooltip.item.type.accessory</t>
+          <t>menu.gold</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Gold: {n}</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>장신구</t>
+          <t>골드: {n}</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>menu.gold</t>
+          <t>shop.sold_out</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Gold: {n}</t>
+          <t>Sold out</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>골드: {n}</t>
+          <t>품절</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>shop.sold_out</t>
+          <t>shop.lbl.have</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Sold out</t>
+          <t>You have</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>품절</t>
+          <t>보유</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>shop.lbl.have</t>
+          <t>shop.lbl.in_stock</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>You have</t>
+          <t>In stock</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>재고</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>shop.lbl.in_stock</t>
+          <t>shop.lbl.sells_for</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Sells for</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>판매가</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>shop.lbl.sells_for</t>
+          <t>shop.worn</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Sells for</t>
+          <t>Worn</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>판매가</t>
+          <t>착용 중</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>shop.worn</t>
+          <t>shop.nothing_to_sell</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Worn</t>
+          <t>Nothing to sell</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>착용 중</t>
+          <t>팔 것이 없습니다</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>shop.nothing_to_sell</t>
+          <t>shop.gold</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Nothing to sell</t>
+          <t>Gold {n}</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>팔 것이 없습니다</t>
+          <t>골드 {n}</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>shop.gold</t>
+          <t>shop.buy</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Gold {n}</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>골드 {n}</t>
+          <t>구매</t>
         </is>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>shop.buy</t>
+          <t>shop.sell</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>판매</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>shop.sell</t>
+          <t>shop.leave</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>판매</t>
+          <t>나가기</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>shop.leave</t>
+          <t>shop.title</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>나가기</t>
+          <t>상인</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>shop.title</t>
+          <t>shop.msg.gold</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Merchant</t>
+          <t>Not enough gold.</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>상인</t>
+          <t>골드가 부족합니다.</t>
         </is>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>shop.msg.gold</t>
+          <t>shop.msg.sold_out</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Not enough gold.</t>
+          <t>Sold out.</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>골드가 부족합니다.</t>
+          <t>품절입니다.</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>shop.msg.sold_out</t>
+          <t>shop.msg.full</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Sold out.</t>
+          <t>You cannot carry more of those.</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>품절입니다.</t>
+          <t>더 이상 가질 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>shop.msg.full</t>
+          <t>shop.msg.owned</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>You cannot carry more of those.</t>
+          <t>You already have that.</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>더 이상 가질 수 없습니다.</t>
+          <t>이미 가지고 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>shop.msg.owned</t>
+          <t>shop.msg.slots</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>You already have that.</t>
+          <t>All your skill slots are full.</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>이미 가지고 있습니다.</t>
+          <t>스킬 칸이 가득 찼습니다.</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>shop.msg.slots</t>
+          <t>shop.msg.equipped</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>All your skill slots are full.</t>
+          <t>Take it off first.</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>스킬 칸이 가득 찼습니다.</t>
+          <t>먼저 장착을 해제하세요.</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>shop.msg.equipped</t>
+          <t>shop.msg.cant</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Take it off first.</t>
+          <t>Cannot do that.</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>먼저 장착을 해제하세요.</t>
+          <t>할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>shop.msg.cant</t>
+          <t>shop.msg.bought</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Cannot do that.</t>
+          <t>Bought {name} for {price}.</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>할 수 없습니다.</t>
+          <t>{name}을(를) {price}에 샀습니다.</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>shop.msg.bought</t>
+          <t>shop.msg.sold</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Bought {name} for {price}.</t>
+          <t>Sold {name} for {price}.</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>{name}을(를) {price}에 샀습니다.</t>
+          <t>{name}을(를) {price}에 팔았습니다.</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>shop.msg.sold</t>
+          <t>item.name.30</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>Sold {name} for {price}.</t>
+          <t>Firebomb</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>{name}을(를) {price}에 팔았습니다.</t>
+          <t>화염병</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>item.name.30</t>
+          <t>item.name.31</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Firebomb</t>
+          <t>Poison Pot</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>화염병</t>
+          <t>독 항아리</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>item.name.31</t>
+          <t>item.name.32</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>Poison Pot</t>
+          <t>Ice Flask</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>독 항아리</t>
+          <t>얼음 병</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>item.name.32</t>
+          <t>item.name.33</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Ice Flask</t>
+          <t>Smoke Bomb</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>얼음 병</t>
+          <t>연막탄</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>item.name.33</t>
+          <t>item.name.40</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Smoke Bomb</t>
+          <t>Copper Ring</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>연막탄</t>
+          <t>구리 반지</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>item.name.40</t>
+          <t>item.name.41</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Copper Ring</t>
+          <t>Guard Ring</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>구리 반지</t>
+          <t>수호 반지</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>item.name.41</t>
+          <t>item.name.42</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Guard Ring</t>
+          <t>Swift Charm</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>수호 반지</t>
+          <t>신속의 부적</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>item.name.42</t>
+          <t>item.name.43</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Swift Charm</t>
+          <t>Sage Charm</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>신속의 부적</t>
+          <t>현자의 부적</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>item.name.43</t>
+          <t>item.name.44</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Sage Charm</t>
+          <t>Stone Charm</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>현자의 부적</t>
+          <t>돌 부적</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>item.name.44</t>
+          <t>item.name.45</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Stone Charm</t>
+          <t>Spring Ring</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>돌 부적</t>
+          <t>샘물 반지</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>item.name.45</t>
+          <t>item.name.46</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Spring Ring</t>
+          <t>Lucky Charm</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>샘물 반지</t>
+          <t>행운의 부적</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>item.name.46</t>
+          <t>item.passive.name.44</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Lucky Charm</t>
+          <t>Hardened</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>행운의 부적</t>
+          <t>단단함</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>item.passive.name.44</t>
+          <t>item.passive.desc.44</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Hardened</t>
+          <t>Take 10% less damage</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>단단함</t>
+          <t>받는 피해 10% 감소</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>item.passive.desc.44</t>
+          <t>item.passive.name.45</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Take 10% less damage</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>받는 피해 10% 감소</t>
+          <t>샘물</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>item.passive.name.45</t>
+          <t>item.passive.desc.45</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>+1 MP every 3 turns</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>샘물</t>
+          <t>3턴마다 MP +1</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>item.passive.desc.45</t>
+          <t>item.passive.name.46</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>+1 MP every 3 turns</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>3턴마다 MP +1</t>
+          <t>행운</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>item.passive.name.46</t>
+          <t>item.passive.desc.46</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Find 15% more gold</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>행운</t>
+          <t>골드를 15% 더 얻음</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>item.passive.desc.46</t>
+          <t>tutorial.timeline.title</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Find 15% more gold</t>
+          <t>Turn order</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>골드를 15% 더 얻음</t>
+          <t>턴 순서</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>tutorial.timeline.title</t>
+          <t>tutorial.timeline.body</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Turn order</t>
+          <t>The strip at the top shows who acts next. Faster fighters act more often, and some skills push an enemy back a turn.</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>턴 순서</t>
+          <t>위쪽 띠는 다음에 행동할 상대를 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 어떤 스킬은 적을 한 턴 뒤로 밀어냅니다.</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>tutorial.timeline.body</t>
+          <t>tutorial.bar.title</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>The strip at the top shows who acts next. Faster fighters act more often, and some skills push an enemy back a turn.</t>
+          <t>The sliding bar</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>위쪽 띠는 다음에 행동할 상대를 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 어떤 스킬은 적을 한 턴 뒤로 밀어냅니다.</t>
+          <t>움직이는 막대</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>tutorial.bar.title</t>
+          <t>tutorial.bar.body</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>The sliding bar</t>
+          <t>A cursor slides along the bar. Press {confirm} when it is over the bright zone. The closer to the middle, the harder you hit.</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>움직이는 막대</t>
+          <t>커서가 막대를 따라 움직입니다. 밝은 구간 위에 왔을 때 {confirm}을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>tutorial.bar.body</t>
+          <t>tutorial.arrows.title</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>A cursor slides along the bar. Press {confirm} when it is over the bright zone. The closer to the middle, the harder you hit.</t>
+          <t>Arrow skills</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>커서가 막대를 따라 움직입니다. 밝은 구간 위에 왔을 때 {confirm}을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
+          <t>화살표 스킬</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>tutorial.arrows.title</t>
+          <t>tutorial.arrows.body</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Arrow skills</t>
+          <t>Skills show a row of arrows. Press {up}{down}{left}{right} in that order before the time bar runs out. A wrong press costs time.</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>화살표 스킬</t>
+          <t>스킬을 쓰면 화살표 줄이 나옵니다. 시간 막대가 다 줄기 전에 {up}{down}{left}{right}으로 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>tutorial.arrows.body</t>
+          <t>tutorial.defence.title</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Skills show a row of arrows. Press {up}{down}{left}{right} in that order before the time bar runs out. A wrong press costs time.</t>
+          <t>Defending</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>스킬을 쓰면 화살표 줄이 나옵니다. 시간 막대가 다 줄기 전에 {up}{down}{left}{right}으로 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
+          <t>막기</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>tutorial.defence.title</t>
+          <t>tutorial.defence.body</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Defending</t>
+          <t>When an enemy winds up a big attack, a bar appears. Press {confirm} on the bright zone to take less damage and shake off its effects.</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>막기</t>
+          <t>적이 큰 공격을 준비하면 막대가 나타납니다. 밝은 구간에서 {confirm}을(를) 누르면 피해가 줄고 부가 효과도 털어냅니다.</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>tutorial.defence.body</t>
+          <t>tutorial.stagger.title</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>When an enemy winds up a big attack, a bar appears. Press {confirm} on the bright zone to take less damage and shake off its effects.</t>
+          <t>Stagger and BREAK</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>적이 큰 공격을 준비하면 막대가 나타납니다. 밝은 구간에서 {confirm}을(를) 누르면 피해가 줄고 부가 효과도 털어냅니다.</t>
+          <t>경직과 브레이크</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>tutorial.stagger.title</t>
+          <t>tutorial.stagger.body</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Stagger and BREAK</t>
+          <t>Good hits fill the enemy's stagger meter. When it is full the enemy goes into BREAK: it loses a turn and takes +50% damage.</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>경직과 브레이크</t>
+          <t>좋은 공격은 적의 경직 게이지를 채웁니다. 가득 차면 적이 브레이크 상태가 되어 한 턴을 잃고 피해를 50% 더 받습니다.</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>tutorial.stagger.body</t>
+          <t>tutorial.cards.title</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Good hits fill the enemy's stagger meter. When it is full the enemy goes into BREAK: it loses a turn and takes +50% damage.</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>좋은 공격은 적의 경직 게이지를 채웁니다. 가득 차면 적이 브레이크 상태가 되어 한 턴을 잃고 피해를 50% 더 받습니다.</t>
+          <t>카드</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>tutorial.cards.title</t>
+          <t>tutorial.cards.body</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Level-ups and skill chests offer 3 cards: a new skill, an upgrade or a passive. Take one, or skip for a little gold.</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>카드</t>
+          <t>레벨업과 스킬 상자는 카드 3장을 보여 줍니다. 새 스킬, 강화, 패시브 중 하나를 고르거나, 건너뛰고 약간의 골드를 받으세요.</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>tutorial.cards.body</t>
+          <t>tutorial.shop.title</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Level-ups and skill chests offer 3 cards: a new skill, an upgrade or a passive. Take one, or skip for a little gold.</t>
+          <t>The shop</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>레벨업과 스킬 상자는 카드 3장을 보여 줍니다. 새 스킬, 강화, 패시브 중 하나를 고르거나, 건너뛰고 약간의 골드를 받으세요.</t>
+          <t>상점</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>tutorial.shop.title</t>
+          <t>tutorial.shop.body</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>The shop</t>
+          <t>The merchant sells potions and gear. Gold is kept for the whole run, and the stock changes with every run.</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>상인은 물약과 장비를 팝니다. 골드는 한 번의 도전 동안 유지되고, 상품은 도전마다 바뀝니다.</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>tutorial.shop.body</t>
+          <t>tutorial.throwables.title</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>The merchant sells potions and gear. Gold is kept for the whole run, and the stock changes with every run.</t>
+          <t>Throwables</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>상인은 물약과 장비를 팝니다. 골드는 한 번의 도전 동안 유지되고, 상품은 도전마다 바뀝니다.</t>
+          <t>투척 도구</t>
         </is>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>tutorial.throwables.title</t>
+          <t>tutorial.throwables.body</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Throwables</t>
+          <t>Throwable items hurt an enemy straight from the item menu. Each one is used up when thrown, so save them for hard fights.</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>투척 도구</t>
+          <t>투척 도구는 아이템 메뉴에서 바로 적에게 피해를 줍니다. 던지면 사라지니 어려운 싸움을 위해 아껴 두세요.</t>
         </is>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>tutorial.throwables.body</t>
+          <t>tutorial.bed.title</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Throwable items hurt an enemy straight from the item menu. Each one is used up when thrown, so save them for hard fights.</t>
+          <t>Beds</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>투척 도구는 아이템 메뉴에서 바로 적에게 피해를 줍니다. 던지면 사라지니 어려운 싸움을 위해 아껴 두세요.</t>
+          <t>침대</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>tutorial.bed.title</t>
+          <t>tutorial.bed.body</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Beds</t>
+          <t>Each bed can be used once per run. Rest to restore all your HP and MP, or use it to upgrade one of your skills.</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>침대</t>
+          <t>침대는 도전마다 한 번씩만 쓸 수 있습니다. 쉬어서 HP와 MP를 모두 채우거나, 스킬 하나를 강화하세요.</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>tutorial.bed.body</t>
+          <t>tutorial.elite.title</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Each bed can be used once per run. Rest to restore all your HP and MP, or use it to upgrade one of your skills.</t>
+          <t>Elites</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>침대는 도전마다 한 번씩만 쓸 수 있습니다. 쉬어서 HP와 MP를 모두 채우거나, 스킬 하나를 강화하세요.</t>
+          <t>정예</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>tutorial.elite.title</t>
+          <t>tutorial.elite.body</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Elites</t>
+          <t>Marked enemies are Elites. They are tougher than normal ones, but their rewards are better.</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>정예</t>
+          <t>표시가 붙은 적은 정예입니다. 일반 적보다 강하지만 보상이 더 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>tutorial.elite.body</t>
+          <t>tutorial.status.title</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Marked enemies are Elites. They are tougher than normal ones, but their rewards are better.</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>표시가 붙은 적은 정예입니다. 일반 적보다 강하지만 보상이 더 좋습니다.</t>
+          <t>상태 이상</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>tutorial.status.title</t>
+          <t>tutorial.status.body</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>Poison, Burn, Bleed and Stun last a few turns. The icons under a name show which ones a fighter has.</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>상태 이상</t>
+          <t>독, 화상, 출혈, 기절은 몇 턴 동안 이어집니다. 이름 아래 아이콘이 걸려 있는 상태를 보여 줍니다.</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>tutorial.status.body</t>
+          <t>tutorial.footer</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Poison, Burn, Bleed and Stun last a few turns. The icons under a name show which ones a fighter has.</t>
+          <t>{confirm} Continue</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>독, 화상, 출혈, 기절은 몇 턴 동안 이어집니다. 이름 아래 아이콘이 걸려 있는 상태를 보여 줍니다.</t>
+          <t>{confirm} 계속</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>tutorial.footer</t>
+          <t>tutorial.more</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>{confirm} Continue</t>
+          <t>+{n} more</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>{confirm} 계속</t>
+          <t>+{n}개 더</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>tutorial.more</t>
+          <t>help.title</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>+{n} more</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>+{n}개 더</t>
+          <t>도움말</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>help.title</t>
+          <t>pause.option.help</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -14859,3152 +14859,3152 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>pause.option.help</t>
+          <t>bed.title</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Bed</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>도움말</t>
+          <t>침대</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>bed.title</t>
+          <t>bed.option.heal</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Bed</t>
+          <t>Rest</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>침대</t>
+          <t>쉬기</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>bed.option.heal</t>
+          <t>bed.option.upgrade</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Upgrade a skill</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>쉬기</t>
+          <t>스킬 강화</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>bed.option.upgrade</t>
+          <t>bed.option.leave</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Upgrade a skill</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>스킬 강화</t>
+          <t>떠나기</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>bed.option.leave</t>
+          <t>bed.help.heal</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Sleep a while and wake with all your HP and MP.</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>떠나기</t>
+          <t>잠시 자고 나면 HP와 MP가 가득 찹니다.</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>bed.help.heal</t>
+          <t>bed.help.upgrade</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Sleep a while and wake with all your HP and MP.</t>
+          <t>Think over one of your skills and make it better for good.</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>잠시 자고 나면 HP와 MP가 가득 찹니다.</t>
+          <t>스킬 하나를 곰곰이 되짚어 영구히 더 강하게 만듭니다.</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>bed.help.upgrade</t>
+          <t>bed.help.upgrade_none</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Think over one of your skills and make it better for good.</t>
+          <t>None of your skills can be upgraded any more.</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>스킬 하나를 곰곰이 되짚어 영구히 더 강하게 만듭니다.</t>
+          <t>더 강화할 수 있는 스킬이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>bed.help.upgrade_none</t>
+          <t>bed.help.leave</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>None of your skills can be upgraded any more.</t>
+          <t>Walk away. The bed stays free for later.</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>더 강화할 수 있는 스킬이 없습니다.</t>
+          <t>그냥 떠납니다. 침대는 나중을 위해 비어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>bed.help.leave</t>
+          <t>bed.help.back</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Walk away. The bed stays free for later.</t>
+          <t>Go back without choosing.</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>그냥 떠납니다. 침대는 나중을 위해 비어 있습니다.</t>
+          <t>고르지 않고 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>bed.help.back</t>
+          <t>bed.lbl.hp</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Go back without choosing.</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>고르지 않고 돌아갑니다.</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>bed.lbl.hp</t>
+          <t>bed.lbl.mp</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>bed.lbl.mp</t>
+          <t>bed.upgrade_title</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Upgrade which skill?</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>어떤 스킬을 강화할까요?</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>bed.upgrade_title</t>
+          <t>bed.used</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Upgrade which skill?</t>
+          <t>You have rested here already. The bed is still warm.</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>어떤 스킬을 강화할까요?</t>
+          <t>이미 여기서 쉬었습니다. 침대는 아직 따뜻합니다.</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>bed.used</t>
+          <t>bed.msg.heal</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>You have rested here already. The bed is still warm.</t>
+          <t>You sleep a while. HP and MP are full again.</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>이미 여기서 쉬었습니다. 침대는 아직 따뜻합니다.</t>
+          <t>잠시 잠들었습니다. HP와 MP가 다시 가득 찼습니다.</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>bed.msg.heal</t>
+          <t>bed.msg.upgrade</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>You sleep a while. HP and MP are full again.</t>
+          <t>{skill} is better now.</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>잠시 잠들었습니다. HP와 MP가 다시 가득 찼습니다.</t>
+          <t>{skill}이(가) 더 강해졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>bed.msg.upgrade</t>
+          <t>settings.row.controls</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>{skill} is better now.</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>{skill}이(가) 더 강해졌습니다.</t>
+          <t>조작</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>settings.row.controls</t>
+          <t>settings.help.controls</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Change the keyboard keys. The controller stays as it is.</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>조작</t>
+          <t>키보드 키를 바꿉니다. 컨트롤러는 그대로입니다.</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>settings.help.controls</t>
+          <t>controls.title</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Change the keyboard keys. The controller stays as it is.</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>키보드 키를 바꿉니다. 컨트롤러는 그대로입니다.</t>
+          <t>조작</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>controls.title</t>
+          <t>controls.row.confirm</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Confirm</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>조작</t>
+          <t>확인</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>controls.row.confirm</t>
+          <t>controls.row.back</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>뒤로</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>controls.row.back</t>
+          <t>controls.row.up</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>뒤로</t>
+          <t>위</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>controls.row.up</t>
+          <t>controls.row.down</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>위</t>
+          <t>아래</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>controls.row.down</t>
+          <t>controls.row.left</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>아래</t>
+          <t>왼쪽</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>controls.row.left</t>
+          <t>controls.row.right</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>왼쪽</t>
+          <t>오른쪽</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>controls.row.right</t>
+          <t>controls.row.run</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>오른쪽</t>
+          <t>달리기</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>controls.row.run</t>
+          <t>controls.row.tab_prev</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Previous tab</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>달리기</t>
+          <t>이전 탭</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>controls.row.tab_prev</t>
+          <t>controls.row.tab_next</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Previous tab</t>
+          <t>Next tab</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>이전 탭</t>
+          <t>다음 탭</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>controls.row.tab_next</t>
+          <t>controls.row.interact</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Next tab</t>
+          <t>Interact</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>다음 탭</t>
+          <t>상호작용</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>controls.row.interact</t>
+          <t>controls.reset</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Reset to defaults</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>상호작용</t>
+          <t>기본값으로</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>controls.reset</t>
+          <t>controls.press_key</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Reset to defaults</t>
+          <t>Press a key...</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>기본값으로</t>
+          <t>키를 누르세요...</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>controls.press_key</t>
+          <t>controls.help.row</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Press a key...</t>
+          <t>Confirm, then press the new key. If another action already uses it, the two swap. Esc cancels.</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>키를 누르세요...</t>
+          <t>확인을 누른 뒤 새 키를 누르세요. 다른 동작이 이미 쓰는 키면 둘이 서로 바뀝니다. Esc로 취소합니다.</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>controls.help.row</t>
+          <t>controls.help.reset</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Confirm, then press the new key. If another action already uses it, the two swap. Esc cancels.</t>
+          <t>Puts every keyboard key back to how it was. The controller is never changed.</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>확인을 누른 뒤 새 키를 누르세요. 다른 동작이 이미 쓰는 키면 둘이 서로 바뀝니다. Esc로 취소합니다.</t>
+          <t>키보드 키를 모두 처음대로 되돌립니다. 컨트롤러는 바뀌지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>controls.help.reset</t>
+          <t>controls.waiting</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Puts every keyboard key back to how it was. The controller is never changed.</t>
+          <t>Press the new key for {action}. Esc cancels.</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>키보드 키를 모두 처음대로 되돌립니다. 컨트롤러는 바뀌지 않습니다.</t>
+          <t>{action}에 쓸 새 키를 누르세요. Esc로 취소합니다.</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>controls.waiting</t>
+          <t>controls.set</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Press the new key for {action}. Esc cancels.</t>
+          <t>Key changed.</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>{action}에 쓸 새 키를 누르세요. Esc로 취소합니다.</t>
+          <t>키가 바뀌었습니다.</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>controls.set</t>
+          <t>controls.swapped</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>Key changed.</t>
+          <t>{other} had that key, so the two swapped.</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>키가 바뀌었습니다.</t>
+          <t>{other}이(가) 그 키를 쓰고 있어 서로 바꿨습니다.</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>controls.swapped</t>
+          <t>controls.reserved</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>{other} had that key, so the two swapped.</t>
+          <t>That key is reserved.</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>{other}이(가) 그 키를 쓰고 있어 서로 바꿨습니다.</t>
+          <t>그 키는 따로 쓰이고 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>controls.reserved</t>
+          <t>controls.unusable</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>That key is reserved.</t>
+          <t>That key cannot be used.</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>그 키는 따로 쓰이고 있습니다.</t>
+          <t>그 키는 쓸 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>controls.unusable</t>
+          <t>controls.reset_done</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>That key cannot be used.</t>
+          <t>Keys are back to the defaults.</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>그 키는 쓸 수 없습니다.</t>
+          <t>키가 기본값으로 돌아갔습니다.</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>controls.reset_done</t>
+          <t>battle.action.guard</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Keys are back to the defaults.</t>
+          <t>GUARD</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>키가 기본값으로 돌아갔습니다.</t>
+          <t>방어</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>battle.action.guard</t>
+          <t>battle.hud.hp</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>GUARD</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>방어</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>battle.hud.hp</t>
+          <t>battle.hud.mp</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>battle.hud.mp</t>
+          <t>battle.hud.level</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Lv {n}</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Lv {n}</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>battle.hud.level</t>
+          <t>battle.menu.mp</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>Lv {n}</t>
+          <t>{mp} MP</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Lv {n}</t>
+          <t>{mp} MP</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>battle.menu.mp</t>
+          <t>battle.det.hits</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>{mp} MP</t>
+          <t>Hits</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>{mp} MP</t>
+          <t>타수</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>battle.det.hits</t>
+          <t>battle.det.hp</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Hits</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>타수</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>battle.det.hp</t>
+          <t>battle.det.mp</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>battle.det.mp</t>
+          <t>battle.item.other</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>A useful item.</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>쓸모 있는 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>battle.item.other</t>
+          <t>battle.item.heal</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>A useful item.</t>
+          <t>Restores your HP.</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>쓸모 있는 아이템입니다.</t>
+          <t>HP를 회복합니다.</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>battle.item.heal</t>
+          <t>battle.item.mp</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Restores your HP.</t>
+          <t>Restores your MP.</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>HP를 회복합니다.</t>
+          <t>MP를 회복합니다.</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>battle.item.mp</t>
+          <t>battle.item.cure</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Restores your MP.</t>
+          <t>Cures {status}.</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>MP를 회복합니다.</t>
+          <t>{status} 상태를 치료합니다.</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>battle.item.cure</t>
+          <t>battle.chip.steadfast</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Cures {status}.</t>
+          <t>Steadfast</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>{status} 상태를 치료합니다.</t>
+          <t>버티기</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>battle.chip.steadfast</t>
+          <t>battle.chip.steadfast.line</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Steadfast</t>
+          <t>Cannot be stunned.</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>버티기</t>
+          <t>기절하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>battle.chip.steadfast.line</t>
+          <t>battle.chip.break.line</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Cannot be stunned.</t>
+          <t>Takes +50% damage until its next turn.</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>기절하지 않습니다.</t>
+          <t>다음 차례까지 받는 피해가 50% 늘어납니다.</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>battle.chip.break.line</t>
+          <t>combat.msg.guard</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Takes +50% damage until its next turn.</t>
+          <t>You brace yourself.</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>다음 차례까지 받는 피해가 50% 늘어납니다.</t>
+          <t>몸을 웅크립니다.</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>combat.msg.guard</t>
+          <t>status.name.status_brace</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>You brace yourself.</t>
+          <t>Braced</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>몸을 웅크립니다.</t>
+          <t>방어 태세</t>
         </is>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>status.name.status_brace</t>
+          <t>status.desc.status_brace</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Braced</t>
+          <t>Braced for the next hit: it deals {pct}% less damage.</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>방어 태세</t>
+          <t>다음 공격에 대비합니다. 피해가 {pct}% 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>status.desc.status_brace</t>
+          <t>battle.hint.list</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>Braced for the next hit: it deals {pct}% less damage.</t>
+          <t>{confirm} Choose   {back} Back</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>다음 공격에 대비합니다. 피해가 {pct}% 줄어듭니다.</t>
+          <t>{confirm} 선택   {back} 뒤로</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>battle.hint.list</t>
+          <t>merchant.greet.0</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>{confirm} Choose   {back} Back</t>
+          <t>You came a long way down. Brave. Or lost.</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>{confirm} 선택   {back} 뒤로</t>
+          <t>꽤 깊이 내려왔군. 용감한 건가, 길을 잃은 건가.</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>merchant.greet.0</t>
+          <t>merchant.greet.1</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>You came a long way down. Brave. Or lost.</t>
+          <t>Coins keep the dark away. Mostly.</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>꽤 깊이 내려왔군. 용감한 건가, 길을 잃은 건가.</t>
+          <t>동전은 어둠을 쫓아 주지. 대개는.</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>merchant.greet.1</t>
+          <t>merchant.greet.2</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Coins keep the dark away. Mostly.</t>
+          <t>Don't ask where I sleep.</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>동전은 어둠을 쫓아 주지. 대개는.</t>
+          <t>내가 어디서 자는지는 묻지 마.</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>merchant.greet.2</t>
+          <t>merchant.greet.3</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Don't ask where I sleep.</t>
+          <t>Buy something. Please.</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>내가 어디서 자는지는 묻지 마.</t>
+          <t>뭐라도 사. 제발.</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>merchant.greet.3</t>
+          <t>merchant.buy.0</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Buy something. Please.</t>
+          <t>Good choice. You will need it.</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>뭐라도 사. 제발.</t>
+          <t>좋은 선택이야. 필요하게 될 거다.</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>merchant.buy.0</t>
+          <t>merchant.buy.1</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Good choice. You will need it.</t>
+          <t>It belonged to someone once.</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>좋은 선택이야. 필요하게 될 거다.</t>
+          <t>한때는 누군가의 물건이었지.</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>merchant.buy.1</t>
+          <t>merchant.buy.2</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>It belonged to someone once.</t>
+          <t>Spend it while you can.</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>한때는 누군가의 물건이었지.</t>
+          <t>쓸 수 있을 때 써 둬.</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>merchant.buy.2</t>
+          <t>merchant.sell.0</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>Spend it while you can.</t>
+          <t>I'll take it. No questions.</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>쓸 수 있을 때 써 둬.</t>
+          <t>받아 두지. 묻진 않을게.</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>merchant.sell.0</t>
+          <t>merchant.sell.1</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>I'll take it. No questions.</t>
+          <t>It will find its way to someone else.</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>받아 두지. 묻진 않을게.</t>
+          <t>그건 또 누군가에게 흘러가겠지.</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>merchant.sell.1</t>
+          <t>merchant.sell.2</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>It will find its way to someone else.</t>
+          <t>Used. Like everything down here.</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>그건 또 누군가에게 흘러가겠지.</t>
+          <t>낡았군. 여기 있는 건 다 그렇지.</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>merchant.sell.2</t>
+          <t>merchant.leave.0</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>Used. Like everything down here.</t>
+          <t>Come back. They always do.</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>낡았군. 여기 있는 건 다 그렇지.</t>
+          <t>또 와. 다들 그러더군.</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>merchant.leave.0</t>
+          <t>merchant.leave.1</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Come back. They always do.</t>
+          <t>Mind the dark. It minds you.</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>또 와. 다들 그러더군.</t>
+          <t>어둠을 조심해. 어둠도 널 지켜보니까.</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>merchant.leave.1</t>
+          <t>merchant.leave.2</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Mind the dark. It minds you.</t>
+          <t>I'll be here. I'm always here.</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>어둠을 조심해. 어둠도 널 지켜보니까.</t>
+          <t>난 여기 있을 거야. 늘 여기 있어.</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>merchant.leave.2</t>
+          <t>combat.msg.defence.resisted</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>I'll be here. I'm always here.</t>
+          <t>Resisted {status}.</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>난 여기 있을 거야. 늘 여기 있어.</t>
+          <t>{status}을(를) 견뎌 냈습니다.</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>combat.msg.defence.resisted</t>
+          <t>combat.msg.defence.summary</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Resisted {status}.</t>
+          <t>{grade} block! Damage -{reduce}%.</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>{status}을(를) 견뎌 냈습니다.</t>
+          <t>{grade} 방어! 피해 -{reduce}%.</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>combat.msg.defence.summary</t>
+          <t>combat.msg.defence.weak</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>{grade} block! Damage -{reduce}%.</t>
+          <t>Not blocked.</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>{grade} 방어! 피해 -{reduce}%.</t>
+          <t>막지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>combat.msg.defence.weak</t>
+          <t>combat.msg.player_cant_escape_this</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>Not blocked.</t>
+          <t>You can't run away from this.</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>막지 못했습니다.</t>
+          <t>이 상대에게서는 도망칠 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>combat.msg.player_cant_escape_this</t>
+          <t>combat.msg.passive.mirror_stitch</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>You can't run away from this.</t>
+          <t>Mirror Stitch repelled a status!</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>이 상대에게서는 도망칠 수 없습니다.</t>
+          <t>거울 바느질이 상태 이상을 튕겨 냈습니다!</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>combat.msg.passive.mirror_stitch</t>
+          <t>combat.msg.passive.pinning_shot</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>Mirror Stitch repelled a status!</t>
+          <t>Pinning Shot stunned the enemy!</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>거울 바느질이 상태 이상을 튕겨 냈습니다!</t>
+          <t>속박 사격이 적을 기절시켰습니다!</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>combat.msg.passive.pinning_shot</t>
+          <t>pause.help.abandon</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>Pinning Shot stunned the enemy!</t>
+          <t>Ends this run now. It counts as a death, but you keep the echo.</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>속박 사격이 적을 기절시켰습니다!</t>
+          <t>지금 도전을 끝냅니다. 죽음으로 기록되지만 메아리는 그대로 가져갑니다.</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>pause.help.abandon</t>
+          <t>pause.help.help</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Ends this run now. It counts as a death, but you keep the echo.</t>
+          <t>Every hint the game has: the ones you have seen and the ones still to come.</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>지금 도전을 끝냅니다. 죽음으로 기록되지만 메아리는 그대로 가져갑니다.</t>
+          <t>게임이 알려 주는 모든 도움말입니다. 본 것도, 앞으로 볼 것도 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>pause.help.help</t>
+          <t>pause.help.quit</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>Every hint the game has: the ones you have seen and the ones still to come.</t>
+          <t>Saves the run and goes to the title. Continue picks it up again.</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>게임이 알려 주는 모든 도움말입니다. 본 것도, 앞으로 볼 것도 있습니다.</t>
+          <t>도전을 저장하고 타이틀로 갑니다. 이어하기로 다시 시작할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>pause.help.quit</t>
+          <t>pause.help.resume</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>Saves the run and goes to the title. Continue picks it up again.</t>
+          <t>Back to the game.</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>도전을 저장하고 타이틀로 갑니다. 이어하기로 다시 시작할 수 있습니다.</t>
+          <t>게임으로 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>pause.help.resume</t>
+          <t>pause.help.settings</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Back to the game.</t>
+          <t>Sound, text, window, language and keys.</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>게임으로 돌아갑니다.</t>
+          <t>소리, 글자, 창, 언어, 키를 바꿉니다.</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>pause.help.settings</t>
+          <t>pause.option.quit</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Sound, text, window, language and keys.</t>
+          <t>Quit to title</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>소리, 글자, 창, 언어, 키를 바꿉니다.</t>
+          <t>타이틀로 나가기</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>pause.option.quit</t>
+          <t>pause.title</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>Quit to title</t>
+          <t>Paused</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>타이틀로 나가기</t>
+          <t>일시 정지</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>pause.title</t>
+          <t>tab.bestiary.attack</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>일시 정지</t>
+          <t>공격</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>tab.bestiary.attack</t>
+          <t>tab.bestiary.boss</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>A boss.</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>공격</t>
+          <t>보스입니다.</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>tab.bestiary.boss</t>
+          <t>tab.bestiary.moves</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>A boss.</t>
+          <t>Moves: {list}.</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>보스입니다.</t>
+          <t>행동: {list}.</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>tab.bestiary.moves</t>
+          <t>tab.bestiary.unknown</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Moves: {list}.</t>
+          <t>You have not met this one yet.</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>행동: {list}.</t>
+          <t>아직 만난 적 없는 적입니다.</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>tab.bestiary.unknown</t>
+          <t>tab.codex</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>You have not met this one yet.</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>아직 만난 적 없는 적입니다.</t>
+          <t>도감</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>tab.codex</t>
+          <t>tab.codex.bestiary</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Bestiary</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>적 도감</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>tab.codex.bestiary</t>
+          <t>tab.codex.bestiary_help</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Bestiary</t>
+          <t>The enemies you have met: their numbers and their moves.</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>적 도감</t>
+          <t>만난 적들의 능력치와 행동입니다.</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>tab.codex.bestiary_help</t>
+          <t>tab.codex.bestiary_title</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>The enemies you have met: their numbers and their moves.</t>
+          <t>Bestiary {n}/{max}</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>만난 적들의 능력치와 행동입니다.</t>
+          <t>적 도감 {n}/{max}</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>tab.codex.bestiary_title</t>
+          <t>tab.codex.history</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Bestiary {n}/{max}</t>
+          <t>Run history</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>적 도감 {n}/{max}</t>
+          <t>도전 기록</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>tab.codex.history</t>
+          <t>tab.codex.history_help</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Run history</t>
+          <t>Every run you have finished, newest first.</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>도전 기록</t>
+          <t>끝낸 도전이 최근 순서로 나옵니다.</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>tab.codex.history_help</t>
+          <t>tab.codex.notes</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Every run you have finished, newest first.</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>끝낸 도전이 최근 순서로 나옵니다.</t>
+          <t>쪽지</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>tab.codex.notes</t>
+          <t>tab.codex.notes_help</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>The notes you have read in the tunnel.</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>쪽지</t>
+          <t>터널에서 읽은 쪽지입니다.</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>tab.codex.notes_help</t>
+          <t>tab.codex.notes_title</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>The notes you have read in the tunnel.</t>
+          <t>Notes {n}/{max}</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>터널에서 읽은 쪽지입니다.</t>
+          <t>쪽지 {n}/{max}</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>tab.codex.notes_title</t>
+          <t>tab.codex.unlocks</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>Notes {n}/{max}</t>
+          <t>Unlocks</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>쪽지 {n}/{max}</t>
+          <t>해금</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>tab.codex.unlocks</t>
+          <t>tab.codex.unlocks_help</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Unlocks</t>
+          <t>What winning has opened up for later runs.</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>해금</t>
+          <t>승리로 이후 도전에 열린 것들입니다.</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>tab.codex.unlocks_help</t>
+          <t>tab.gear</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>What winning has opened up for later runs.</t>
+          <t>Gear</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>승리로 이후 도전에 열린 것들입니다.</t>
+          <t>장비</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>tab.gear</t>
+          <t>tab.gear.bag</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Gear</t>
+          <t>Bag</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>가방</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>tab.gear.bag</t>
+          <t>tab.gear.empty</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Nothing worn</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>가방</t>
+          <t>착용 없음</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>tab.gear.empty</t>
+          <t>tab.gear.empty_help</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Nothing worn</t>
+          <t>Nothing is worn in this slot.</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>착용 없음</t>
+          <t>이 칸에는 아무것도 착용하지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>tab.gear.empty_help</t>
+          <t>tab.gear.no_accessory</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>Nothing is worn in this slot.</t>
+          <t>No accessory</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>이 칸에는 아무것도 착용하지 않았습니다.</t>
+          <t>장신구 없음</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>tab.gear.no_accessory</t>
+          <t>tab.gear.no_armor</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>No accessory</t>
+          <t>No armor</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>장신구 없음</t>
+          <t>방어구 없음</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>tab.gear.no_armor</t>
+          <t>tab.gear.no_weapon</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>No armor</t>
+          <t>No weapon</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>방어구 없음</t>
+          <t>무기 없음</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>tab.gear.no_weapon</t>
+          <t>tab.gear.replaces</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>No weapon</t>
+          <t>Replaces {item}.</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>무기 없음</t>
+          <t>{item}을(를) 대체합니다.</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>tab.gear.replaces</t>
+          <t>tab.gear.worn</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>Replaces {item}.</t>
+          <t>Worn</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>{item}을(를) 대체합니다.</t>
+          <t>착용 중</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>tab.gear.worn</t>
+          <t>tab.hint.back</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Worn</t>
+          <t>{back} Back</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>착용 중</t>
+          <t>{back} 뒤로</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>tab.hint.back</t>
+          <t>tab.hint.change</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>{back} Back</t>
+          <t>{left}{right} Change</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>{back} 뒤로</t>
+          <t>{left}{right} 변경</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>tab.hint.change</t>
+          <t>tab.hint.close</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>{left}{right} Change</t>
+          <t>{back} Close</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>{left}{right} 변경</t>
+          <t>{back} 닫기</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>tab.hint.close</t>
+          <t>tab.hint.equip</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>{back} Close</t>
+          <t>{confirm} Equip</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>{back} 닫기</t>
+          <t>{confirm} 착용</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>tab.hint.equip</t>
+          <t>tab.hint.open</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>{confirm} Equip</t>
+          <t>{confirm} Open</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>{confirm} 착용</t>
+          <t>{confirm} 열기</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>tab.hint.open</t>
+          <t>tab.hint.select</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>{confirm} Open</t>
+          <t>{confirm} Select</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>{confirm} 열기</t>
+          <t>{confirm} 선택</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>tab.hint.select</t>
+          <t>tab.hint.takeoff</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>{confirm} Select</t>
+          <t>{confirm} Take off</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>{confirm} 선택</t>
+          <t>{confirm} 해제</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>tab.hint.takeoff</t>
+          <t>tab.hint.use</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>{confirm} Take off</t>
+          <t>{confirm} Use</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>{confirm} 해제</t>
+          <t>{confirm} 사용</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>tab.hint.use</t>
+          <t>tab.hist.abandoned</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>{confirm} Use</t>
+          <t>You gave this run up on floor {n}.</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>{confirm} 사용</t>
+          <t>{n}층에서 도전을 포기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>tab.hist.abandoned</t>
+          <t>tab.hist.died</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>You gave this run up on floor {n}.</t>
+          <t>You fell on floor {n}.</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>{n}층에서 도전을 포기했습니다.</t>
+          <t>{n}층에서 쓰러졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>tab.hist.died</t>
+          <t>tab.hist.died_to</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>You fell on floor {n}.</t>
+          <t>Floor {n}: felled by {name}.</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>{n}층에서 쓰러졌습니다.</t>
+          <t>{n}층: {name}에게 쓰러졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>tab.hist.died_to</t>
+          <t>tab.hist.row</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Floor {n}: felled by {name}.</t>
+          <t>{cls} Lv {n}</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>{n}층: {name}에게 쓰러졌습니다.</t>
+          <t>{cls} Lv {n}</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>tab.hist.row</t>
+          <t>tab.hist.won</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>{cls} Lv {n}</t>
+          <t>You climbed out of the tunnel.</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>{cls} Lv {n}</t>
+          <t>터널을 빠져나왔습니다.</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>tab.hist.won</t>
+          <t>tab.items</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>You climbed out of the tunnel.</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>터널을 빠져나왔습니다.</t>
+          <t>아이템</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>tab.items</t>
+          <t>tab.items.key</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>An item you keep for the way ahead.</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>앞으로의 길을 위해 간직하는 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>tab.items.key</t>
+          <t>tab.items.none</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>An item you keep for the way ahead.</t>
+          <t>Nothing in your bag</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>앞으로의 길을 위해 간직하는 아이템입니다.</t>
+          <t>소지품이 없습니다</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>tab.items.none</t>
+          <t>tab.items.none_help</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Nothing in your bag</t>
+          <t>Potions, throwables and keys you find show up here.</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>소지품이 없습니다</t>
+          <t>찾은 물약, 투척 아이템, 열쇠가 여기에 나옵니다.</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>tab.items.none_help</t>
+          <t>tab.lbl.base</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>Potions, throwables and keys you find show up here.</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>찾은 물약, 투척 아이템, 열쇠가 여기에 나옵니다.</t>
+          <t>기본</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>tab.lbl.base</t>
+          <t>tab.lbl.best_floor</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Best floor</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>기본</t>
+          <t>최고 층</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>tab.lbl.best_floor</t>
+          <t>tab.lbl.effects</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>Best floor</t>
+          <t>Effects</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>최고 층</t>
+          <t>효과</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>tab.lbl.effects</t>
+          <t>tab.lbl.elite</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Effects</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>정예</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>tab.lbl.elite</t>
+          <t>tab.lbl.falls</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Falls</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>정예</t>
+          <t>추락</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>tab.lbl.falls</t>
+          <t>tab.lbl.floor</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Falls</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>추락</t>
+          <t>층</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>tab.lbl.floor</t>
+          <t>tab.lbl.gear</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>Gear</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>층</t>
+          <t>장비</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>tab.lbl.gear</t>
+          <t>tab.lbl.gold</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Gear</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>골드</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>tab.lbl.gold</t>
+          <t>tab.lbl.hp</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>tab.lbl.hp</t>
+          <t>tab.lbl.kills</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Foes beaten</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>처치한 적</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>tab.lbl.kills</t>
+          <t>tab.lbl.level</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>Foes beaten</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>처치한 적</t>
+          <t>레벨</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>tab.lbl.level</t>
+          <t>tab.lbl.met</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>레벨</t>
+          <t>만난 횟수</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>tab.lbl.met</t>
+          <t>tab.lbl.seed</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Seed</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>만난 횟수</t>
+          <t>시드</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>tab.lbl.seed</t>
+          <t>tab.lbl.seed_small</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Seed {n}</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>시드</t>
+          <t>시드 {n}</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>tab.lbl.seed_small</t>
+          <t>tab.lbl.total</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>Seed {n}</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>시드 {n}</t>
+          <t>합계</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>tab.lbl.total</t>
+          <t>tab.lbl.upgrade</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Upgrade</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>합계</t>
+          <t>강화</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>tab.lbl.upgrade</t>
+          <t>tab.lbl.wins</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>Upgrade</t>
+          <t>Wins</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>강화</t>
+          <t>승리</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>tab.lbl.wins</t>
+          <t>tab.lbl.xp</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>Wins</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>승리</t>
+          <t>경험치</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>tab.lbl.xp</t>
+          <t>tab.notes.unknown</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>A note you have not found yet. Look at the walls.</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>경험치</t>
+          <t>아직 찾지 못한 쪽지입니다. 벽을 살펴보세요.</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>tab.notes.unknown</t>
+          <t>tab.settings</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>A note you have not found yet. Look at the walls.</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>아직 찾지 못한 쪽지입니다. 벽을 살펴보세요.</t>
+          <t>설정</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>tab.settings</t>
+          <t>tab.skills</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>스킬</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>tab.skills</t>
+          <t>tab.skills.none</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>No skills yet</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>스킬</t>
+          <t>스킬 없음</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>tab.skills.none</t>
+          <t>tab.skills.none_help</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>No skills yet</t>
+          <t>Cards and chests teach skills. They appear here with the arrows to press.</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>스킬 없음</t>
+          <t>카드와 상자에서 스킬을 얻습니다. 누를 화살표와 함께 여기에 나옵니다.</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>tab.skills.none_help</t>
+          <t>tab.skills.passives</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Cards and chests teach skills. They appear here with the arrows to press.</t>
+          <t>Passives</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>카드와 상자에서 스킬을 얻습니다. 누를 화살표와 함께 여기에 나옵니다.</t>
+          <t>패시브</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>tab.skills.passives</t>
+          <t>tab.status</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>Passives</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>패시브</t>
+          <t>상태</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>tab.status</t>
+          <t>tab.title.codex</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>도감</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>tab.title.codex</t>
+          <t>tab.title.gear</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>Gear</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>도감</t>
+          <t>장비</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>tab.title.gear</t>
+          <t>tab.title.items</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>Gear</t>
+          <t>Items</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>아이템</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>tab.title.items</t>
+          <t>tab.title.skills</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>Items</t>
+          <t>Skills {n}/{max}</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>스킬 {n}/{max}</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>tab.title.skills</t>
+          <t>tab.title.status</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Skills {n}/{max}</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>스킬 {n}/{max}</t>
+          <t>능력치</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>tab.title.status</t>
+          <t>tab.unlock.nobody</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Nobody</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>무명</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>tab.unlock.nobody</t>
+          <t>tab.unlock.nobody_off</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Nobody</t>
+          <t>Win a run to unlock a fighter with no class.</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>무명</t>
+          <t>승리하면 직업이 없는 전사가 해금됩니다.</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>tab.unlock.nobody_off</t>
+          <t>tab.unlock.nobody_on</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>Win a run to unlock a fighter with no class.</t>
+          <t>A fighter with no class. Throws {m}x as hard and carries {cap} of each throwable.</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>승리하면 직업이 없는 전사가 해금됩니다.</t>
+          <t>직업이 없는 전사입니다. 투척 아이템을 {m}배 강하게 던지고 종류마다 {cap}개를 가질 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>tab.unlock.nobody_on</t>
+          <t>tab.val.abandoned</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>A fighter with no class. Throws {m}x as hard and carries {cap} of each throwable.</t>
+          <t>Gave up</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>직업이 없는 전사입니다. 투척 아이템을 {m}배 강하게 던지고 종류마다 {cap}개를 가질 수 있습니다.</t>
+          <t>포기</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>tab.val.abandoned</t>
+          <t>tab.val.applied</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>Gave up</t>
+          <t>Applied</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>포기</t>
+          <t>적용됨</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>tab.val.applied</t>
+          <t>tab.val.floor</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Floor {n}</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>적용됨</t>
+          <t>{n}층</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>tab.val.floor</t>
+          <t>tab.val.locked</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>Floor {n}</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>{n}층</t>
+          <t>잠김</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>tab.val.locked</t>
+          <t>tab.val.max</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>MAX</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>잠김</t>
+          <t>최대</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>tab.val.max</t>
+          <t>tab.val.none</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>MAX</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>최대</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>tab.val.none</t>
+          <t>tab.val.seen</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Seen</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>목격</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>tab.val.seen</t>
+          <t>tab.val.unlocked</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>Seen</t>
+          <t>Unlocked</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>목격</t>
+          <t>해금됨</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>tab.val.unlocked</t>
+          <t>tab.val.won</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Unlocked</t>
+          <t>Won</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>해금됨</t>
+          <t>승리</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>tab.val.won</t>
+          <t>status.desc.status_crit_up_many</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>Won</t>
+          <t>In every {n} hits, {reds} are criticals.</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>승리</t>
+          <t>{n}번 공격 중 {reds}번은 치명타입니다.</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>status.desc.status_crit_up_many</t>
+          <t>battle.action.run_no</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>In every {n} hits, {reds} are criticals.</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>{n}번 공격 중 {reds}번은 치명타입니다.</t>
+          <t>불가</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>battle.action.run_no</t>
+          <t>pause.help.in_battle</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Not available during a battle.</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>불가</t>
+          <t>전투 중에는 사용할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>pause.help.in_battle</t>
+          <t>title.splash.press_key</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Not available during a battle.</t>
+          <t>Press any key</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>전투 중에는 사용할 수 없습니다.</t>
+          <t>아무 키나 누르세요</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>title.splash.press_key</t>
+          <t>title.splash.press_button</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>Press any key</t>
+          <t>Press any button</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>아무 키나 누르세요</t>
+          <t>아무 버튼이나 누르세요</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>title.splash.press_button</t>
+          <t>title.card.cant</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>Press any button</t>
+          <t>Can't continue</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>아무 버튼이나 누르세요</t>
+          <t>이어할 수 없음</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>title.card.cant</t>
+          <t>title.card.time</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>Can't continue</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>이어할 수 없음</t>
+          <t>플레이 시간</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>title.card.time</t>
+          <t>dialogue.sys_class_chest_guard.0</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Wait, there was a chest back there. I think I should open it...</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>플레이 시간</t>
+          <t>잠깐, 저 뒤에 상자가 있었어. 열어 봐야겠어...</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>dialogue.sys_class_chest_guard.0</t>
+          <t>dialogue.sys_class_chest_guard.1</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>Wait, there was a chest back there. I think I should open it...</t>
+          <t>...there might be something I can use to protect myself.</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>잠깐, 저 뒤에 상자가 있었어. 열어 봐야겠어...</t>
+          <t>...나를 지킬 만한 뭔가가 들어 있을지도 몰라.</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>dialogue.sys_class_chest_guard.1</t>
+          <t>settings.row.rumble</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>...there might be something I can use to protect myself.</t>
+          <t>Rumble</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>...나를 지킬 만한 뭔가가 들어 있을지도 몰라.</t>
+          <t>진동</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>settings.row.rumble</t>
+          <t>settings.help.rumble</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>Rumble</t>
+          <t>Short controller vibration on Perfect hits, BREAK, big hits and defeat.</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>진동</t>
+          <t>완벽한 공격, 브레이크, 큰 피해, 쓰러질 때 컨트롤러가 짧게 진동합니다.</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>settings.help.rumble</t>
+          <t>echo.pick.title</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Short controller vibration on Perfect hits, BREAK, big hits and defeat.</t>
+          <t>Keep one skill you remember</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>완벽한 공격, 브레이크, 큰 피해, 쓰러질 때 컨트롤러가 짧게 진동합니다.</t>
+          <t>기억하는 스킬 하나를 간직합니다</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>echo.pick.title</t>
+          <t>battle.det.damage</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>Keep one echo of the last fall</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>지난 추락의 메아리 하나를 간직합니다</t>
+          <t>피해</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>battle.det.damage</t>
+          <t>battle.det.perfect</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Perfect</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>피해</t>
+          <t>완벽</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>battle.det.perfect</t>
+          <t>battle.preview.damage</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>Perfect</t>
+          <t>Damage {n}</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>완벽</t>
+          <t>피해 {n}</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>battle.preview.damage</t>
+          <t>battle.preview.perfect</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Damage {n}</t>
+          <t>Perfect {n}</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>피해 {n}</t>
+          <t>완벽 {n}</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>battle.preview.perfect</t>
+          <t>battle.preview.hits</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Perfect {n}</t>
+          <t>{n} x{hits}</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>완벽 {n}</t>
+          <t>{n} x{hits}</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>battle.preview.hits</t>
+          <t>battle.speed.mark</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>{n} x{hits}</t>
+          <t>x2</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>{n} x{hits}</t>
+          <t>x2</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>battle.speed.mark</t>
+          <t>tab.system</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>시스템</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>tab.system</t>
+          <t>tab.title.system</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -18021,204 +18021,204 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>tab.title.system</t>
+          <t>tab.system.quit_battle_help</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Goes back to the title. Continue puts you back just before this fight.</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>타이틀로 나갑니다. 이어하기를 하면 이 전투 직전부터 다시 시작합니다.</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>tab.system.quit_battle_help</t>
+          <t>settings.keep.title</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Goes back to the title. Continue puts you back just before this fight.</t>
+          <t>Keep this setting?</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>타이틀로 나갑니다. 이어하기를 하면 이 전투 직전부터 다시 시작합니다.</t>
+          <t>이 설정을 유지할까요?</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>settings.keep.title</t>
+          <t>settings.keep.body</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>Keep this setting?</t>
+          <t>It goes back by itself in {n} s.</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>이 설정을 유지할까요?</t>
+          <t>{n}초 뒤에 자동으로 원래대로 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>settings.keep.body</t>
+          <t>settings.keep.hint</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>It goes back by itself in {n} s.</t>
+          <t>{confirm} Keep   {back} Revert</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>{n}초 뒤에 자동으로 원래대로 돌아갑니다.</t>
+          <t>{confirm} 유지   {back} 되돌리기</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>settings.keep.hint</t>
+          <t>confirm.abandon</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>{confirm} Keep   {back} Revert</t>
+          <t>Abandon this run? It counts as a death, but you keep the echo.</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>{confirm} 유지   {back} 되돌리기</t>
+          <t>이번 도전을 포기할까요? 죽은 것으로 기록되지만 메아리는 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>confirm.abandon</t>
+          <t>confirm.quit</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>Abandon this run? It counts as a death, but you keep the echo.</t>
+          <t>Quit to title? The run is saved and Continue picks it up again.</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>이번 도전을 포기할까요? 죽은 것으로 기록되지만 메아리는 남습니다.</t>
+          <t>타이틀로 나갈까요? 도전은 저장되며 이어하기로 계속할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>confirm.quit</t>
+          <t>confirm.quit_battle</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>Quit to title? The run is saved and Continue picks it up again.</t>
+          <t>Quit to title? Continue puts you back just before this fight.</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>타이틀로 나갈까요? 도전은 저장되며 이어하기로 계속할 수 있습니다.</t>
+          <t>타이틀로 나갈까요? 이어하기를 하면 이 전투 직전으로 돌아옵니다.</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>confirm.quit_battle</t>
+          <t>confirm.new_game</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>Quit to title? Continue puts you back just before this fight.</t>
+          <t>Start a new game? The saved run will be abandoned.</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>타이틀로 나갈까요? 이어하기를 하면 이 전투 직전으로 돌아옵니다.</t>
+          <t>새 게임을 시작할까요? 저장된 도전은 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>confirm.new_game</t>
+          <t>confirm.echo</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>Start a new game? The saved run will be abandoned.</t>
+          <t>Keep {name} as your echo?</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>새 게임을 시작할까요? 저장된 도전은 사라집니다.</t>
+          <t>{name}을(를) 메아리로 남길까요?</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>confirm.echo</t>
+          <t>confirm.replace</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>Keep {name} as your echo?</t>
+          <t>Forget {forget} and learn {learn}?</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>{name}을(를) 메아리로 남길까요?</t>
+          <t>{forget}을(를) 잊고 {learn}을(를) 배울까요?</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>confirm.replace</t>
+          <t>confirm.sell</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>Forget {forget} and learn {learn}?</t>
+          <t>Sell {name} for {price}?</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>{forget}을(를) 잊고 {learn}을(를) 배울까요?</t>
+          <t>{name}을(를) {price}에 팔까요?</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>confirm.sell</t>
+          <t>class.skill.unknown</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Sell {name} for {price}?</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>{name}을(를) {price}에 팔까요?</t>
+          <t>???</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Received {item} x{qty}.</t>
+          <t>Received [a]{item}[/a] x{qty}.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{item} x{qty}을(를) 받았습니다.</t>
+          <t>[a]{item}[/a] x{qty}을(를) 받았습니다.</t>
         </is>
       </c>
     </row>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>A Weak press counts as OK (once per turn)</t>
+          <t>A [t]Weak[/t] press counts as [t]OK[/t] (once per turn)</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>약함 판정이 무난으로 처리됩니다 (턴당 1회)</t>
+          <t>[t]약함[/t] 판정이 [t]무난[/t]으로 처리됩니다 (턴당 1회)</t>
         </is>
       </c>
     </row>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>First hit: -1 DEF for 2 turns</t>
+          <t>First hit: -1 [t]DEF[/t] for 2 turns</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>첫 타격: 2턴 동안 DEF -1</t>
+          <t>첫 타격: 2턴 동안 [t]DEF[/t] -1</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>+1 MP every 2 turns, +1 physical damage taken</t>
+          <t>+1 [t]MP[/t] every 2 turns, +1 physical damage taken</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2턴마다 MP +1, 받는 물리 피해 +1</t>
+          <t>2턴마다 [t]MP[/t] +1, 받는 물리 피해 +1</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Reflects the first status (costs 1 MP)</t>
+          <t>Reflects the first status (costs 1 [t]MP[/t])</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>첫 상태 이상을 반사 (MP 1 소모)</t>
+          <t>첫 상태 이상을 반사 ([t]MP[/t] 1 소모)</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>+35% damage to foes below 35% HP</t>
+          <t>+35% damage to foes below 35% [t]HP[/t]</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>HP 35% 미만 적에게 피해 +35%</t>
+          <t>[t]HP[/t] 35% 미만 적에게 피해 +35%</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>A Good press counts as Perfect (once per turn)</t>
+          <t>A [t]Good[/t] press counts as [a]Perfect[/a] (once per turn)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>좋음 판정이 완벽으로 처리됩니다 (턴당 1회)</t>
+          <t>[t]좋음[/t] 판정이 [a]완벽[/a]으로 처리됩니다 (턴당 1회)</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Good or Perfect: may Stun (3-turn cooldown)</t>
+          <t>[t]Good[/t] or [a]Perfect[/a]: may [t]Stun[/t] (3-turn cooldown)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>좋음 이상: 기절시킬 수 있음 (재사용 3턴)</t>
+          <t>[t]좋음[/t] 또는 [a]완벽[/a]: [t]기절[/t]시킬 수 있음 (재사용 3턴)</t>
         </is>
       </c>
     </row>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>+1 MP every 2 turns</t>
+          <t>+1 [t]MP[/t] every 2 turns</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2턴마다 MP +1</t>
+          <t>2턴마다 [t]MP[/t] +1</t>
         </is>
       </c>
     </row>
@@ -5123,12 +5123,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>+25% skill damage, Perfect +1 MP</t>
+          <t>+25% skill damage, [a]Perfect[/a] +1 [t]MP[/t]</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>스킬 피해 +25%, 완벽 판정 시 MP +1</t>
+          <t>스킬 피해 +25%, [a]완벽[/a] 판정 시 [t]MP[/t] +1</t>
         </is>
       </c>
     </row>
@@ -6500,12 +6500,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Increases spell damage and max MP.</t>
+          <t>Increases spell damage and max [t]MP[/t].</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>마법 피해와 최대 MP를 늘립니다.</t>
+          <t>마법 피해와 최대 [t]MP[/t]를 늘립니다.</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Increases physical damage (basic attacks and ATK skills).</t>
+          <t>Increases physical damage (basic attacks and [t]ATK[/t] skills).</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>물리 피해(기본 공격과 ATK 스킬)를 늘립니다.</t>
+          <t>물리 피해(기본 공격과 [t]ATK[/t] 스킬)를 늘립니다.</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Lose {tick} HP each turn, then 1 stack fades ({stacks} stacks, max {max}).{mods}</t>
+          <t>Lose {tick} [t]HP[/t] each turn, then 1 stack fades ({stacks} stacks, max {max}).{mods}</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>매 턴 {tick} HP를 잃고, 중첩이 1 줄어듭니다 ({stacks}중첩, 최대 {max}).{mods}</t>
+          <t>매 턴 {tick} [t]HP[/t]를 잃고, 중첩이 1 줄어듭니다 ({stacks}중첩, 최대 {max}).{mods}</t>
         </is>
       </c>
     </row>
@@ -8574,12 +8574,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Lose HP equal to its stacks each turn, then 1 stack fades. Stacks up to {max}.{mods}</t>
+          <t>Lose [t]HP[/t] equal to its stacks each turn, then 1 stack fades. Stacks up to {max}.{mods}</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>매 턴 중첩 수만큼 HP를 잃고, 중첩이 1 줄어듭니다. 최대 {max}중첩.{mods}</t>
+          <t>매 턴 중첩 수만큼 [t]HP[/t]를 잃고, 중첩이 1 줄어듭니다. 최대 {max}중첩.{mods}</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Lose {tick} HP each time you act ({stacks} stacks, max {max}), for {turns} more turns.{mods}</t>
+          <t>Lose {tick} [t]HP[/t] each time you act ({stacks} stacks, max {max}), for {turns} more turns.{mods}</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>행동할 때마다 {tick} HP를 잃습니다 ({stacks}중첩, 최대 {max}). {turns}턴 더 지속.{mods}</t>
+          <t>행동할 때마다 {tick} [t]HP[/t]를 잃습니다 ({stacks}중첩, 최대 {max}). {turns}턴 더 지속.{mods}</t>
         </is>
       </c>
     </row>
@@ -8608,12 +8608,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Lose {tick} HP per stack each time you act. Stacks up to {max}, lasts {dur} turns.{mods}</t>
+          <t>Lose {tick} [t]HP[/t] per stack each time you act. Stacks up to {max}, lasts {dur} turns.{mods}</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>행동할 때마다 중첩당 {tick} HP를 잃습니다. 최대 {max}중첩, {dur}턴 지속.{mods}</t>
+          <t>행동할 때마다 중첩당 {tick} [t]HP[/t]를 잃습니다. 최대 {max}중첩, {dur}턴 지속.{mods}</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Lose {tick} HP each turn for {turns} more turns.{mods}</t>
+          <t>Lose {tick} [t]HP[/t] each turn for {turns} more turns.{mods}</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>매 턴 {tick} HP를 잃습니다. {turns}턴 더 지속.{mods}</t>
+          <t>매 턴 {tick} [t]HP[/t]를 잃습니다. {turns}턴 더 지속.{mods}</t>
         </is>
       </c>
     </row>
@@ -8642,12 +8642,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Lose a fixed amount of HP (it grows with the caster's MAG) each turn for {dur} turns. Does not stack.{mods}</t>
+          <t>Lose a fixed amount of [t]HP[/t] (it grows with the caster's [t]MAG[/t]) each turn for {dur} turns. Does not stack.{mods}</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>매 턴 정해진 HP(시전자의 MAG에 비례)를 {dur}턴 동안 잃습니다. 중첩되지 않습니다.{mods}</t>
+          <t>매 턴 정해진 [t]HP[/t](시전자의 [t]MAG[/t]에 비례)를 {dur}턴 동안 잃습니다. 중첩되지 않습니다.{mods}</t>
         </is>
       </c>
     </row>
@@ -8659,12 +8659,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Pushed back on the turn bar. Then Steadfast: cannot be stunned for 2 turns.</t>
+          <t>Pushed back on the turn bar. Then [t]Steadfast[/t]: cannot be stunned for 2 turns.</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>차례가 뒤로 밀립니다. 이후 2턴간 버티기 상태가 되어 기절하지 않습니다.</t>
+          <t>차례가 뒤로 밀립니다. 이후 2턴간 [t]버티기[/t] 상태가 되어 [t]기절[/t]하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>For {turns} turns: you see the enemy's next move and every Perfect zone is {pct}% wider.</t>
+          <t>For {turns} turns: you see the enemy's next move and every [a]Perfect[/a] zone is {pct}% wider.</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>{turns}턴 동안 적의 다음 행동이 보이고 모든 완벽 구간이 {pct}% 넓어집니다.</t>
+          <t>{turns}턴 동안 적의 다음 행동이 보이고 모든 [a]완벽[/a] 구간이 {pct}% 넓어집니다.</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8761,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Recover {n} MP each turn.</t>
+          <t>Recover {n} [t]MP[/t] each turn.</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>매 턴 MP를 {n} 회복합니다.</t>
+          <t>매 턴 [t]MP[/t]를 {n} 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Press confirm to go on</t>
+          <t>Press [k:confirm] to go on</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>확인을 눌러 계속</t>
+          <t>[k:confirm]을(를) 눌러 계속</t>
         </is>
       </c>
     </row>
@@ -9169,12 +9169,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Up / Down to choose, confirm to take it</t>
+          <t>[k:up][k:down] Choose   [k:confirm] Take it</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>위/아래로 선택, 확인으로 가져가기</t>
+          <t>[k:up][k:down] 고르기   [k:confirm] 가져가기</t>
         </is>
       </c>
     </row>
@@ -9934,12 +9934,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Gain {status} for {turns} turns.</t>
+          <t>Gain [t]{status}[/t] for {turns} turns.</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>{status} 효과를 {turns}턴 동안 얻는다.</t>
+          <t>[t]{status}[/t] 효과를 {turns}턴 동안 얻는다.</t>
         </is>
       </c>
     </row>
@@ -9968,12 +9968,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>{chance}% to inflict {status}.</t>
+          <t>{chance}% to inflict [t]{status}[/t].</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>{chance}% 확률로 {status} 부여.</t>
+          <t>{chance}% 확률로 [t]{status}[/t] 부여.</t>
         </is>
       </c>
     </row>
@@ -10104,12 +10104,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>{left}{right} Choose   {confirm} Take</t>
+          <t>[k:left][k:right] Choose   [k:confirm] Take</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>{left}{right} 고르기   {confirm} 받기</t>
+          <t>[k:left][k:right] 고르기   [k:confirm] 받기</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>빠르고 날카롭다. 높은 속도, 독과 연속 사격을 찾아보자.</t>
+          <t>빠르고 날카롭다. 높은 속도, [t]독[/t]과 연속 사격을 찾아보자.</t>
         </is>
       </c>
     </row>
@@ -10359,12 +10359,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>A spell caster. Great magic and MP, five skills to find.</t>
+          <t>A spell caster. Great magic and [t]MP[/t], five skills to find.</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>주문 시전자. 뛰어난 마법과 MP, 찾아야 할 스킬 5개.</t>
+          <t>주문 시전자. 뛰어난 마법과 [t]MP[/t], 찾아야 할 스킬 5개.</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10495,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Light on your feet: +{n} SPD for good.</t>
+          <t>Light on your feet: +{n} [t]SPD[/t] for good.</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>가벼운 발걸음: 영구히 SPD +{n}.</t>
+          <t>가벼운 발걸음: 영구히 [t]SPD[/t] +{n}.</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Poison you apply adds {n} extra stack.</t>
+          <t>[t]Poison[/t] you apply adds {n} extra stack.</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>내가 거는 독이 {n}중첩 더 쌓인다.</t>
+          <t>내가 거는 [t]독[/t]이 {n}중첩 더 쌓인다.</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Restore {n} HP after each fight you win.</t>
+          <t>Restore {n} [t]HP[/t] after each fight you win.</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>전투에서 이길 때마다 HP를 {n} 회복한다.</t>
+          <t>전투에서 이길 때마다 [t]HP[/t]를 {n} 회복한다.</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10597,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Perfect zones are {n}% wider.</t>
+          <t>[a]Perfect[/a] zones are {n}% wider.</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>완벽 구간이 {n}% 넓어진다.</t>
+          <t>[a]완벽[/a] 구간이 {n}% 넓어진다.</t>
         </is>
       </c>
     </row>
@@ -10665,12 +10665,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Regain {n} MP at the start of each of your turns.</t>
+          <t>Regain {n} [t]MP[/t] at the start of each of your turns.</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>내 턴이 시작될 때마다 MP를 {n} 회복한다.</t>
+          <t>내 턴이 시작될 때마다 [t]MP[/t]를 {n} 회복한다.</t>
         </is>
       </c>
     </row>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Enemies start each fight with {n} stagger.</t>
+          <t>Enemies start each fight with {n} [t]stagger[/t].</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>전투가 시작될 때 적의 경직이 {n} 쌓여 있다.</t>
+          <t>전투가 시작될 때 적의 [t]경직[/t]이 {n} 쌓여 있다.</t>
         </is>
       </c>
     </row>
@@ -10767,12 +10767,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Thicker hide: +{n} DEF for good.</t>
+          <t>Thicker hide: +{n} [t]DEF[/t] for good.</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>두꺼운 가죽: 영구히 DEF +{n}.</t>
+          <t>두꺼운 가죽: 영구히 [t]DEF[/t] +{n}.</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Guard on yourself lasts {n} turns longer.</t>
+          <t>[t]Guard[/t] on yourself lasts {n} turns longer.</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>A harder swing: +{n} ATK for good.</t>
+          <t>A harder swing: +{n} [t]ATK[/t] for good.</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>더 묵직한 일격: 영구히 ATK +{n}.</t>
+          <t>더 묵직한 일격: 영구히 [t]ATK[/t] +{n}.</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Quicker than the wind: +{n} SPD for good.</t>
+          <t>Quicker than the wind: +{n} [t]SPD[/t] for good.</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>바람보다 빠르게: 영구히 SPD +{n}.</t>
+          <t>바람보다 빠르게: 영구히 [t]SPD[/t] +{n}.</t>
         </is>
       </c>
     </row>
@@ -10937,12 +10937,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Regain {n} MP after each fight you win.</t>
+          <t>Regain {n} [t]MP[/t] after each fight you win.</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>전투에서 이길 때마다 MP를 {n} 회복한다.</t>
+          <t>전투에서 이길 때마다 [t]MP[/t]를 {n} 회복한다.</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>A deeper well: +{n} MAG for good.</t>
+          <t>A deeper well: +{n} [t]MAG[/t] for good.</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>더 깊은 샘: 영구히 MAG +{n}.</t>
+          <t>더 깊은 샘: 영구히 [t]MAG[/t] +{n}.</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Your skills cost {n} MP less (never below 1).</t>
+          <t>Your skills cost {n} [t]MP[/t] less (never below 1).</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>스킬의 MP 소모가 {n} 줄어든다 (최소 1).</t>
+          <t>스킬의 [t]MP[/t] 소모가 {n} 줄어든다 (최소 1).</t>
         </is>
       </c>
     </row>
@@ -11073,12 +11073,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Healing potions also restore {n} MP.</t>
+          <t>Healing potions also restore {n} [t]MP[/t].</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>회복 물약이 MP도 {n} 회복시킨다.</t>
+          <t>회복 물약이 [t]MP[/t]도 {n} 회복시킨다.</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Restore {n}% of your HP and MP now.</t>
+          <t>Restore {n}% of your [t]HP[/t] and [t]MP[/t] now.</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>지금 HP와 MP를 {n}% 회복한다.</t>
+          <t>지금 [t]HP[/t]와 [t]MP[/t]를 {n}% 회복한다.</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>적에게 독 {n}중첩을 겁니다. 턴을 소모합니다.</t>
+          <t>적에게 [t]독[/t] {n}중첩을 겁니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>위력 {power}의 피해를 주고 기절시켜 적을 뒤로 밉니다. 턴을 소모합니다.</t>
+          <t>위력 {power}의 피해를 주고 [t]기절[/t]시켜 적을 뒤로 밉니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13096,12 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Throw it to dodge the next attack ({turns} turns); a Perfect throw lets you slip away. Costs your turn.</t>
+          <t>Throw it to dodge the next attack ({turns} turns); a [a]Perfect[/a] throw lets you slip away. Costs your turn.</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>다음 공격을 피합니다({turns}턴). 완벽하게 던지면 도망칩니다. 턴을 소모합니다.</t>
+          <t>다음 공격을 피합니다({turns}턴). [a]완벽[/a]하게 던지면 도망칩니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
@@ -13181,12 +13181,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Restores {n} HP.</t>
+          <t>Restores {n} [t]HP[/t].</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>HP를 {n}만큼 회복합니다.</t>
+          <t>[t]HP[/t]를 {n}만큼 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -13198,12 +13198,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Restores {n} MP.</t>
+          <t>Restores {n} [t]MP[/t].</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>MP를 {n}만큼 회복합니다.</t>
+          <t>[t]MP[/t]를 {n}만큼 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -14405,12 +14405,12 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>+1 MP every 3 turns</t>
+          <t>+1 [t]MP[/t] every 3 turns</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>3턴마다 MP +1</t>
+          <t>3턴마다 [t]MP[/t] +1</t>
         </is>
       </c>
     </row>
@@ -14507,12 +14507,12 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>A cursor slides along the bar. Press {confirm} when it is over the bright zone. The closer to the middle, the harder you hit.</t>
+          <t>A cursor slides along the bar. Press [k:confirm] when it is over the bright zone. The closer to the middle, the harder you hit.</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>커서가 막대를 따라 움직입니다. 밝은 구간 위에 왔을 때 {confirm}을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
+          <t>커서가 막대를 따라 움직입니다. 밝은 구간 위에 왔을 때 [k:confirm]을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
         </is>
       </c>
     </row>
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Skills show a row of arrows. Press {up}{down}{left}{right} in that order before the time bar runs out. A wrong press costs time.</t>
+          <t>Skills show a row of arrows. Press [k:up][k:down][k:left][k:right] in that order before the time bar runs out. A wrong press costs time.</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>스킬을 쓰면 화살표 줄이 나옵니다. 시간 막대가 다 줄기 전에 {up}{down}{left}{right}으로 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
+          <t>스킬을 쓰면 화살표 줄이 나옵니다. 시간 막대가 다 줄기 전에 [k:up][k:down][k:left][k:right]으로 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
         </is>
       </c>
     </row>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>When an enemy winds up a big attack, a bar appears. Press {confirm} on the bright zone to take less damage and shake off its effects.</t>
+          <t>When an enemy winds up a big attack, a bar appears. Press [k:confirm] on the bright zone to take less damage and shake off its effects.</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>적이 큰 공격을 준비하면 막대가 나타납니다. 밝은 구간에서 {confirm}을(를) 누르면 피해가 줄고 부가 효과도 털어냅니다.</t>
+          <t>적이 큰 공격을 준비하면 막대가 나타납니다. 밝은 구간에서 [k:confirm]을(를) 누르면 피해가 줄고 부가 효과도 털어냅니다.</t>
         </is>
       </c>
     </row>
@@ -14609,12 +14609,12 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Good hits fill the enemy's stagger meter. When it is full the enemy goes into BREAK: it loses a turn and takes +50% damage.</t>
+          <t>[t]Good[/t] hits fill the enemy's [t]stagger[/t] meter. When it is full the enemy goes into [a]BREAK[/a]: it loses a turn and takes +50% damage.</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>좋은 공격은 적의 경직 게이지를 채웁니다. 가득 차면 적이 브레이크 상태가 되어 한 턴을 잃고 피해를 50% 더 받습니다.</t>
+          <t>좋은 공격은 적의 [t]경직[/t] 게이지를 채웁니다. 가득 차면 적이 [a]브레이크[/a] 상태가 되어 한 턴을 잃고 피해를 50% 더 받습니다.</t>
         </is>
       </c>
     </row>
@@ -14745,12 +14745,12 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Each bed can be used once per run. Rest to restore all your HP and MP, or use it to upgrade one of your skills.</t>
+          <t>Each bed can be used once per run. Rest to restore all your [t]HP[/t] and [t]MP[/t], or use it to upgrade one of your skills.</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>침대는 도전마다 한 번씩만 쓸 수 있습니다. 쉬어서 HP와 MP를 모두 채우거나, 스킬 하나를 강화하세요.</t>
+          <t>침대는 도전마다 한 번씩만 쓸 수 있습니다. 쉬어서 [t]HP[/t]와 [t]MP[/t]를 모두 채우거나, 스킬 하나를 강화하세요.</t>
         </is>
       </c>
     </row>
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Marked enemies are Elites. They are tougher than normal ones, but their rewards are better.</t>
+          <t>Marked enemies are [t]Elites[/t]. They are tougher than normal ones, but their rewards are better.</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>표시가 붙은 적은 정예입니다. 일반 적보다 강하지만 보상이 더 좋습니다.</t>
+          <t>표시가 붙은 적은 [t]정예[/t]입니다. 일반 적보다 강하지만 보상이 더 좋습니다.</t>
         </is>
       </c>
     </row>
@@ -14813,12 +14813,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Poison, Burn, Bleed and Stun last a few turns. The icons under a name show which ones a fighter has.</t>
+          <t>[t]Poison[/t], [t]Burn[/t], [t]Bleed[/t] and [t]Stun[/t] last a few turns. The icons under a name show which ones a fighter has.</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>독, 화상, 출혈, 기절은 몇 턴 동안 이어집니다. 이름 아래 아이콘이 걸려 있는 상태를 보여 줍니다.</t>
+          <t>[t]독[/t], [t]화상[/t], [t]출혈[/t], [t]기절[/t]은 몇 턴 동안 이어집니다. 이름 아래 아이콘이 걸려 있는 상태를 보여 줍니다.</t>
         </is>
       </c>
     </row>
@@ -14830,12 +14830,12 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>{confirm} Continue</t>
+          <t>[k:confirm] Continue</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>{confirm} 계속</t>
+          <t>[k:confirm] 계속</t>
         </is>
       </c>
     </row>
@@ -15697,12 +15697,12 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>Restores your HP.</t>
+          <t>Restores your [t]HP[/t].</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>HP를 회복합니다.</t>
+          <t>[t]HP[/t]를 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -15714,12 +15714,12 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Restores your MP.</t>
+          <t>Restores your [t]MP[/t].</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>MP를 회복합니다.</t>
+          <t>[t]MP[/t]를 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -15731,12 +15731,12 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Cures {status}.</t>
+          <t>Cures [t]{status}[/t].</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>{status} 상태를 치료합니다.</t>
+          <t>[t]{status}[/t] 상태를 치료합니다.</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>기절하지 않습니다.</t>
+          <t>[t]기절[/t]하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>{confirm} Choose   {back} Back</t>
+          <t>[k:confirm] Choose</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>{confirm} 선택   {back} 뒤로</t>
+          <t>[k:confirm] 선택</t>
         </is>
       </c>
     </row>
@@ -16734,12 +16734,12 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>{back} Back</t>
+          <t>[k:back] Back</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>{back} 뒤로</t>
+          <t>[k:back] 뒤로</t>
         </is>
       </c>
     </row>
@@ -16751,12 +16751,12 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>{left}{right} Change</t>
+          <t>[k:left][k:right] Change</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>{left}{right} 변경</t>
+          <t>[k:left][k:right] 변경</t>
         </is>
       </c>
     </row>
@@ -16768,12 +16768,12 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>{back} Close</t>
+          <t>[k:back] Close</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>{back} 닫기</t>
+          <t>[k:back] 닫기</t>
         </is>
       </c>
     </row>
@@ -16785,12 +16785,12 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>{confirm} Equip</t>
+          <t>[k:confirm] Equip</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>{confirm} 착용</t>
+          <t>[k:confirm] 착용</t>
         </is>
       </c>
     </row>
@@ -16802,12 +16802,12 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>{confirm} Open</t>
+          <t>[k:confirm] Open</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>{confirm} 열기</t>
+          <t>[k:confirm] 열기</t>
         </is>
       </c>
     </row>
@@ -16819,12 +16819,12 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>{confirm} Select</t>
+          <t>[k:confirm] Select</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>{confirm} 선택</t>
+          <t>[k:confirm] 선택</t>
         </is>
       </c>
     </row>
@@ -16836,12 +16836,12 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>{confirm} Take off</t>
+          <t>[k:confirm] Take off</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>{confirm} 해제</t>
+          <t>[k:confirm] 해제</t>
         </is>
       </c>
     </row>
@@ -16853,12 +16853,12 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>{confirm} Use</t>
+          <t>[k:confirm] Use</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>{confirm} 사용</t>
+          <t>[k:confirm] 사용</t>
         </is>
       </c>
     </row>
@@ -18213,12 +18213,12 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Raises your max HP by {n} and heals {n} HP.</t>
+          <t>Raises your max [t]HP[/t] by {n} and heals {n} [t]HP[/t].</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>최대 HP가 {n} 오르고 HP를 {n} 회복합니다.</t>
+          <t>최대 [t]HP[/t]가 {n} 오르고 [t]HP[/t]를 {n} 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Raises your max MP by {n} and restores {n} MP.</t>
+          <t>Raises your max [t]MP[/t] by {n} and restores {n} [t]MP[/t].</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>최대 MP가 {n} 오르고 MP를 {n} 회복합니다.</t>
+          <t>최대 [t]MP[/t]가 {n} 오르고 [t]MP[/t]를 {n} 회복합니다.</t>
         </is>
       </c>
     </row>
@@ -18332,12 +18332,12 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>{confirm} Keep   {back} Revert</t>
+          <t>[k:confirm] Keep   [k:back] Revert</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>{confirm} 유지   {back} 되돌리기</t>
+          <t>[k:confirm] 유지   [k:back] 되돌리기</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1054"/>
+  <dimension ref="A1:C1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Worn</t>
+          <t>Equipped</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Nothing worn</t>
+          <t>Nothing equipped</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>Nothing is worn in this slot.</t>
+          <t>Nothing is equipped in this slot.</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Worn</t>
+          <t>Equipped</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -18338,6 +18338,686 @@
       <c r="C1054" t="inlineStr">
         <is>
           <t>{confirm} 유지   {back} 되돌리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>status.short.status_poison</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>PSN</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>독</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>status.short.status_bleed</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>BLD</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>status.short.status_burn</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>status.short.status_stun</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>STN</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>기절</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>status.short.status_guard</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>GRD</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>방어</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>status.short.status_dmg_up</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>REV</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>기세</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>status.short.status_evasion</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>EVA</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>회피</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>status.short.status_crit_up</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>AIM</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>조준</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>status.short.status_hit_up</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>FORE</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>선견</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>status.short.status_meditation</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>명상</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>status.short.status_solidify</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>굳힘</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>status.short.status_bloodthirsty</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Thirst</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>갈증</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>status.short.status_blessing</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>축복</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>status.short.status_sunder</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Sunder</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>분쇄</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>status.short.status_brace</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Brace</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>태세</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>battle.chip.steadfast.short</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Steady</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>버티기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>battle.chip.break.short</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>브레이크</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>status.turns_left</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>{turns} turns left.</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>{turns}턴 남았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>status.turn_left</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>1 turn left.</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>1턴 남았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>bed.msg.rested</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>You are already rested.</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>이미 충분히 쉬었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>bed.msg.nothing_to_upgrade</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Nothing to upgrade there.</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>강화할 수 있는 것이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>bed.help.heal_rested</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>You are already rested. Come back when HP or MP is missing.</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>이미 충분히 쉬었습니다. HP나 MP가 줄었을 때 다시 오세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>item.msg.nothing_happens</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Nothing happens.</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>아무 일도 일어나지 않았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>help.stats.title</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Stats &amp; terms</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>능력치와 용어</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>help.stats.help</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>What Power, ATK, DEF, MAG, SPD, Crit, the grades, BREAK and every status mean.</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>위력, ATK, DEF, MAG, SPD, 치명타, 등급, 브레이크와 모든 상태 이상의 뜻입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>help.term.crit</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>치명타</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>help.term.good</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>좋음</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>help.term.ok</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>무난</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>help.term.weak</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>약함</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>help.term.break</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>브레이크</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>help.line.power</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>How hard a weapon or skill hits. More Power means more damage.</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>무기나 스킬의 타격 세기입니다. 위력이 높을수록 피해가 커집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>help.line.hp</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Health. At 0 HP you fall.</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>체력입니다. HP가 0이 되면 쓰러집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>help.line.mp</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Magic points. Skills spend them; potions and rest restore them.</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>스킬을 쓰면 줄어드는 마력입니다. 물약과 휴식으로 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>help.line.crit</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>A critical hit deals {mult} times the damage. Take Aim and some gear raise the odds.</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>치명타는 피해를 {mult}배로 줍니다. 조준과 일부 장비가 확률을 높입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>help.line.perfect</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Press in the bright zone of the bar for +{pct}% damage.</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>막대의 밝은 구간에서 누르면 피해가 {pct}% 늘어납니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>help.line.good</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Press near the middle for +{pct}% damage.</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>가운데 근처에서 누르면 피해가 {pct}% 늘어납니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>help.line.ok</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Press on the bar but off the middle for normal damage.</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>막대 위에서 가운데를 벗어나 누르면 보통 피해를 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>help.line.weak</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Miss the zone and the hit deals {pct}% less damage.</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>구간을 놓치면 피해가 {pct}% 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>help.line.break</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Good hits fill the stagger meter. When it is full the enemy loses a turn and takes +{pct}% damage.</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>좋은 공격은 경직 게이지를 채웁니다. 가득 차면 적이 한 턴을 잃고 피해를 {pct}% 더 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>help.line.elite</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>A marked, tougher enemy with a special trait. Its rewards are better.</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>표시가 붙은 더 강한 적으로, 특별한 특성이 있습니다. 보상이 더 좋습니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1111"/>
+  <dimension ref="A1:C1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -19310,6 +19310,686 @@
         </is>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>choice.stranger.ask.0</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>There you are.</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>거기 있었군.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>choice.stranger.ask.1</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Do you remember me?</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>나를 기억해?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>choice.stranger.label.0</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Should I?</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>기억해야 해?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>choice.stranger.label.1</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Back off.</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>저리 가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>choice.stranger.reply1.0</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Not yet.</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>아직은 아니야.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>choice.stranger.reply1.1</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Ask again when the tunnel has had you a few more times.</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>터널이 널 몇 번 더 삼키면 다시 물어봐.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>choice.stranger.reply2.0</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Ha. Fair.</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>하하, 그렇겠지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>choice.stranger.reply2.1</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Nobody does, at first.</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>처음엔 다들 그래.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>choice.stranger.again1.0</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Still asking if you should?</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>아직도 기억해야 하는지 묻는군?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>choice.stranger.again1.1</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>You'll know me when you stop asking.</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>묻기를 그만두면 알게 될 거야.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>choice.stranger.again2.0</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Still telling me to back off?</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>아직도 저리 가라고 하는군?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>choice.stranger.again2.1</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>I'm patient. I've had practice.</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>난 참을성이 있어. 연습을 많이 했거든.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>choice.merchant.ask.0</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Tell me, friend.</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>말해 봐, 친구.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>choice.merchant.ask.1</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Looking for a way out, or something to buy?</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>나갈 길을 찾는 거야, 아니면 살 게 있는 거야?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>choice.merchant.label.0</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>A way out.</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>나갈 길.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>choice.merchant.label.1</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Something to buy.</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>살 물건.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>choice.merchant.reply1.0</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Ha. They all say that.</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>하하, 다들 그렇게 말하지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>choice.merchant.reply1.1</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Shop first. Hope walks better with a full pack.</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>일단 사. 짐이 든든해야 희망도 잘 걷거든.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>choice.merchant.reply2.0</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Good. Buying I understand.</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>좋아. 장사라면 내가 잘 알지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>choice.merchant.reply2.1</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Asking after exits gets people killed.</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>출구를 캐묻다 죽은 사람이 한둘이 아니야.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>choice.merchant.again1.0</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Found your way out yet? No? Then buy something.</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>나갈 길은 찾았어? 아직이면 뭐라도 사.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>choice.merchant.again2.0</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Back to spend, I hope. That I understand.</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>돈 쓰러 왔길 바란다. 그거라면 내가 잘 알지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>choice.map_page.ask.0</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>You read it twice.</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>두 번 읽는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>choice.map_page.ask.1</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Whose hand is this?</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>누구의 글씨일까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>choice.map_page.label.0</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Mine.</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>내 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>choice.map_page.label.1</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Someone else's.</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>남의 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>choice.map_page.reply1.0</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Yours. You say it out loud.</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>내 글씨다. 소리 내어 말해 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>choice.map_page.reply1.1</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>The ink seems to settle.</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>잉크가 가라앉는 듯하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>choice.map_page.reply2.0</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Not yours. You say it out loud.</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>내 글씨가 아니다. 소리 내어 말해 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>choice.map_page.reply2.1</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>The ink shivers.</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>잉크가 떨리는 듯하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>choice.map_page.again1.0</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>The ink is dry now. You've stopped doubting the hand.</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>잉크가 말랐다. 이 글씨를 더는 의심하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>choice.map_page.again2.0</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>The ink is dry now. You still say it isn't yours.</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>잉크가 말랐다. 그래도 내 글씨가 아니라고 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>choice.wake.ask.0</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Your head swims.</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>머리가 어지럽다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>choice.wake.ask.1</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Your body waits for you to decide.</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>몸이 당신의 결정을 기다린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>choice.wake.label.0</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Sit up.</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>일어난다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>choice.wake.label.1</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Lie still.</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>가만히 있는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>choice.wake.reply1.0</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>You push up. The stone lets go of your back slowly.</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>몸을 일으킨다. 돌바닥이 등을 천천히 놓아 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>choice.wake.reply2.0</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>You lie still. The ceiling says nothing. Neither do you.</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>가만히 누워 있다. 천장은 말이 없다. 당신도 그렇다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>choice.wake.again1.0</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Your body already knows how to get up.</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>몸은 이미 일어나는 법을 안다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>choice.wake.again2.0</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>You lie still a while first. You always do now.</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>먼저 한참 누워 있는다. 이제는 늘 그렇다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1111"/>
+  <dimension ref="A1:C1113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -19310,6 +19310,40 @@
         </is>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>menu.msg.items_in_fight</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>In a fight, use ITEM in the battle menu.</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>전투 중에는 전투 메뉴의 아이템을 사용하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>menu.msg.gear_in_fight</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>You can't change gear in a fight.</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>전투 중에는 장비를 바꿀 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1151"/>
+  <dimension ref="A1:C1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>How was that even alive?! I nearly died.</t>
+          <t>That thing was alive. And I nearly wasn't.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>저게 어떻게 살아 있지?! 죽을 뻔했어.</t>
+          <t>저 녀석, 살아 있었어. 난 하마터면 죽을 뻔했고.</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>God, I just need to get out of here.</t>
+          <t>Okay. Okay. I just need to get out of here.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>맙소사... 어서 여기서 나가야 해.</t>
+          <t>좋아. 좋아. 어서 여기서 나가야 해.</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thank the Almighty...</t>
+          <t>Air. Actual air...</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>신이시여, 감사합니다...</t>
+          <t>공기다. 진짜 공기...</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>I need to find out where I am.</t>
+          <t>First, I need to know where I am.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>여기가 어딘지 알아내야 해.</t>
+          <t>먼저 여기가 어딘지 알아야 해.</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Isn't this the raid party?</t>
+          <t>Is that... the raid party?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>... What on earth...</t>
+          <t>...What happened out here?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>...대체 이게 무슨...</t>
+          <t>...여기서 무슨 일이 있었던 거지?</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>I wasn't so lucky after all.</t>
+          <t>So much for lucky.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>결국 나는 운이 좋았던 게 아니었어.</t>
+          <t>운이 좋았다니, 웃기네.</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>We're glad you made it all the way to the end.</t>
+          <t>You made it to the end. We're glad.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>끝까지 함께해 주셔서 정말 기쁩니다.</t>
+          <t>끝까지 와 주셔서 기쁩니다.</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>We're looking to use what we learned from this game for our next title.</t>
+          <t>What we learned here goes into our next game.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>우리는 이 게임에서 배운 점들을 다음 작품에 담아낼 계획입니다.</t>
+          <t>이번에 배운 것은 다음 작품에 담겠습니다.</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Please support our next development :)</t>
+          <t>Please support our next game.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>다음 작품도 응원해 주세요 :)</t>
+          <t>다음 작품도 응원해 주세요.</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>This is not a world of fantasy, magic, and dragons.</t>
+          <t>This is not a world of magic and dragons.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>이곳은 환상과 마법, 용의 세계가 아니다.</t>
+          <t>이곳은 마법과 용의 세계가 아니다.</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>It was worth it...</t>
+          <t>It seemed worth it...</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>그만한 가치는 있었다...</t>
+          <t>그만한 가치가 있어 보였다...</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>This is a world of gritty medieval kingdoms and warring countries.</t>
+          <t>This is a world of mud, borders and kings.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>이곳은 거칠고 투박한 중세 왕국과 전쟁 중인 나라들의 세계다.</t>
+          <t>이곳은 진흙과 국경, 그리고 왕들의 세계다.</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>There were rumors of conscription for the war between two kingdoms.</t>
+          <t>Word came that the crown was drafting men for the war.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>두 왕국의 전쟁을 위해 징집이 있을 거라는 소문이 돌았다.</t>
+          <t>전쟁에 나갈 사람들을 징집한다는 소문이 돌았다.</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The reward was enough to set you up for a year...</t>
+          <t>The pay would feed you for a year...</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>보수는 1년을 먹고살기에 충분했다...</t>
+          <t>보수면 1년은 먹고살 수 있었다...</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The plan was to ambush the enemy using a shortcut.</t>
+          <t>The plan was to ambush the enemy by a shortcut.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Good thing you grew up here and knew the forest.</t>
+          <t>You grew up in these woods. You knew every path.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>이곳에서 자라 숲을 잘 아는 게 다행이었다.</t>
+          <t>당신은 이 숲에서 자랐다. 길이란 길은 다 알았다.</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>You knew it was a mistake. You could feel it.</t>
+          <t>Your stomach knew it was a mistake.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>잘못된 일이라는 걸 알았다. 느낄 수 있었다.</t>
+          <t>배 속이 먼저 알았다. 이건 잘못이라고.</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>You hear cracking...</t>
+          <t>Stone cracks somewhere overhead...</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>갈라지는 소리가 들린다...</t>
+          <t>머리 위 어딘가에서 돌이 갈라진다...</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Small tremors...</t>
+          <t>Dust sifts onto your shoulders...</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>작은 떨림...</t>
+          <t>어깨 위로 먼지가 내려앉는다...</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>You'd never heard of such a tunnel in all your life.</t>
+          <t>You had never heard of a tunnel there. Not once.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>평생 그런 터널은 들어 본 적이 없었다.</t>
+          <t>그곳에 터널이 있다는 말은 들어 본 적이 없었다. 한 번도.</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>You couldn't help thinking it was a joke...</t>
+          <t>You took it for a joke...</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>농담이라고 생각할 수밖에 없었다...</t>
+          <t>농담인 줄 알았다...</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>There really was a tunnel. You could hardly believe it.</t>
+          <t>The tunnel was real. None of your maps had room for it.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>터널은 정말로 있었다. 믿기 어려웠다.</t>
+          <t>터널은 진짜였다. 당신의 어떤 지도에도 들어갈 자리가 없었다.</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The group ventured deep into the tunnel, heading toward the enemy castle...</t>
+          <t>The raid party went in, toward the enemy castle...</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>일행은 적의 성을 향해 터널 깊숙이 들어갔다...</t>
+          <t>토벌대는 적의 성을 향해 터널 안으로 들어갔다...</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>You were just the navigator for this raid party.</t>
+          <t>You were only the navigator.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>당신은 이 토벌대의 길잡이일 뿐이었다.</t>
+          <t>당신은 길잡이일 뿐이었다.</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>And this place never existed before...</t>
+          <t>The day before, there was only hillside.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>그리고 이곳은 전에는 없던 곳이었다...</t>
+          <t>전날까지만 해도 그곳엔 산비탈뿐이었다.</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Like it was waiting here.</t>
+          <t>Like it was waiting for a hand like mine.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>마치 여기서 기다리고 있었던 것처럼.</t>
+          <t>나 같은 손을 기다리고 있었던 것처럼.</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>This chest shouldn't know me.</t>
+          <t>How does a chest know my size?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>이 상자가 나를 알 리 없는데.</t>
+          <t>상자가 내 몸 치수를 어떻게 알지?</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Somehow... my hands already know.</t>
+          <t>My hands already know it.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>어쩐지... 손이 이미 알고 있어.</t>
+          <t>손이 이미 알고 있어.</t>
         </is>
       </c>
     </row>
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>...The page is filled with symbols.</t>
+          <t>...Just symbols, page after page.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>...페이지가 온통 기호투성이야.</t>
+          <t>...페이지마다 기호뿐이야.</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>And I understand. It shows me where to place my hands.</t>
+          <t>Then I understand. It shows me where to put my hands.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>그러자 이해가 된다. 손을 어디에 둬야 하는지 알려 준다.</t>
+          <t>그러자 이해가 돼. 손을 어디에 둬야 하는지 알려 줘.</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>It's broken.</t>
+          <t>Splinters and a rusted hoop.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>이미 부서졌다.</t>
+          <t>나뭇조각과 녹슨 쇠테.</t>
         </is>
       </c>
     </row>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>A pile of old bones.</t>
+          <t>A pile of bones. Old, and picked clean.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>오래된 뼈 무더기.</t>
+          <t>오래된 뼈 무더기. 살점 하나 남지 않았다.</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>How can such creatures exist?</t>
+          <t>I grew up in these hills. None of that lived here.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>이런 생물이 어떻게 존재하지?</t>
+          <t>난 이 산골에서 자랐어. 저런 건 없었다고.</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Some sort of mutated animals...</t>
+          <t>Sick animals, maybe. Something in the water...</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>돌연변이 짐승 같은 건가...</t>
+          <t>병든 짐승일지도. 물 때문인가...</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>You extinguish the flame.</t>
+          <t>You put out the flame. The dark leans in.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>불을 껐다.</t>
+          <t>불을 껐다. 어둠이 가까이 다가온다.</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>The flame is out.</t>
+          <t>Only cold ash is left.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>불이 꺼져 있다.</t>
+          <t>식은 재만 남아 있다.</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Just what I need to get out of this place.</t>
+          <t>Something in there might get me out of here.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>여기서 나가려면 꼭 필요한 것이다.</t>
+          <t>저 안에 여기서 나갈 방법이 있을지도 몰라.</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Wha... What just happened?</t>
+          <t>Ugh... What just happened?</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>뭐... 방금 무슨 일이 일어난 거야?</t>
+          <t>으윽... 방금 무슨 일이야?</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>I knew it. There's something wrong about this place.</t>
+          <t>I knew it. This tunnel was never right.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>역시 그랬어. 이곳은 뭔가 이상해.</t>
+          <t>역시. 이 터널은 처음부터 이상했어.</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>I need to get back.</t>
+          <t>I have to get back up.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>돌아가야 해.</t>
+          <t>위로 돌아가야 해.</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>You extinguish the torch.</t>
+          <t>You put out the torch. The corner goes black.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>횃불을 껐다.</t>
+          <t>횃불을 껐다. 한쪽 구석이 까맣게 잠긴다.</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3253,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>A sturdy tree.</t>
+          <t>A tree, growing where none should.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>튼튼한 나무.</t>
+          <t>있을 리 없는 곳에 나무가 자라고 있다.</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>A cut tree stump.</t>
+          <t>A stump, cut clean with a saw.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>베어 낸 나무 그루터기.</t>
+          <t>톱으로 깨끗이 베어 낸 그루터기.</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>You brush away dust from a weathered grave.</t>
+          <t>You brush the dust from the stone. No name under it.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>비바람에 깎인 무덤의 먼지를 털어 낸다.</t>
+          <t>돌의 먼지를 털어 낸다. 그 밑에도 이름은 없다.</t>
         </is>
       </c>
     </row>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>The earth around this grave feels recently disturbed.</t>
+          <t>The earth is loose, as if turned this morning.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>이 무덤 주위의 흙은 최근에 파헤쳐진 듯하다.</t>
+          <t>흙이 푹신하다. 오늘 아침에 파헤친 것처럼.</t>
         </is>
       </c>
     </row>
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>This grave has been here for a long, long time.</t>
+          <t>Older than the tunnel, by the look of it.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>이 무덤은 아주 오래전부터 여기 있었다.</t>
+          <t>생김새로 보아 터널보다 오래된 무덤이다.</t>
         </is>
       </c>
     </row>
@@ -11243,12 +11243,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>So this is how it ends.</t>
+          <t>Is this it? It is so quiet.</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>결국 이렇게 끝나는구나.</t>
+          <t>이게 끝인가? 너무 조용하다.</t>
         </is>
       </c>
     </row>
@@ -11260,12 +11260,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>The floor gives way beneath you.</t>
+          <t>Your own breath is the last thing you hear.</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>발밑의 바닥이 꺼진다.</t>
+          <t>마지막으로 들리는 건 자기 숨소리다.</t>
         </is>
       </c>
     </row>
@@ -11277,12 +11277,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>You were sure that was the end.</t>
+          <t>You were sure that was it. You were wrong.</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>분명 이게 끝이라고 생각했다.</t>
+          <t>이게 끝이라고 확신했다. 틀렸다.</t>
         </is>
       </c>
     </row>
@@ -11362,12 +11362,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dying is starting to feel like routine.</t>
+          <t>You know the ceiling before you open your eyes.</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>죽는 일이 일상처럼 느껴지기 시작한다.</t>
+          <t>눈을 뜨기도 전에 천장이 어떤지 안다.</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>{killer}. You don't even flinch anymore.</t>
+          <t>{killer}. Your hands don't even shake.</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>{killer}. 이제 놀라지도 않는다.</t>
+          <t>{killer}. 이제 손도 떨리지 않는다.</t>
         </is>
       </c>
     </row>
@@ -11736,12 +11736,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>You wake where you first fell. Alive.</t>
+          <t>Cold stone under your cheek. You are where you fell. Alive, at least.</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>처음 떨어진 곳에서 눈을 뜬다. 살아 있다.</t>
+          <t>뺨에 차가운 돌이 닿는다. 떨어진 그 자리다. 적어도 살아 있다.</t>
         </is>
       </c>
     </row>
@@ -11753,12 +11753,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>The same stone. The same cold. You wake again.</t>
+          <t>The same stone, the same cold. You almost expected it.</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>같은 돌바닥. 같은 냉기. 다시 눈을 뜬다.</t>
+          <t>같은 돌바닥, 같은 냉기. 어쩐지 예상했던 일이다.</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>You wake at the entrance. It almost feels like home.</t>
+          <t>The stone is almost warm now. It feels a little like home.</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>입구에서 눈을 뜬다. 어쩐지 집처럼 느껴진다.</t>
+          <t>돌바닥이 이제 거의 따뜻하다. 어쩐지 집 같다.</t>
         </is>
       </c>
     </row>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>You made these. You don't remember making them.</t>
+          <t>Your thumb fits the groove exactly.</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>당신이 새긴 것이다. 새긴 기억은 없다.</t>
+          <t>당신의 엄지가 홈에 꼭 맞는다.</t>
         </is>
       </c>
     </row>
@@ -17805,12 +17805,12 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>Wait, there was a chest back there. I think I should open it...</t>
+          <t>Wait. There was a chest back there.</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>잠깐, 저 뒤에 상자가 있었어. 열어 봐야겠어...</t>
+          <t>잠깐. 저 뒤에 상자가 있었어.</t>
         </is>
       </c>
     </row>
@@ -17822,12 +17822,12 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>...there might be something I can use to protect myself.</t>
+          <t>...Something in it might keep me alive.</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>...나를 지킬 만한 뭔가가 들어 있을지도 몰라.</t>
+          <t>...안에 살아남는 데 쓸 만한 게 있을지도 몰라.</t>
         </is>
       </c>
     </row>
@@ -19403,12 +19403,12 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Ask again when the tunnel has had you a few more times.</t>
+          <t>Ask again when the tunnel has had you a bit longer.</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>터널이 널 몇 번 더 삼키면 다시 물어봐.</t>
+          <t>터널이 널 좀 더 삼키면 다시 물어봐.</t>
         </is>
       </c>
     </row>
@@ -19987,6 +19987,941 @@
       <c r="C1151" t="inlineStr">
         <is>
           <t>먼저 한참 누워 있는다. 이제는 늘 그렇다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.0</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.1</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Oh, what the hell is that?</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>아니, 저게 대체 뭐야?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.2</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Half cow, half man?</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>반은 소, 반은 사람?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.3</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>That breathing. Those horns...</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>저 숨소리. 저 뿔...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.4</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>And he's blocking the only way forward.</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>하필 하나뿐인 길을 막고 서 있어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.5</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_mini_boss.6</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Fuck.</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>젠장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_final_boss.0</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_final_boss.1</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Another demon.</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>또 악마인가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_final_boss.2</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>This one is different.</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>이번 놈은 달라.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_final_boss.3</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>As if it's looking for something...</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>무언가를 찾는 것 같아...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_final_boss.4</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>dialogue.first_encounter_final_boss.5</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>...someone.</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>...누군가를.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.0</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>*Pant*... Whew.</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>*헉*... 휴.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.1</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>A wolf now? Seriously?</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>이번엔 늑대라고? 진짜로?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.2</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Where do these things come from?</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>이것들은 다 어디서 나오는 거야?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.3</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.4</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Standing here won't answer that.</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>여기 서 있어도 답은 안 나와.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.5</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Keep moving.</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>계속 가자.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_stranger_encounter_reaction.0</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Get your hands off me...</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>손 치워...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_stranger_encounter_reaction.1</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>He smiled the whole time.</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>그 녀석, 내내 웃고 있었어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_stranger_encounter_reaction.2</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Are they all demons down here?</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>여기 있는 건 전부 악마야?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_stranger_encounter_reaction.3</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>What else would they be.</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>달리 뭐겠어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_stranger_encounter_reaction.4</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_stranger_encounter_reaction.5</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>I have to keep moving.</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>계속 움직여야 해.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_level_up_reaction.0</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_level_up_reaction.1</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>The walls tilt. Easy... easy.</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>벽이 기운다. 진정해... 진정해.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_level_up_reaction.2</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>I think I'm going to be sick...</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>토할 것 같아...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_level_up_reaction.3</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Why does it feel like I've been training for years?</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>왜 몇 년 동안 훈련한 것처럼 몸이 쑤시지?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_level_up_reaction.4</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_level_up_reaction.5</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>...and different.</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>...그리고 달라졌어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_equippable_item_reaction.0</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>This might come in handy.</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>쓸모가 있겠는걸.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_equippable_item_reaction.1</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_equippable_item_reaction.2</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Chests every few steps.</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>몇 걸음마다 상자가 있어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_equippable_item_reaction.3</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Gear that fits like it was made for me.</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>내 몸에 맞춘 듯한 장비들.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_equippable_item_reaction.4</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Somebody wants me armed.</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>누군가 내가 무장하길 바라는 거야.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>dialogue.sys_first_equippable_item_reaction.5</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>But why arm us, if they wanted us dead?</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>우리를 죽일 셈이면 왜 무기를 쥐여 주지?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.0</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>*Huff*... *Wheeze*... Fuck.</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>*헉*... *쌕*... 젠장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.1</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.2</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>I did it. I actually did it.</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>해냈어. 정말 해냈어.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.3</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.4</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Still...</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>그런데...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.5</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Nothing here makes sense.</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>여긴 아무것도 말이 안 돼.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.6</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Am I the only one seeing this?</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>이걸 보는 게 나뿐인가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.7</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Who cares. The exit is right there.</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>아무렴 어때. 출구가 바로 저기야.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>dialogue.sys_final_boss_defeated_reaction.8</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Time to find the others, and a way home.</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>동료들을 찾아서 집으로 가는 길을 찾자.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.0</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.1</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>(Colors flood in, far too bright.)</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>(색이 쏟아져 들어온다. 너무 밝다.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.2</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>(Black threads curl through your sight, then vanish.)</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>(검은 실 같은 것이 시야를 휘감았다가 사라진다.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.3</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>(The tunnel snaps back around you.)</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>(터널이 다시 당신을 에워싼다.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.4</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Huh?</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>응?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.5</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.6</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>My head...</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>머리가...</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.7</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>It feels like it's about to split.</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>쪼개질 것 같아.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>dialogue.sys_floor9_5_exit_reaction.8</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>(You clutch your head while walking toward the exit.)</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>(머리를 부여잡고 출구를 향해 걷는다.)</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>First hit: -1 [t]DEF[/t] for 2 turns</t>
+          <t>Your first hit cuts the enemy's [t]DEF[/t] by 1 for 2 turns</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>첫 타격: 2턴 동안 [t]DEF[/t] -1</t>
+          <t>첫 타격이 적의 [t]DEF[/t]를 2턴 동안 1 낮춘다</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>First hit -3 damage (once per battle)</t>
+          <t>The first hit you take deals 3 less damage (once per battle)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>After a hit: next hit -40% (2-turn cooldown)</t>
+          <t>After you are hit, the next hit deals 40% less (2-turn cooldown)</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>-30% damage from big hits</t>
+          <t>Big hits deal 30% less damage</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>+1 [t]MP[/t] every 2 turns, +1 physical damage taken</t>
+          <t>+1 [t]MP[/t] every 2 turns, but physical hits deal 1 more damage</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>+10% skill damage, +1 status turn</t>
+          <t>Skills deal +10% damage; your statuses last 1 turn longer</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Reflects the first status (costs 1 [t]MP[/t])</t>
+          <t>Reflects the first status cast on you (once per battle, costs 1 [t]MP[/t])</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>첫 상태 이상을 반사 ([t]MP[/t] 1 소모)</t>
+          <t>첫 상태 이상을 반사 (전투마다 1회, [t]MP[/t] 1 소모)</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>+35% damage to foes below 35% [t]HP[/t]</t>
+          <t>+35% damage to enemies under 35% [t]HP[/t]</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[t]Good[/t] or [a]Perfect[/a]: may [t]Stun[/t] (3-turn cooldown)</t>
+          <t>A [t]Good[/t] or [a]Perfect[/a] press may [t]Stun[/t] the enemy (3-turn cooldown)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>[t]좋음[/t] 또는 [a]완벽[/a]: [t]기절[/t]시킬 수 있음 (재사용 3턴)</t>
+          <t>[t]좋음[/t] 또는 [a]완벽[/a] 판정 시 적을 [t]기절[/t]시킬 수 있음 (재사용 3턴)</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>+30% damage to foes with a status</t>
+          <t>+30% damage to enemies with a status</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>+15% skill damage, +1 status turn</t>
+          <t>Skills deal +15% damage; your statuses last 1 turn longer</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>+25% skill damage, [a]Perfect[/a] +1 [t]MP[/t]</t>
+          <t>Skills deal +25% damage; a [a]Perfect[/a] press gives +1 [t]MP[/t]</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Turns the screen shake on hits on or off.</t>
+          <t>Screen shake when a hit lands: on or off.</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>How many times the picture is enlarged in a window. Only used when windowed. You are asked to keep a change.</t>
+          <t>How many times the picture is enlarged. Windowed mode only. You are asked to keep a change.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Pushed back on the turn bar. Then [t]Steadfast[/t]: cannot be stunned for 2 turns.</t>
+          <t>Pushed back on the turn strip. Then [t]Steadfast[/t]: cannot be stunned for 2 turns.</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Blocks the next incoming hit.</t>
+          <t>Blocks the next hit.</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Dodges the next incoming attack.</t>
+          <t>Dodges the next attack.</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Until hit: take {take}% less, deal {deal}% more damage.</t>
+          <t>Until you are hit: take {take}% less damage, deal {deal}% more.</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Next incoming hit deals {pct}% less damage.</t>
+          <t>The next hit you take deals {pct}% less damage.</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Lose defense.{mods}</t>
+          <t>Lowers [t]DEF[/t].{mods}</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>방어력이 떨어집니다.{mods}</t>
+          <t>[t]DEF[/t]가 떨어집니다.{mods}</t>
         </is>
       </c>
     </row>
@@ -10291,12 +10291,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>A scout of the dark tunnels. Quick and sharp: poison and double shots.</t>
+          <t>A scout of the dark. Quick, with [t]Poison[/t] and double shots.</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>어두운 터널의 척후병. 빠르고 날카롭습니다. 독과 연속 사격.</t>
+          <t>어둠 속의 척후병. 빠르고, [t]독[/t]과 연속 사격을 쓴다.</t>
         </is>
       </c>
     </row>
@@ -10308,12 +10308,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Guard of the fallen keep. Hits hard, takes hits harder. Stands firm.</t>
+          <t>Guard of a keep that fell. Hits hard, slow to be hurt.</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>무너진 보루의 수호병. 강하게 치고 더 단단히 버팁니다.</t>
+          <t>무너진 보루의 수호병. 세게 치고 좀처럼 다치지 않는다.</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>A scholar who heard the dark. Frail, but great magic and mana.</t>
+          <t>A scholar the dark read back. Frail; spells hit hard.</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>어둠의 소리를 들은 학자. 약하지만 마법과 마나가 대단합니다.</t>
+          <t>어둠이 읽어 낸 학자. 약하지만 마법이 강하다.</t>
         </is>
       </c>
     </row>
@@ -10342,12 +10342,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>No name, no past, no skills. Only blade, passives and items.</t>
+          <t>No name, no past, no skills. A blade and your pockets.</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>이름도 과거도 스킬도 없습니다. 칼과 패시브와 아이템뿐.</t>
+          <t>이름도 과거도 스킬도 없다. 칼 한 자루와 주머니뿐이다.</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>[t]Poison[/t] you apply adds {n} extra stack.</t>
+          <t>[t]Poison[/t] you inflict adds {n} extra stack.</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Your enchantments are snuffed out!</t>
+          <t>Your buffs are snuffed out!</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>당신의 강화 효과가 꺼졌습니다!</t>
+          <t>당신의 버프가 꺼졌습니다!</t>
         </is>
       </c>
     </row>
@@ -13011,12 +13011,12 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Throw it for {power} power of damage; it burns for {turns} turns. Costs your turn.</t>
+          <t>Hits for {power} power and inflicts [t]Burn[/t] for {turns} turns. Costs your turn.</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>위력 {power}의 피해를 주고 {turns}턴 동안 불탑니다. 턴을 소모합니다.</t>
+          <t>위력 {power}의 피해를 주고 {turns}턴 동안 [t]화상[/t]을 입힙니다. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Throw it to poison the enemy with {n} stacks. Costs your turn.</t>
+          <t>Inflicts {n} stacks of [t]Poison[/t]. Costs your turn.</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Throw it for {power} power of damage and a stun that pushes the enemy back. Costs your turn.</t>
+          <t>Hits for {power} power and inflicts [t]Stun[/t], pushing the enemy back. Costs your turn.</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Throw it to dodge the next attack ({turns} turns); a [a]Perfect[/a] throw lets you slip away. Costs your turn.</t>
+          <t>Dodge the next attack ({turns} turns). A [a]Perfect[/a] throw lets you slip away. Costs your turn.</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Wear it for {bonus}.</t>
+          <t>Gives {bonus} while equipped.</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Wear it: {line}.</t>
+          <t>While equipped: {line}.</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>A ring or charm worn in the accessory slot.</t>
+          <t>A ring or charm for the accessory slot.</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>The strip at the top shows who acts next. Faster fighters act more often, and some skills push an enemy back a turn.</t>
+          <t>The top strip shows who acts next. Faster fighters act more often, and some skills push an enemy back a turn.</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>위쪽 띠는 다음에 행동할 상대를 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 어떤 스킬은 적을 한 턴 뒤로 밀어냅니다.</t>
+          <t>위쪽 띠가 다음에 행동할 차례를 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 일부 스킬은 적을 한 턴 뒤로 밉니다.</t>
         </is>
       </c>
     </row>
@@ -14456,12 +14456,12 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>The sliding bar</t>
+          <t>Timing bar</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>움직이는 막대</t>
+          <t>타이밍 막대</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14473,12 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>A cursor slides along the bar. Press [k:confirm] when it is over the bright zone. The closer to the middle, the harder you hit.</t>
+          <t>Press [k:confirm] when the cursor is on the bright zone. The closer to the middle, the harder the hit.</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>커서가 막대를 따라 움직입니다. 밝은 구간 위에 왔을 때 [k:confirm]을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
+          <t>커서가 밝은 구간에 있을 때 [k:confirm]을(를) 누르세요. 가운데에 가까울수록 더 세게 때립니다.</t>
         </is>
       </c>
     </row>
@@ -14507,12 +14507,12 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Skills show a row of arrows. Press [k:up][k:down][k:left][k:right] in that order before the time bar runs out. A wrong press costs time.</t>
+          <t>Match the row of arrows with [k:up][k:down][k:left][k:right], in order, before the time bar empties. A wrong press costs time.</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>스킬을 쓰면 화살표 줄이 나옵니다. 시간 막대가 다 줄기 전에 [k:up][k:down][k:left][k:right]으로 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
+          <t>시간 막대가 비기 전에 [k:up][k:down][k:left][k:right]으로 화살표 줄을 순서대로 누르세요. 틀리면 시간이 깎입니다.</t>
         </is>
       </c>
     </row>
@@ -14558,12 +14558,12 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Stagger and BREAK</t>
+          <t>Stagger</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>경직과 브레이크</t>
+          <t>경직</t>
         </is>
       </c>
     </row>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>[t]Good[/t] hits fill the enemy's [t]stagger[/t] meter. When it is full the enemy goes into [a]BREAK[/a]: it loses a turn and takes +50% damage.</t>
+          <t>[t]Good[/t] hits fill the enemy's [t]stagger[/t] meter. When it is full: [a]BREAK[/a]. The enemy loses a turn and takes +50% damage.</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>좋은 공격은 적의 [t]경직[/t] 게이지를 채웁니다. 가득 차면 적이 [a]브레이크[/a] 상태가 되어 한 턴을 잃고 피해를 50% 더 받습니다.</t>
+          <t>[t]좋음[/t] 판정 공격은 적의 [t]경직[/t] 게이지를 채웁니다. 가득 차면 [a]브레이크[/a]. 적은 한 턴을 잃고 피해를 50% 더 받습니다.</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Level-ups and skill chests offer 3 cards: a new skill, an upgrade or a passive. Take one, or skip for a little gold.</t>
+          <t>Level-ups and skill chests offer 3 cards: a skill, an upgrade or a passive. Take one, or skip for a little gold.</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>The merchant sells potions and gear. Gold is kept for the whole run, and the stock changes with every run.</t>
+          <t>The merchant sells potions and gear. Gold lasts the whole run; the stock changes every run.</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Throwable items hurt an enemy straight from the item menu. Each one is used up when thrown, so save them for hard fights.</t>
+          <t>Throw them from the item menu to hurt an enemy. Each is used up, so save them for hard fights.</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Each bed can be used once per run. Rest to restore all your [t]HP[/t] and [t]MP[/t], or use it to upgrade one of your skills.</t>
+          <t>Each bed works once per run. Rest to restore all your [t]HP[/t] and [t]MP[/t], or upgrade one skill.</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Marked enemies are [t]Elites[/t]. They are tougher than normal ones, but their rewards are better.</t>
+          <t>Marked enemies are [t]Elites[/t]: tougher than the rest, with better rewards.</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>[t]Poison[/t], [t]Burn[/t], [t]Bleed[/t] and [t]Stun[/t] last a few turns. The icons under a name show which ones a fighter has.</t>
+          <t>Icons under a name show a fighter's statuses, like [t]Poison[/t] or [t]Burn[/t]. They last a few turns.</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>[t]독[/t], [t]화상[/t], [t]출혈[/t], [t]기절[/t]은 몇 턴 동안 이어집니다. 이름 아래 아이콘이 걸려 있는 상태를 보여 줍니다.</t>
+          <t>이름 아래 아이콘은 [t]독[/t]이나 [t]화상[/t] 같은 상태 이상을 보여 줍니다. 몇 턴 동안 이어집니다.</t>
         </is>
       </c>
     </row>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>퍼펙트 비율</t>
+          <t>완벽 비율</t>
         </is>
       </c>
     </row>
@@ -19199,12 +19199,12 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>A critical hit deals {mult} times the damage. Take Aim and some gear raise the odds.</t>
+          <t>A critical hit deals {mult} times the damage. [t]Take Aim[/t] and some gear raise the odds.</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>치명타는 피해를 {mult}배로 줍니다. 조준과 일부 장비가 확률을 높입니다.</t>
+          <t>치명타는 피해를 {mult}배로 줍니다. [t]조준[/t]과 일부 장비가 확률을 높입니다.</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Press on the bar but off the middle for normal damage.</t>
+          <t>Press on the bar, off the middle, for normal damage.</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
@@ -19284,12 +19284,12 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Good hits fill the stagger meter. When it is full the enemy loses a turn and takes +{pct}% damage.</t>
+          <t>Good hits fill the [t]stagger[/t] meter. When it is full the enemy loses a turn and takes +{pct}% damage.</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>좋은 공격은 경직 게이지를 채웁니다. 가득 차면 적이 한 턴을 잃고 피해를 {pct}% 더 받습니다.</t>
+          <t>좋은 공격은 [t]경직[/t] 게이지를 채웁니다. 가득 차면 적이 한 턴을 잃고 피해를 {pct}% 더 받습니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1153"/>
+  <dimension ref="A1:C1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -20024,6 +20024,23 @@
         </is>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>controls.waiting_pad</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Press the new key for {action}. [k:back] cancels.</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>{action}에 쓸 새 키를 누르세요. [k:back] 버튼으로 취소합니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATTACK</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ITEM</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKILL</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PERFECT</t>
+          <t>Perfect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Select class</t>
+          <t>Choose Class</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Select difficulty</t>
+          <t>Choose Difficulty</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>New game</t>
+          <t>New Game</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Load game</t>
+          <t>Load Game</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Exit game</t>
+          <t>Quit Game</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Item not in inventory.</t>
+          <t>Item not in bag.</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Learn a skill</t>
+          <t>Learn a Skill</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Available points: {points}</t>
+          <t>Available Points: {points}</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Level cap</t>
+          <t>Level Cap</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Bag</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>All classes</t>
+          <t>All Classes</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>{classes} only</t>
+          <t>{classes} Only</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Effect: Multiple statuses</t>
+          <t>Effect: Multiple Statuses</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Effect: Steal one random item</t>
+          <t>Effect: Steal One Random Item</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Teaches: Unknown skill</t>
+          <t>Teaches: Unknown Skill</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Key item</t>
+          <t>Key Item</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Affects combat performance.</t>
+          <t>Affects battle performance.</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>All allies</t>
+          <t>All Allies</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>All enemies</t>
+          <t>All Enemies</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Exit to main menu</t>
+          <t>Quit to Title</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>메인 메뉴로 나가기</t>
+          <t>타이틀로 나가기</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Load game</t>
+          <t>Load Game</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Save game</t>
+          <t>Save Game</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Hold to skip</t>
+          <t>Hold to Skip</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Text speed</t>
+          <t>Text Speed</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Screen shake</t>
+          <t>Screen Shake</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Timing assist</t>
+          <t>Timing Assist</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Chars per sec</t>
+          <t>Chars per Sec</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Window size</t>
+          <t>Window Size</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>차례가 뒤로 밀립니다. 이후 2턴간 [t]버티기[/t] 상태가 되어 [t]기절[/t]하지 않습니다.</t>
+          <t>턴이 뒤로 밀립니다. 이후 2턴간 [t]버티기[/t] 상태가 되어 [t]기절[/t]하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Recover {n} [t]MP[/t] each turn.</t>
+          <t>Restore {n} [t]MP[/t] each turn.</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Abandon run</t>
+          <t>Abandon Run</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>You gave up the run.</t>
+          <t>You abandoned the run.</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>쓰러뜨린 상대: {name}</t>
+          <t>쓰러진 원인: {name}</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Press [k:confirm] to go on</t>
+          <t>Press [k:confirm] to continue</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>[k:up][k:down] Choose   [k:confirm] Take it</t>
+          <t>[k:up][k:down] Choose   [k:confirm] Take</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>[k:up][k:down] 고르기   [k:confirm] 가져가기</t>
+          <t>[k:up][k:down] 선택   [k:confirm] 받기</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Carry one echo into the next fall</t>
+          <t>Carry One Echo into the Next Fall</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Falls so far: {n}</t>
+          <t>Falls So Far: {n}</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Floor reached: {n}</t>
+          <t>Floor Reached: {n}</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>{name}의 차례가 뒤로 밀렸습니다!</t>
+          <t>{name}의 턴이 뒤로 밀렸습니다!</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>차례가 뒤로 밀렸습니다!</t>
+          <t>턴이 뒤로 밀렸습니다!</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Main stat</t>
+          <t>Main Stat</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Poison stacks</t>
+          <t>Poison Stacks</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>After fight</t>
+          <t>After Battle</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Potion find</t>
+          <t>Potion Find</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Perfect zone</t>
+          <t>Perfect Zone</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Each turn</t>
+          <t>Each Turn</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Skill power</t>
+          <t>Skill Power</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Status turns</t>
+          <t>Status Turns</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Class passive</t>
+          <t>Class Passive</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>[k:left][k:right] 고르기   [k:confirm] 받기</t>
+          <t>[k:left][k:right] 선택   [k:confirm] 받기</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Skip: +{gold} gold</t>
+          <t>Skip: +{gold} Gold</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Choose a card</t>
+          <t>Choose a Card</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Keep my skills</t>
+          <t>Keep My Skills</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Gives up: {line}</t>
+          <t>Loses: {line}</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Learn {skill}: replace which?</t>
+          <t>Learn {skill}: Replace Which?</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Level {lvl}: place 1 point</t>
+          <t>Level {lvl}: Place 1 Point</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Restore {n} [t]HP[/t] after each fight you win.</t>
+          <t>Restore {n} [t]HP[/t] after each battle you win.</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Enemies start each fight with {n} [t]stagger[/t].</t>
+          <t>Enemies start each battle with {n} [t]stagger[/t].</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Regain {n} [t]MP[/t] after each fight you win.</t>
+          <t>Regain {n} [t]MP[/t] after each battle you win.</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>{n}% chance to find a potion after each fight you win.</t>
+          <t>{n}% chance to find a potion after each battle you win.</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Floor reached</t>
+          <t>Floor Reached</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Foes beaten</t>
+          <t>Enemies Beaten</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>쓰러뜨린 적</t>
+          <t>처치한 적</t>
         </is>
       </c>
     </row>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Falls so far</t>
+          <t>Falls So Far</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>ELITE</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>착용 효과: {bonus}.</t>
+          <t>장착 효과: {bonus}.</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>착용 효과: {line}.</t>
+          <t>장착 효과: {line}.</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13135,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>장신구 칸에 착용하는 반지나 부적입니다.</t>
+          <t>장신구 칸에 장착하는 반지나 부적입니다.</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Push back</t>
+          <t>Push Back</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Evasion</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Carry up to</t>
+          <t>Carry Limit</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Damage taken</t>
+          <t>Damage Taken</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Regenerating: heals {pct}% of its HP each turn.</t>
+          <t>Regenerating: restores {pct}% of its HP each turn.</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Sold out</t>
+          <t>Sold Out</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>You have</t>
+          <t>You Have</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>In Stock</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Sells for</t>
+          <t>Sells For</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>착용 중</t>
+          <t>장착 중</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>Nothing to sell</t>
+          <t>Nothing to Sell</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Gold {n}</t>
+          <t>Gold: {n}</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>골드 {n}</t>
+          <t>골드: {n}</t>
         </is>
       </c>
     </row>
@@ -14065,7 +14065,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Take it off first.</t>
+          <t>Unequip it first.</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Turn order</t>
+          <t>Turn Order</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>위쪽 띠가 다음에 행동할 차례를 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 일부 스킬은 적을 한 턴 뒤로 밉니다.</t>
+          <t>위쪽 띠가 다음에 행동할 턴을 보여 줍니다. 빠른 쪽이 더 자주 행동하고, 일부 스킬은 적을 한 턴 뒤로 밉니다.</t>
         </is>
       </c>
     </row>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Timing bar</t>
+          <t>Timing Bar</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Arrow skills</t>
+          <t>Arrow Skills</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>The shop</t>
+          <t>The Shop</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Throw them from the item menu to hurt an enemy. Each is used up, so save them for hard fights.</t>
+          <t>Throw them from the item menu to hurt an enemy. Each is used up, so save them for hard battles.</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>투척 도구는 아이템 메뉴에서 바로 적에게 피해를 줍니다. 던지면 사라지니 어려운 싸움을 위해 아껴 두세요.</t>
+          <t>투척 도구는 아이템 메뉴에서 바로 적에게 피해를 줍니다. 던지면 사라지니 어려운 전투를 위해 아껴 두세요.</t>
         </is>
       </c>
     </row>
@@ -14886,7 +14886,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>쉬기</t>
+          <t>휴식</t>
         </is>
       </c>
     </row>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Upgrade a skill</t>
+          <t>Upgrade a Skill</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>떠나기</t>
+          <t>나가기</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Upgrade which skill?</t>
+          <t>Upgrade Which Skill?</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Previous tab</t>
+          <t>Previous Tab</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Next tab</t>
+          <t>Next Tab</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Reset to defaults</t>
+          <t>Reset to Defaults</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>GUARD</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>다음 차례까지 받는 피해가 50% 늘어납니다.</t>
+          <t>다음 턴까지 받는 피해가 50% 늘어납니다.</t>
         </is>
       </c>
     </row>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>이 상대에게서는 도망칠 수 없습니다.</t>
+          <t>이 적에게서는 도망칠 수 없습니다.</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>Quit to title</t>
+          <t>Quit to Title</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>Run history</t>
+          <t>Run History</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Notes found {n}/{max}</t>
+          <t>Notes Found {n}/{max}</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>가방</t>
+          <t>소지품</t>
         </is>
       </c>
     </row>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>Nothing equipped</t>
+          <t>Nothing Equipped</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>착용 없음</t>
+          <t>장착 없음</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>이 칸에는 아무것도 착용하지 않았습니다.</t>
+          <t>이 칸에는 아무것도 장착하지 않았습니다.</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>No accessory</t>
+          <t>No Accessory</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>No armor</t>
+          <t>No Armor</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>No weapon</t>
+          <t>No Weapon</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>착용 중</t>
+          <t>장착 중</t>
         </is>
       </c>
     </row>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>[k:confirm] 착용</t>
+          <t>[k:confirm] 장착</t>
         </is>
       </c>
     </row>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>[k:confirm] Select</t>
+          <t>[k:confirm] Choose</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>[k:confirm] Take off</t>
+          <t>[k:confirm] Unequip</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>You gave this run up on floor {n}.</t>
+          <t>You abandoned this run on floor {n}.</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>Nothing in your bag</t>
+          <t>Nothing in Your Bag</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Best floor</t>
+          <t>Best Floor</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Foes beaten</t>
+          <t>Enemies Beaten</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>No skills yet</t>
+          <t>No Skills Yet</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -17465,12 +17465,12 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>능력치</t>
+          <t>상태</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Gave up</t>
+          <t>Abandoned</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Press any key</t>
+          <t>Press Any Key</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>Press any button</t>
+          <t>Press Any Button</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>Can't continue</t>
+          <t>Can't Continue</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Keep one skill you remember</t>
+          <t>Keep One Skill You Remember</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Perfect rate</t>
+          <t>Perfect Rate</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Crits landed</t>
+          <t>Crits Landed</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>Damage dealt</t>
+          <t>Damage Dealt</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
@@ -18043,7 +18043,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Damage taken</t>
+          <t>Damage Taken</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>Fights won</t>
+          <t>Battles Won</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>Run time</t>
+          <t>Run Time</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>Raises your max [t]HP[/t] by {n} and heals {n} [t]HP[/t].</t>
+          <t>Raises your max [t]HP[/t] by {n} and restores {n} [t]HP[/t].</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Goes back to the title. Continue puts you back just before this fight.</t>
+          <t>Goes back to the title. Continue puts you back just before this battle.</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>Keep this setting?</t>
+          <t>Keep This Setting?</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Choose a seed</t>
+          <t>Choose a Seed</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Random seed</t>
+          <t>Random Seed</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>Enter seed</t>
+          <t>Enter Seed</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Enter seed</t>
+          <t>Enter Seed</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>최대 9자리. 같은 시드, 같은 모험.</t>
+          <t>최대 9자리. 같은 시드, 같은 도전.</t>
         </is>
       </c>
     </row>
@@ -18439,7 +18439,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>[k:back] 뒤로   [k:tab_prev] 지우기</t>
+          <t>[k:back] 뒤로   [k:tab_prev] 삭제</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Quit to title? Continue puts you back just before this fight.</t>
+          <t>Quit to title? Continue puts you back just before this battle.</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Stats &amp; terms</t>
+          <t>Stats &amp; Terms</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
@@ -19998,7 +19998,7 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>In a fight, use ITEM in the battle menu.</t>
+          <t>In a battle, use Item in the battle menu.</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>You can't change gear in a fight.</t>
+          <t>You can't change gear during a battle.</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -9934,7 +9934,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Strike for {power} power.</t>
+          <t>Hit for {power} power.</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>{chance}% to inflict [t]{status}[/t].</t>
+          <t>{chance}% [t]{status}[/t].</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Strike {hits} times for {power} power each.</t>
+          <t>Hit {hits} times for {power} power each.</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>{n}% chance to find a potion after each battle you win.</t>
+          <t>After each win, {n}% to find a potion.</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Hits for {power} power and inflicts [t]Burn[/t] for {turns} turns. Costs your turn.</t>
+          <t>Hits for {power} power. Inflicts [t]Burn[/t] for {turns} turns. Costs your turn.</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Hits for {power} power and inflicts [t]Stun[/t], pushing the enemy back. Costs your turn.</t>
+          <t>Hits for {power} power. [t]Stun[/t] and push back. Costs your turn.</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Dodge the next attack ({turns} turns). A [a]Perfect[/a] throw lets you slip away. Costs your turn.</t>
+          <t>Dodge for {turns} turns. [a]Perfect[/a]: escape. Costs your turn.</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>다음 공격을 피합니다({turns}턴). [a]완벽[/a]하게 던지면 도망칩니다. 턴을 소모합니다.</t>
+          <t>{turns}턴 회피. [a]완벽[/a]하면 도망. 턴을 소모합니다.</t>
         </is>
       </c>
     </row>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>만난 횟수</t>
+          <t>만남</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>목격</t>
+          <t>봄</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1209"/>
+  <dimension ref="A1:C1210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -20976,6 +20976,23 @@
         </is>
       </c>
     </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>combat.msg.overpower_prefix</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>You overpower {enemy}.</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>{enemy}을(를) 가볍게 쓰러뜨렸습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1210"/>
+  <dimension ref="A1:C1212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>GOOD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Perfect</t>
+          <t>PERFECT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>WEAK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20990,6 +20990,40 @@
       <c r="C1210" t="inlineStr">
         <is>
           <t>{enemy}을(를) 가볍게 쓰러뜨렸습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>controls.reset_ask</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Reset every key to its default?</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>모든 키를 기본값으로 되돌릴까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>controls.reset_same</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Keys were already the defaults.</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>키가 이미 기본값입니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1211"/>
+  <dimension ref="A1:C1212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21010,6 +21010,23 @@
         </is>
       </c>
     </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>profile.default_name</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>프로필</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1212"/>
+  <dimension ref="A1:C1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21027,6 +21027,227 @@
         </is>
       </c>
     </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>save.slot.name</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Save {n}</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>저장 {n}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>save.slot.empty</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>비어 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>save.slot.cant</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Cannot load</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>불러올 수 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>save.lbl.saved</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Last Saved</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>마지막 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>save.slot.help_load</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Pick up this run where you left it.</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>중단한 곳에서 이 도전을 이어갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>save.slot.help_over</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>A new game here replaces this run.</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>여기서 새 게임을 시작하면 이 도전은 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>save.slot.help_empty</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>No run is saved in this file.</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>이 파일에는 저장된 도전이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>save.overwrite.title</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Overwrite which save file?</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>어느 저장 파일을 덮어쓸까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>save.overwrite.ask</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Overwrite Save {n}? The run in it will be lost.</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>저장 {n}을(를) 덮어쓸까요? 그 안의 도전은 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>save.delete.ask</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Delete Save {n}? The run in it will be lost.</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>저장 {n}을(를) 삭제할까요? 그 안의 도전은 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>save.hint.load</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>[k:confirm] Load</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>[k:confirm] 불러오기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>save.hint.overwrite</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>[k:confirm] Overwrite</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>[k:confirm] 덮어쓰기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>save.hint.delete</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>[k:tab_prev] Delete</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>[k:tab_prev] 삭제</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1225"/>
+  <dimension ref="A1:C1244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21248,6 +21248,329 @@
         </is>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>profile.btn</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>[k:tab_prev] Profile</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>[k:tab_prev] 프로필</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>profile.title</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Profiles</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>프로필</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>profile.row.new</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>New Profile</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>새 프로필</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>profile.val.active</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>사용 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>profile.lbl.runs</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>도전 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>profile.help.active</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>The profile in use. Its Codex, run history and story are the ones you see.</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>지금 쓰는 프로필입니다. 도감, 도전 기록, 이야기는 이 프로필의 것입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>profile.help.other</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Switch to this profile. Its Codex, run history, story and save files come with it.</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>이 프로필로 바꿉니다. 도감, 도전 기록, 이야기, 저장 파일도 함께 바뀝니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>profile.help.new</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Start a new profile. Its Codex and run history are empty and the story begins again.</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>새 프로필을 만듭니다. 도감과 도전 기록은 비어 있고 이야기는 처음부터 시작합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>profile.hint.switch</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>[k:confirm] Switch</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>[k:confirm] 바꾸기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>profile.hint.create</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>[k:confirm] Create</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>[k:confirm] 만들기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>profile.delete.ask</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Delete profile {name}? Its Codex, history and save files are lost.</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>프로필 {name}을(를) 삭제할까요? 도감, 기록, 저장 파일이 모두 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>profile.name.need</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Enter a name.</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>이름을 입력하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>profile.name.key_space</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>띄어쓰기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>profile.name.key_delete</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>profile.name.key_ok</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>profile.name.hint_pick</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>[k:confirm] Pick</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>[k:confirm] 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>profile.name.hint_cancel</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>[k:back] Cancel</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>[k:back] 취소</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>profile.name.info_kb</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Up to 12 letters. Backspace deletes, Enter finishes.</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>최대 12자. Backspace로 지우고 Enter로 끝냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>profile.name.info_pad</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Up to 12 letters. Pick them on the grid.</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>최대 12자. 칸에서 골라 입력하세요.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1244"/>
+  <dimension ref="A1:C1245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21571,6 +21571,23 @@
         </is>
       </c>
     </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>codex.btn</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>[k:tab_next] Codex</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>[k:tab_next] 도감</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1212"/>
+  <dimension ref="A1:C1214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -15782,12 +15782,12 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Braced for the next hit: it deals {pct}% less damage.</t>
+          <t>Until your next turn every hit you take deals {pct}% less damage.</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>다음 공격에 대비합니다. 피해가 {pct}% 줄어듭니다.</t>
+          <t>내 다음 턴까지 받는 모든 공격의 피해가 {pct}% 줄어듭니다.</t>
         </is>
       </c>
     </row>
@@ -21024,6 +21024,40 @@
       <c r="C1212" t="inlineStr">
         <is>
           <t>프로필</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>combat.msg.guard_mp</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>You brace yourself. +{mp} MP</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>몸을 웅크립니다. MP +{mp}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>combat.pop.guard_mp</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>+{mp} MP</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>MP +{mp}</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1214"/>
+  <dimension ref="A1:C1216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21061,6 +21061,40 @@
         </is>
       </c>
     </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>shop.reason.full</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Bag full for this item</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>이 아이템은 더 들 수 없습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>shop.reason.owned</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Already owned</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>이미 가지고 있습니다</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1216"/>
+  <dimension ref="A1:C1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21095,6 +21095,346 @@
         </is>
       </c>
     </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>runflow.title.t1.1</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>The dark closes over you.</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>어둠이 당신을 덮는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>runflow.title.t1.2</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Is this the end?</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>이게 끝일까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>runflow.title.t2.0</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Not the end.</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>끝이 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>runflow.title.t2.1</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>It begins again.</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>다시 시작된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>runflow.title.t2.2</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Back so soon.</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>벌써 돌아왔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>runflow.title.t3.0</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>You know the way.</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>길을 안다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>runflow.title.t3.1</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>The same fall.</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>같은 추락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>runflow.title.t3.2</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Down, once more.</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>다시, 아래로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>runflow.title.t4.0</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Nothing new.</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>새로울 것 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>runflow.title.t4.1</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Quiet again.</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>다시 고요하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>runflow.title.t4.2</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>No one came.</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>아무도 오지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>runflow.title.t5.0</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Home again.</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>다시 집이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>runflow.title.t5.1</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>As expected.</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>짐작대로다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>runflow.title.t5.2</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>You stay.</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>당신은 남는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>runflow.title.won.0</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>The choir falls silent.</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>성가대가 침묵한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>runflow.title.won.1</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>The tunnel lets go.</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>터널이 당신을 놓아준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>runflow.title.won.2</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>The way is open.</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>길이 열렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>runflow.title.abandoned.0</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>You let go.</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>당신은 손을 놓았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>runflow.title.abandoned.1</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>The tunnel waits.</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>터널은 기다린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>runflow.title.abandoned.2</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>You turned back.</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>당신은 돌아섰다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Received [a]{item}[/a] x{qty}.</t>
+          <t>Received {item} x{qty}.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>[a]{item}[/a] x{qty}을(를) 받았습니다.</t>
+          <t>{item} x{qty}을(를) 받았습니다.</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1245"/>
+  <dimension ref="A1:C1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6500,12 +6500,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Increases spell damage and max [t]MP[/t].</t>
+          <t>Increases spell damage.</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>마법 피해와 최대 [t]MP[/t]를 늘립니다.</t>
+          <t>마법 피해를 늘립니다.</t>
         </is>
       </c>
     </row>
@@ -19029,12 +19029,12 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>What Power, ATK, DEF, MAG, SPD, Crit, the grades, BREAK and every status mean.</t>
+          <t>What Power, ATK, DEF, MAG, SPD, VIG, MND, Crit, the grades, BREAK and every status mean.</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>위력, ATK, DEF, MAG, SPD, 치명타, 등급, 브레이크와 모든 상태 이상의 뜻입니다.</t>
+          <t>위력, ATK, DEF, MAG, SPD, VIG, MND, 치명타, 등급, 브레이크와 모든 상태 이상의 뜻입니다.</t>
         </is>
       </c>
     </row>
@@ -21585,6 +21585,74 @@
       <c r="C1245" t="inlineStr">
         <is>
           <t>[k:tab_next] 도감</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>menu.tooltip.stat.vig.desc</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Raises max [t]HP[/t]. The more you add, the less each point gives.</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>최대 [t]HP[/t]를 늘립니다. 많이 올릴수록 포인트 하나의 효과는 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>menu.tooltip.stat.mnd.desc</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Raises max [t]MP[/t]. The more you add, the less each point gives.</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>최대 [t]MP[/t]를 늘립니다. 많이 올릴수록 포인트 하나의 효과는 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>tab.lbl.max_hp</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Max HP</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>최대 HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>tab.lbl.max_mp</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Max MP</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>최대 MP</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1249"/>
+  <dimension ref="A1:C1250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21656,6 +21656,23 @@
         </is>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>tab.val.level_up</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Level Up</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>레벨 업</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1250"/>
+  <dimension ref="A1:C1249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -18072,2030 +18072,2030 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>levelup.gain</t>
+          <t>tab.system</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>{stat} +{n}</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>{stat} +{n}</t>
+          <t>시스템</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>levelup.growth</t>
+          <t>tab.title.system</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>{name} growth: {gains}</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>{name} 성장: {gains}</t>
+          <t>시스템</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>cards.stat.maxhp</t>
+          <t>tab.system.quit_battle_help</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>Max HP +{n}</t>
+          <t>Goes back to the title. Continue puts you back just before this battle.</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>최대 HP +{n}</t>
+          <t>타이틀로 나갑니다. 이어하기를 하면 이 전투 직전부터 다시 시작합니다.</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>cards.stat.maxmp</t>
+          <t>settings.keep.title</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>Max MP +{n}</t>
+          <t>Keep This Setting?</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>최대 MP +{n}</t>
+          <t>이 설정을 유지할까요?</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>cards.stat.maxhp.desc</t>
+          <t>settings.keep.body</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>Raises your max [t]HP[/t] by {n} and restores {n} [t]HP[/t].</t>
+          <t>It goes back by itself in {n} s.</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>최대 [t]HP[/t]가 {n} 오르고 [t]HP[/t]를 {n} 회복합니다.</t>
+          <t>{n}초 뒤에 자동으로 원래대로 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>cards.stat.maxmp.desc</t>
+          <t>settings.keep.hint</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>Raises your max [t]MP[/t] by {n} and restores {n} [t]MP[/t].</t>
+          <t>[k:confirm] Keep   [k:back] Revert</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>최대 [t]MP[/t]가 {n} 오르고 [t]MP[/t]를 {n} 회복합니다.</t>
+          <t>[k:confirm] 유지   [k:back] 되돌리기</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>tab.system</t>
+          <t>seed.choice.title</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Choose a Seed</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>시드 선택</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>tab.title.system</t>
+          <t>seed.choice.random</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Random Seed</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>시스템</t>
+          <t>무작위 시드</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>tab.system.quit_battle_help</t>
+          <t>seed.choice.enter</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Goes back to the title. Continue puts you back just before this battle.</t>
+          <t>Enter Seed</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>타이틀로 나갑니다. 이어하기를 하면 이 전투 직전부터 다시 시작합니다.</t>
+          <t>시드 입력</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>settings.keep.title</t>
+          <t>seed.entry.title</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Keep This Setting?</t>
+          <t>Enter Seed</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>이 설정을 유지할까요?</t>
+          <t>시드 입력</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>settings.keep.body</t>
+          <t>seed.entry.info</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>It goes back by itself in {n} s.</t>
+          <t>Up to 9 digits. Same seed, same run.</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>{n}초 뒤에 자동으로 원래대로 돌아갑니다.</t>
+          <t>최대 9자리. 같은 시드, 같은 도전.</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>settings.keep.hint</t>
+          <t>seed.entry.need</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>[k:confirm] Keep   [k:back] Revert</t>
+          <t>Enter a seed above zero.</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>[k:confirm] 유지   [k:back] 되돌리기</t>
+          <t>0보다 큰 시드를 입력하세요.</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>seed.choice.title</t>
+          <t>seed.entry.hint</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>Choose a Seed</t>
+          <t>[k:up][k:down] Digit   [k:left][k:right] Move</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>시드 선택</t>
+          <t>[k:up][k:down] 숫자   [k:left][k:right] 이동</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>seed.choice.random</t>
+          <t>seed.entry.hint2</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Random Seed</t>
+          <t>[k:confirm] Start</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>무작위 시드</t>
+          <t>[k:confirm] 시작</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>seed.choice.enter</t>
+          <t>seed.entry.hint3</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Enter Seed</t>
+          <t>[k:back] Back   [k:tab_prev] Delete</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>시드 입력</t>
+          <t>[k:back] 뒤로   [k:tab_prev] 삭제</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>seed.entry.title</t>
+          <t>confirm.abandon</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>Enter Seed</t>
+          <t>Abandon this run? It counts as a death, but you keep the echo.</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>시드 입력</t>
+          <t>이번 도전을 포기할까요? 죽은 것으로 기록되지만 메아리는 남습니다.</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>seed.entry.info</t>
+          <t>confirm.quit</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Up to 9 digits. Same seed, same run.</t>
+          <t>Quit to title? The run is saved and Continue picks it up again.</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>최대 9자리. 같은 시드, 같은 도전.</t>
+          <t>타이틀로 나갈까요? 도전은 저장되며 이어하기로 계속할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>seed.entry.need</t>
+          <t>confirm.quit_battle</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>Enter a seed above zero.</t>
+          <t>Quit to title? Continue puts you back just before this battle.</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>0보다 큰 시드를 입력하세요.</t>
+          <t>타이틀로 나갈까요? 이어하기를 하면 이 전투 직전으로 돌아옵니다.</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>seed.entry.hint</t>
+          <t>confirm.new_game</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>[k:up][k:down] Digit   [k:left][k:right] Move</t>
+          <t>Start a new game? The saved run will be abandoned.</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>[k:up][k:down] 숫자   [k:left][k:right] 이동</t>
+          <t>새 게임을 시작할까요? 저장된 도전은 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>seed.entry.hint2</t>
+          <t>confirm.echo</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>[k:confirm] Start</t>
+          <t>Keep {name} as your echo?</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>[k:confirm] 시작</t>
+          <t>{name}을(를) 메아리로 남길까요?</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>seed.entry.hint3</t>
+          <t>confirm.replace</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>[k:back] Back   [k:tab_prev] Delete</t>
+          <t>Forget {forget} and learn {learn}?</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>[k:back] 뒤로   [k:tab_prev] 삭제</t>
+          <t>{forget}을(를) 잊고 {learn}을(를) 배울까요?</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>confirm.abandon</t>
+          <t>confirm.sell</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>Abandon this run? It counts as a death, but you keep the echo.</t>
+          <t>Sell {name} for {price}?</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>이번 도전을 포기할까요? 죽은 것으로 기록되지만 메아리는 남습니다.</t>
+          <t>{name}을(를) {price}에 팔까요?</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>confirm.quit</t>
+          <t>tab.hint.read</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>Quit to title? The run is saved and Continue picks it up again.</t>
+          <t>[k:confirm] Read</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>타이틀로 나갈까요? 도전은 저장되며 이어하기로 계속할 수 있습니다.</t>
+          <t>[k:confirm] 읽기</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>confirm.quit_battle</t>
+          <t>tab.hint.scroll</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>Quit to title? Continue puts you back just before this battle.</t>
+          <t>[k:up][k:down] Scroll</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>타이틀로 나갈까요? 이어하기를 하면 이 전투 직전으로 돌아옵니다.</t>
+          <t>[k:up][k:down] 넘기기</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>confirm.new_game</t>
+          <t>note.found</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Start a new game? The saved run will be abandoned.</t>
+          <t>Note found: {title}</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>새 게임을 시작할까요? 저장된 도전은 사라집니다.</t>
+          <t>쪽지를 찾았다: {title}</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>confirm.echo</t>
+          <t>class.skill.unknown</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>Keep {name} as your echo?</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>{name}을(를) 메아리로 남길까요?</t>
+          <t>???</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>confirm.replace</t>
+          <t>status.short.status_poison</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>Forget {forget} and learn {learn}?</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>{forget}을(를) 잊고 {learn}을(를) 배울까요?</t>
+          <t>독</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>confirm.sell</t>
+          <t>status.short.status_bleed</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>Sell {name} for {price}?</t>
+          <t>BLD</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>{name}을(를) {price}에 팔까요?</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>tab.hint.read</t>
+          <t>status.short.status_burn</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>[k:confirm] Read</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>[k:confirm] 읽기</t>
+          <t>화상</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>tab.hint.scroll</t>
+          <t>status.short.status_stun</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>[k:up][k:down] Scroll</t>
+          <t>STN</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>[k:up][k:down] 넘기기</t>
+          <t>기절</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>note.found</t>
+          <t>status.short.status_guard</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>Note found: {title}</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>쪽지를 찾았다: {title}</t>
+          <t>방어</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>class.skill.unknown</t>
+          <t>status.short.status_dmg_up</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>기세</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>status.short.status_poison</t>
+          <t>status.short.status_evasion</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>PSN</t>
+          <t>EVA</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>독</t>
+          <t>회피</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>status.short.status_bleed</t>
+          <t>status.short.status_crit_up</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>BLD</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>조준</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>status.short.status_burn</t>
+          <t>status.short.status_hit_up</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>FORE</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>화상</t>
+          <t>선견</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>status.short.status_stun</t>
+          <t>status.short.status_meditation</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>STN</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>기절</t>
+          <t>명상</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>status.short.status_guard</t>
+          <t>status.short.status_solidify</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>Solid</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>방어</t>
+          <t>굳힘</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>status.short.status_dmg_up</t>
+          <t>status.short.status_bloodthirsty</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>REV</t>
+          <t>Thirst</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>기세</t>
+          <t>갈증</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>status.short.status_evasion</t>
+          <t>status.short.status_blessing</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>EVA</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>회피</t>
+          <t>축복</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>status.short.status_crit_up</t>
+          <t>status.short.status_sunder</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>Sunder</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>조준</t>
+          <t>분쇄</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>status.short.status_hit_up</t>
+          <t>status.short.status_brace</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>FORE</t>
+          <t>Brace</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>선견</t>
+          <t>태세</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>status.short.status_meditation</t>
+          <t>battle.chip.steadfast.short</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>Steady</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>명상</t>
+          <t>버티기</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>status.short.status_solidify</t>
+          <t>battle.chip.break.short</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Solid</t>
+          <t>BREAK</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>굳힘</t>
+          <t>브레이크</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>status.short.status_bloodthirsty</t>
+          <t>status.turns_left</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>Thirst</t>
+          <t>{turns} turns left.</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>갈증</t>
+          <t>{turns}턴 남았습니다.</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>status.short.status_blessing</t>
+          <t>status.turn_left</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Bless</t>
+          <t>1 turn left.</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>축복</t>
+          <t>1턴 남았습니다.</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>status.short.status_sunder</t>
+          <t>bed.msg.rested</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>Sunder</t>
+          <t>You are already rested.</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>분쇄</t>
+          <t>이미 충분히 쉬었습니다.</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>status.short.status_brace</t>
+          <t>bed.msg.nothing_to_upgrade</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>Brace</t>
+          <t>Nothing to upgrade there.</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>태세</t>
+          <t>강화할 수 있는 것이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>battle.chip.steadfast.short</t>
+          <t>bed.help.heal_rested</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>Steady</t>
+          <t>You are already rested. Come back when HP or MP is missing.</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>버티기</t>
+          <t>이미 충분히 쉬었습니다. HP나 MP가 줄었을 때 다시 오세요.</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>battle.chip.break.short</t>
+          <t>item.msg.nothing_happens</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>BREAK</t>
+          <t>Nothing happens.</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>브레이크</t>
+          <t>아무 일도 일어나지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>status.turns_left</t>
+          <t>help.stats.title</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>{turns} turns left.</t>
+          <t>Stats &amp; Terms</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>{turns}턴 남았습니다.</t>
+          <t>능력치와 용어</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>status.turn_left</t>
+          <t>help.stats.help</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>1 turn left.</t>
+          <t>What Power, ATK, DEF, MAG, SPD, VIG, MND, Crit, the grades, BREAK and every status mean.</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>1턴 남았습니다.</t>
+          <t>위력, ATK, DEF, MAG, SPD, VIG, MND, 치명타, 등급, 브레이크와 모든 상태 이상의 뜻입니다.</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>bed.msg.rested</t>
+          <t>help.term.crit</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>You are already rested.</t>
+          <t>Crit</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>이미 충분히 쉬었습니다.</t>
+          <t>치명타</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>bed.msg.nothing_to_upgrade</t>
+          <t>help.term.good</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Nothing to upgrade there.</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>강화할 수 있는 것이 없습니다.</t>
+          <t>좋음</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>bed.help.heal_rested</t>
+          <t>help.term.ok</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>You are already rested. Come back when HP or MP is missing.</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>이미 충분히 쉬었습니다. HP나 MP가 줄었을 때 다시 오세요.</t>
+          <t>무난</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>item.msg.nothing_happens</t>
+          <t>help.term.weak</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>Nothing happens.</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>아무 일도 일어나지 않았습니다.</t>
+          <t>약함</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>help.stats.title</t>
+          <t>help.term.break</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>Stats &amp; Terms</t>
+          <t>BREAK</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>능력치와 용어</t>
+          <t>브레이크</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>help.stats.help</t>
+          <t>help.line.power</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>What Power, ATK, DEF, MAG, SPD, VIG, MND, Crit, the grades, BREAK and every status mean.</t>
+          <t>How hard a weapon or skill hits. More Power means more damage.</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>위력, ATK, DEF, MAG, SPD, VIG, MND, 치명타, 등급, 브레이크와 모든 상태 이상의 뜻입니다.</t>
+          <t>무기나 스킬의 타격 세기입니다. 위력이 높을수록 피해가 커집니다.</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>help.term.crit</t>
+          <t>help.line.hp</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t>Health. At 0 HP you fall.</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>치명타</t>
+          <t>체력입니다. HP가 0이 되면 쓰러집니다.</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>help.term.good</t>
+          <t>help.line.mp</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Magic points. Skills spend them; potions and rest restore them.</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>좋음</t>
+          <t>스킬을 쓰면 줄어드는 마력입니다. 물약과 휴식으로 회복합니다.</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>help.term.ok</t>
+          <t>help.line.crit</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>A critical hit deals {mult} times the damage. [t]Take Aim[/t] and some gear raise the odds.</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>무난</t>
+          <t>치명타는 피해를 {mult}배로 줍니다. [t]조준[/t]과 일부 장비가 확률을 높입니다.</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>help.term.weak</t>
+          <t>help.line.perfect</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Press in the bright zone of the bar for +{pct}% damage.</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>약함</t>
+          <t>막대의 밝은 구간에서 누르면 피해가 {pct}% 늘어납니다.</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>help.term.break</t>
+          <t>help.line.good</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>BREAK</t>
+          <t>Press near the middle for +{pct}% damage.</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>브레이크</t>
+          <t>가운데 근처에서 누르면 피해가 {pct}% 늘어납니다.</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>help.line.power</t>
+          <t>help.line.ok</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>How hard a weapon or skill hits. More Power means more damage.</t>
+          <t>Press on the bar, off the middle, for normal damage.</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>무기나 스킬의 타격 세기입니다. 위력이 높을수록 피해가 커집니다.</t>
+          <t>막대 위에서 가운데를 벗어나 누르면 보통 피해를 줍니다.</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>help.line.hp</t>
+          <t>help.line.weak</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Health. At 0 HP you fall.</t>
+          <t>Miss the zone and the hit deals {pct}% less damage.</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>체력입니다. HP가 0이 되면 쓰러집니다.</t>
+          <t>구간을 놓치면 피해가 {pct}% 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>help.line.mp</t>
+          <t>help.line.break</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Magic points. Skills spend them; potions and rest restore them.</t>
+          <t>Good hits fill the [t]stagger[/t] meter. When it is full the enemy loses a turn and takes +{pct}% damage.</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>스킬을 쓰면 줄어드는 마력입니다. 물약과 휴식으로 회복합니다.</t>
+          <t>좋은 공격은 [t]경직[/t] 게이지를 채웁니다. 가득 차면 적이 한 턴을 잃고 피해를 {pct}% 더 받습니다.</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>help.line.crit</t>
+          <t>help.line.elite</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>A critical hit deals {mult} times the damage. [t]Take Aim[/t] and some gear raise the odds.</t>
+          <t>A marked, tougher enemy with a special trait. Its rewards are better.</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>치명타는 피해를 {mult}배로 줍니다. [t]조준[/t]과 일부 장비가 확률을 높입니다.</t>
+          <t>표시가 붙은 더 강한 적으로, 특별한 특성이 있습니다. 보상이 더 좋습니다.</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>help.line.perfect</t>
+          <t>choice.stranger.ask.0</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Press in the bright zone of the bar for +{pct}% damage.</t>
+          <t>There you are.</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>막대의 밝은 구간에서 누르면 피해가 {pct}% 늘어납니다.</t>
+          <t>거기 있었군.</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>help.line.good</t>
+          <t>choice.stranger.ask.1</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Press near the middle for +{pct}% damage.</t>
+          <t>Do you remember me?</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>가운데 근처에서 누르면 피해가 {pct}% 늘어납니다.</t>
+          <t>나를 기억해?</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>help.line.ok</t>
+          <t>choice.stranger.label.0</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>Press on the bar, off the middle, for normal damage.</t>
+          <t>Should I?</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>막대 위에서 가운데를 벗어나 누르면 보통 피해를 줍니다.</t>
+          <t>기억해야 해?</t>
         </is>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>help.line.weak</t>
+          <t>choice.stranger.label.1</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Miss the zone and the hit deals {pct}% less damage.</t>
+          <t>Back off.</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>구간을 놓치면 피해가 {pct}% 줄어듭니다.</t>
+          <t>저리 가.</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>help.line.break</t>
+          <t>choice.stranger.reply1.0</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Good hits fill the [t]stagger[/t] meter. When it is full the enemy loses a turn and takes +{pct}% damage.</t>
+          <t>Not yet.</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>좋은 공격은 [t]경직[/t] 게이지를 채웁니다. 가득 차면 적이 한 턴을 잃고 피해를 {pct}% 더 받습니다.</t>
+          <t>아직은 아니야.</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>help.line.elite</t>
+          <t>choice.stranger.reply1.1</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>A marked, tougher enemy with a special trait. Its rewards are better.</t>
+          <t>Ask again when the tunnel has had you a bit longer.</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>표시가 붙은 더 강한 적으로, 특별한 특성이 있습니다. 보상이 더 좋습니다.</t>
+          <t>터널이 널 좀 더 삼키면 다시 물어봐.</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>choice.stranger.ask.0</t>
+          <t>choice.stranger.reply2.0</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>There you are.</t>
+          <t>Ha. Fair.</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>거기 있었군.</t>
+          <t>하하, 그렇겠지.</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>choice.stranger.ask.1</t>
+          <t>choice.stranger.reply2.1</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Do you remember me?</t>
+          <t>Nobody does, at first.</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>나를 기억해?</t>
+          <t>처음엔 다들 그래.</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>choice.stranger.label.0</t>
+          <t>choice.stranger.again1.0</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Should I?</t>
+          <t>Still asking if you should?</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>기억해야 해?</t>
+          <t>아직도 기억해야 하는지 묻는군?</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>choice.stranger.label.1</t>
+          <t>choice.stranger.again1.1</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Back off.</t>
+          <t>You'll know me when you stop asking.</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>저리 가.</t>
+          <t>묻기를 그만두면 알게 될 거야.</t>
         </is>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>choice.stranger.reply1.0</t>
+          <t>choice.stranger.again2.0</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Not yet.</t>
+          <t>Still telling me to back off?</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>아직은 아니야.</t>
+          <t>아직도 저리 가라고 하는군?</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>choice.stranger.reply1.1</t>
+          <t>choice.stranger.again2.1</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Ask again when the tunnel has had you a bit longer.</t>
+          <t>I'm patient. I've had practice.</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>터널이 널 좀 더 삼키면 다시 물어봐.</t>
+          <t>난 참을성이 있어. 연습을 많이 했거든.</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>choice.stranger.reply2.0</t>
+          <t>choice.merchant.ask.0</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Ha. Fair.</t>
+          <t>Tell me, friend.</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>하하, 그렇겠지.</t>
+          <t>말해 봐, 친구.</t>
         </is>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>choice.stranger.reply2.1</t>
+          <t>choice.merchant.ask.1</t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Nobody does, at first.</t>
+          <t>Looking for a way out, or something to buy?</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>처음엔 다들 그래.</t>
+          <t>나갈 길을 찾는 거야, 아니면 살 게 있는 거야?</t>
         </is>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>choice.stranger.again1.0</t>
+          <t>choice.merchant.label.0</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Still asking if you should?</t>
+          <t>A way out.</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>아직도 기억해야 하는지 묻는군?</t>
+          <t>나갈 길.</t>
         </is>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>choice.stranger.again1.1</t>
+          <t>choice.merchant.label.1</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>You'll know me when you stop asking.</t>
+          <t>Something to buy.</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>묻기를 그만두면 알게 될 거야.</t>
+          <t>살 물건.</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>choice.stranger.again2.0</t>
+          <t>choice.merchant.reply1.0</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Still telling me to back off?</t>
+          <t>Ha. They all say that.</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>아직도 저리 가라고 하는군?</t>
+          <t>하하, 다들 그렇게 말하지.</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>choice.stranger.again2.1</t>
+          <t>choice.merchant.reply1.1</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>I'm patient. I've had practice.</t>
+          <t>Shop first. Hope walks better with a full pack.</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>난 참을성이 있어. 연습을 많이 했거든.</t>
+          <t>일단 사. 짐이 든든해야 희망도 잘 걷거든.</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>choice.merchant.ask.0</t>
+          <t>choice.merchant.reply2.0</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Tell me, friend.</t>
+          <t>Good. Buying I understand.</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>말해 봐, 친구.</t>
+          <t>좋아. 장사라면 내가 잘 알지.</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>choice.merchant.ask.1</t>
+          <t>choice.merchant.reply2.1</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Looking for a way out, or something to buy?</t>
+          <t>Asking after exits gets people killed.</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>나갈 길을 찾는 거야, 아니면 살 게 있는 거야?</t>
+          <t>출구를 캐묻다 죽은 사람이 한둘이 아니야.</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>choice.merchant.label.0</t>
+          <t>choice.merchant.again1.0</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>A way out.</t>
+          <t>Found your way out yet? No? Then buy something.</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>나갈 길.</t>
+          <t>나갈 길은 찾았어? 아직이면 뭐라도 사.</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>choice.merchant.label.1</t>
+          <t>choice.merchant.again2.0</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>Something to buy.</t>
+          <t>Back to spend, I hope. That I understand.</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>살 물건.</t>
+          <t>돈 쓰러 왔길 바란다. 그거라면 내가 잘 알지.</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>choice.merchant.reply1.0</t>
+          <t>choice.map_page.ask.0</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>Ha. They all say that.</t>
+          <t>You read it twice.</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>하하, 다들 그렇게 말하지.</t>
+          <t>두 번 읽는다.</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>choice.merchant.reply1.1</t>
+          <t>choice.map_page.ask.1</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Shop first. Hope walks better with a full pack.</t>
+          <t>Whose hand is this?</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>일단 사. 짐이 든든해야 희망도 잘 걷거든.</t>
+          <t>누구의 글씨일까?</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>choice.merchant.reply2.0</t>
+          <t>choice.map_page.label.0</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>Good. Buying I understand.</t>
+          <t>Mine.</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>좋아. 장사라면 내가 잘 알지.</t>
+          <t>내 것.</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>choice.merchant.reply2.1</t>
+          <t>choice.map_page.label.1</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>Asking after exits gets people killed.</t>
+          <t>Someone else's.</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>출구를 캐묻다 죽은 사람이 한둘이 아니야.</t>
+          <t>남의 것.</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>choice.merchant.again1.0</t>
+          <t>choice.map_page.reply1.0</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>Found your way out yet? No? Then buy something.</t>
+          <t>Yours. You say it out loud.</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>나갈 길은 찾았어? 아직이면 뭐라도 사.</t>
+          <t>내 글씨다. 소리 내어 말해 본다.</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>choice.merchant.again2.0</t>
+          <t>choice.map_page.reply1.1</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Back to spend, I hope. That I understand.</t>
+          <t>The ink seems to settle.</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>돈 쓰러 왔길 바란다. 그거라면 내가 잘 알지.</t>
+          <t>잉크가 가라앉는 듯하다.</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>choice.map_page.ask.0</t>
+          <t>choice.map_page.reply2.0</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>You read it twice.</t>
+          <t>Not yours. You say it out loud.</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>두 번 읽는다.</t>
+          <t>내 글씨가 아니다. 소리 내어 말해 본다.</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>choice.map_page.ask.1</t>
+          <t>choice.map_page.reply2.1</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Whose hand is this?</t>
+          <t>The ink shivers.</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>누구의 글씨일까?</t>
+          <t>잉크가 떨리는 듯하다.</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>choice.map_page.label.0</t>
+          <t>choice.map_page.again1.0</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Mine.</t>
+          <t>The ink is dry now. You've stopped doubting the hand.</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>내 것.</t>
+          <t>잉크가 말랐다. 이 글씨를 더는 의심하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>choice.map_page.label.1</t>
+          <t>choice.map_page.again2.0</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Someone else's.</t>
+          <t>The ink is dry now. You still say it isn't yours.</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>남의 것.</t>
+          <t>잉크가 말랐다. 그래도 내 글씨가 아니라고 말한다.</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>choice.map_page.reply1.0</t>
+          <t>choice.wake.ask.0</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Yours. You say it out loud.</t>
+          <t>Your head swims.</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>내 글씨다. 소리 내어 말해 본다.</t>
+          <t>머리가 어지럽다.</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>choice.map_page.reply1.1</t>
+          <t>choice.wake.ask.1</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>The ink seems to settle.</t>
+          <t>Your body waits for you to decide.</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>잉크가 가라앉는 듯하다.</t>
+          <t>몸이 당신의 결정을 기다린다.</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>choice.map_page.reply2.0</t>
+          <t>choice.wake.label.0</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Not yours. You say it out loud.</t>
+          <t>Sit up.</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>내 글씨가 아니다. 소리 내어 말해 본다.</t>
+          <t>일어난다.</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>choice.map_page.reply2.1</t>
+          <t>choice.wake.label.1</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>The ink shivers.</t>
+          <t>Lie still.</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>잉크가 떨리는 듯하다.</t>
+          <t>가만히 있는다.</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>choice.map_page.again1.0</t>
+          <t>choice.wake.reply1.0</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>The ink is dry now. You've stopped doubting the hand.</t>
+          <t>You push up. The stone lets go of your back slowly.</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>잉크가 말랐다. 이 글씨를 더는 의심하지 않는다.</t>
+          <t>몸을 일으킨다. 돌바닥이 등을 천천히 놓아 준다.</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>choice.map_page.again2.0</t>
+          <t>choice.wake.reply2.0</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>The ink is dry now. You still say it isn't yours.</t>
+          <t>You lie still. The ceiling says nothing. Neither do you.</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>잉크가 말랐다. 그래도 내 글씨가 아니라고 말한다.</t>
+          <t>가만히 누워 있다. 천장은 말이 없다. 당신도 그렇다.</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>choice.wake.ask.0</t>
+          <t>choice.wake.again1.0</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>Your head swims.</t>
+          <t>Your body already knows how to get up.</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>머리가 어지럽다.</t>
+          <t>몸은 이미 일어나는 법을 안다.</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>choice.wake.ask.1</t>
+          <t>choice.wake.again2.0</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Your body waits for you to decide.</t>
+          <t>You lie still a while first. You always do now.</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>몸이 당신의 결정을 기다린다.</t>
+          <t>먼저 한참 누워 있는다. 이제는 늘 그렇다.</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>choice.wake.label.0</t>
+          <t>menu.msg.items_in_fight</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>Sit up.</t>
+          <t>In a battle, use Item in the battle menu.</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>일어난다.</t>
+          <t>전투 중에는 전투 메뉴의 아이템을 사용하세요.</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>choice.wake.label.1</t>
+          <t>menu.msg.gear_in_fight</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>Lie still.</t>
+          <t>You can't change gear during a battle.</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>가만히 있는다.</t>
+          <t>전투 중에는 장비를 바꿀 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>choice.wake.reply1.0</t>
+          <t>dialogue.first_encounter_mini_boss.0</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>You push up. The stone lets go of your back slowly.</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>몸을 일으킨다. 돌바닥이 등을 천천히 놓아 준다.</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>choice.wake.reply2.0</t>
+          <t>dialogue.first_encounter_mini_boss.1</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>You lie still. The ceiling says nothing. Neither do you.</t>
+          <t>Oh, what the hell is that?</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>가만히 누워 있다. 천장은 말이 없다. 당신도 그렇다.</t>
+          <t>아니, 저게 대체 뭐야?</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>choice.wake.again1.0</t>
+          <t>dialogue.first_encounter_mini_boss.2</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>Your body already knows how to get up.</t>
+          <t>Half cow, half man?</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>몸은 이미 일어나는 법을 안다.</t>
+          <t>반은 소, 반은 사람?</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>choice.wake.again2.0</t>
+          <t>dialogue.first_encounter_mini_boss.3</t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>You lie still a while first. You always do now.</t>
+          <t>That breathing. Those horns...</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>먼저 한참 누워 있는다. 이제는 늘 그렇다.</t>
+          <t>저 숨소리. 저 뿔...</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>menu.msg.items_in_fight</t>
+          <t>dialogue.first_encounter_mini_boss.4</t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>In a battle, use Item in the battle menu.</t>
+          <t>And he's blocking the only way forward.</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>전투 중에는 전투 메뉴의 아이템을 사용하세요.</t>
+          <t>하필 하나뿐인 길을 막고 서 있어.</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>menu.msg.gear_in_fight</t>
+          <t>dialogue.first_encounter_mini_boss.5</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>You can't change gear during a battle.</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>전투 중에는 장비를 바꿀 수 없습니다.</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.0</t>
+          <t>dialogue.first_encounter_mini_boss.6</t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Fuck.</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>젠장.</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.1</t>
+          <t>dialogue.first_encounter_final_boss.0</t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>Oh, what the hell is that?</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>아니, 저게 대체 뭐야?</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.2</t>
+          <t>dialogue.first_encounter_final_boss.1</t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Half cow, half man?</t>
+          <t>Another demon.</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>반은 소, 반은 사람?</t>
+          <t>또 악마인가.</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.3</t>
+          <t>dialogue.first_encounter_final_boss.2</t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>That breathing. Those horns...</t>
+          <t>This one is different.</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>저 숨소리. 저 뿔...</t>
+          <t>이번 놈은 달라.</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.4</t>
+          <t>dialogue.first_encounter_final_boss.3</t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>And he's blocking the only way forward.</t>
+          <t>As if it's looking for something...</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>하필 하나뿐인 길을 막고 서 있어.</t>
+          <t>무언가를 찾는 것 같아...</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.5</t>
+          <t>dialogue.first_encounter_final_boss.4</t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
@@ -20112,296 +20112,296 @@
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_mini_boss.6</t>
+          <t>dialogue.first_encounter_final_boss.5</t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Fuck.</t>
+          <t>...someone.</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>젠장.</t>
+          <t>...누군가를.</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_final_boss.0</t>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.0</t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>*Pant*... Whew.</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>*헉*... 휴.</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_final_boss.1</t>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.1</t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Another demon.</t>
+          <t>A wolf now? Seriously?</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>또 악마인가.</t>
+          <t>이번엔 늑대라고? 진짜로?</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_final_boss.2</t>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.2</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>This one is different.</t>
+          <t>Where do these things come from?</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>이번 놈은 달라.</t>
+          <t>이것들은 다 어디서 나오는 거야?</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_final_boss.3</t>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.3</t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>As if it's looking for something...</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>무언가를 찾는 것 같아...</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_final_boss.4</t>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.4</t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Standing here won't answer that.</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>여기 서 있어도 답은 안 나와.</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>dialogue.first_encounter_final_boss.5</t>
+          <t>dialogue.sys_floor2_dire_wolf_reaction.5</t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>...someone.</t>
+          <t>Keep moving.</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>...누군가를.</t>
+          <t>계속 가자.</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor2_dire_wolf_reaction.0</t>
+          <t>dialogue.sys_first_stranger_encounter_reaction.0</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>*Pant*... Whew.</t>
+          <t>Get your hands off me...</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>*헉*... 휴.</t>
+          <t>손 치워...</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor2_dire_wolf_reaction.1</t>
+          <t>dialogue.sys_first_stranger_encounter_reaction.1</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>A wolf now? Seriously?</t>
+          <t>He smiled the whole time.</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>이번엔 늑대라고? 진짜로?</t>
+          <t>그 녀석, 내내 웃고 있었어.</t>
         </is>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor2_dire_wolf_reaction.2</t>
+          <t>dialogue.sys_first_stranger_encounter_reaction.2</t>
         </is>
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>Where do these things come from?</t>
+          <t>Are they all demons down here?</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>이것들은 다 어디서 나오는 거야?</t>
+          <t>여기 있는 건 전부 악마야?</t>
         </is>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor2_dire_wolf_reaction.3</t>
+          <t>dialogue.sys_first_stranger_encounter_reaction.3</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>What else would they be.</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>달리 뭐겠어.</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor2_dire_wolf_reaction.4</t>
+          <t>dialogue.sys_first_stranger_encounter_reaction.4</t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Standing here won't answer that.</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>여기 서 있어도 답은 안 나와.</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor2_dire_wolf_reaction.5</t>
+          <t>dialogue.sys_first_stranger_encounter_reaction.5</t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Keep moving.</t>
+          <t>I have to keep moving.</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>계속 가자.</t>
+          <t>계속 움직여야 해.</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_stranger_encounter_reaction.0</t>
+          <t>dialogue.sys_first_level_up_reaction.0</t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>Get your hands off me...</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>손 치워...</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_stranger_encounter_reaction.1</t>
+          <t>dialogue.sys_first_level_up_reaction.1</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>He smiled the whole time.</t>
+          <t>The walls tilt. Easy... easy.</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>그 녀석, 내내 웃고 있었어.</t>
+          <t>벽이 기운다. 진정해... 진정해.</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_stranger_encounter_reaction.2</t>
+          <t>dialogue.sys_first_level_up_reaction.2</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>Are they all demons down here?</t>
+          <t>I think I'm going to be sick...</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>여기 있는 건 전부 악마야?</t>
+          <t>토할 것 같아...</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_stranger_encounter_reaction.3</t>
+          <t>dialogue.sys_first_level_up_reaction.3</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>What else would they be.</t>
+          <t>Why does it feel like I've been training for years?</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>달리 뭐겠어.</t>
+          <t>왜 몇 년 동안 훈련한 것처럼 몸이 쑤시지?</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_stranger_encounter_reaction.4</t>
+          <t>dialogue.sys_first_level_up_reaction.4</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
@@ -20418,143 +20418,143 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_stranger_encounter_reaction.5</t>
+          <t>dialogue.sys_first_level_up_reaction.5</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>I have to keep moving.</t>
+          <t>...and different.</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>계속 움직여야 해.</t>
+          <t>...그리고 달라졌어.</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_level_up_reaction.0</t>
+          <t>dialogue.sys_first_equippable_item_reaction.0</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>This might come in handy.</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>쓸모가 있겠는걸.</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_level_up_reaction.1</t>
+          <t>dialogue.sys_first_equippable_item_reaction.1</t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>The walls tilt. Easy... easy.</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>벽이 기운다. 진정해... 진정해.</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_level_up_reaction.2</t>
+          <t>dialogue.sys_first_equippable_item_reaction.2</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>I think I'm going to be sick...</t>
+          <t>Chests every few steps.</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>토할 것 같아...</t>
+          <t>몇 걸음마다 상자가 있어.</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_level_up_reaction.3</t>
+          <t>dialogue.sys_first_equippable_item_reaction.3</t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>Why does it feel like I've been training for years?</t>
+          <t>Gear that fits like it was made for me.</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>왜 몇 년 동안 훈련한 것처럼 몸이 쑤시지?</t>
+          <t>내 몸에 맞춘 듯한 장비들.</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_level_up_reaction.4</t>
+          <t>dialogue.sys_first_equippable_item_reaction.4</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Somebody wants me armed.</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>누군가 내가 무장하길 바라는 거야.</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_level_up_reaction.5</t>
+          <t>dialogue.sys_first_equippable_item_reaction.5</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>...and different.</t>
+          <t>But why arm us, if they wanted us dead?</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>...그리고 달라졌어.</t>
+          <t>우리를 죽일 셈이면 왜 무기를 쥐여 주지?</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_equippable_item_reaction.0</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.0</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>This might come in handy.</t>
+          <t>*Huff*... *Wheeze*... Fuck.</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>쓸모가 있겠는걸.</t>
+          <t>*헉*... *쌕*... 젠장.</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_equippable_item_reaction.1</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.1</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
@@ -20571,126 +20571,126 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_equippable_item_reaction.2</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.2</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>Chests every few steps.</t>
+          <t>I did it. I actually did it.</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>몇 걸음마다 상자가 있어.</t>
+          <t>해냈어. 정말 해냈어.</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_equippable_item_reaction.3</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.3</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>Gear that fits like it was made for me.</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>내 몸에 맞춘 듯한 장비들.</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_equippable_item_reaction.4</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.4</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>Somebody wants me armed.</t>
+          <t>Still...</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>누군가 내가 무장하길 바라는 거야.</t>
+          <t>그런데...</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>dialogue.sys_first_equippable_item_reaction.5</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.5</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>But why arm us, if they wanted us dead?</t>
+          <t>Nothing here makes sense.</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>우리를 죽일 셈이면 왜 무기를 쥐여 주지?</t>
+          <t>여긴 아무것도 말이 안 돼.</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.0</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.6</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>*Huff*... *Wheeze*... Fuck.</t>
+          <t>Am I the only one seeing this?</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>*헉*... *쌕*... 젠장.</t>
+          <t>이걸 보는 게 나뿐인가?</t>
         </is>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.1</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.7</t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Who cares. The exit is right there.</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>아무렴 어때. 출구가 바로 저기야.</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.2</t>
+          <t>dialogue.sys_final_boss_defeated_reaction.8</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>I did it. I actually did it.</t>
+          <t>Time to find the others, and a way home.</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>해냈어. 정말 해냈어.</t>
+          <t>동료들을 찾아서 집으로 가는 길을 찾자.</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.3</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.0</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
@@ -20707,969 +20707,952 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.4</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.1</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>Still...</t>
+          <t>(Colors flood in, far too bright.)</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>그런데...</t>
+          <t>(색이 쏟아져 들어온다. 너무 밝다.)</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.5</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.2</t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>Nothing here makes sense.</t>
+          <t>(Black threads curl through your sight, then vanish.)</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>여긴 아무것도 말이 안 돼.</t>
+          <t>(검은 실 같은 것이 시야를 휘감았다가 사라진다.)</t>
         </is>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.6</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.3</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>Am I the only one seeing this?</t>
+          <t>(The tunnel snaps back around you.)</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>이걸 보는 게 나뿐인가?</t>
+          <t>(터널이 다시 당신을 에워싼다.)</t>
         </is>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.7</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.4</t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>Who cares. The exit is right there.</t>
+          <t>Huh?</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>아무렴 어때. 출구가 바로 저기야.</t>
+          <t>응?</t>
         </is>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>dialogue.sys_final_boss_defeated_reaction.8</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.5</t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Time to find the others, and a way home.</t>
+          <t>...</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>동료들을 찾아서 집으로 가는 길을 찾자.</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.0</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.6</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>My head...</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>머리가...</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.1</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.7</t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>(Colors flood in, far too bright.)</t>
+          <t>It feels like it's about to split.</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>(색이 쏟아져 들어온다. 너무 밝다.)</t>
+          <t>쪼개질 것 같아.</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.2</t>
+          <t>dialogue.sys_floor9_5_exit_reaction.8</t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>(Black threads curl through your sight, then vanish.)</t>
+          <t>(You clutch your head while walking toward the exit.)</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>(검은 실 같은 것이 시야를 휘감았다가 사라진다.)</t>
+          <t>(머리를 부여잡고 출구를 향해 걷는다.)</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.3</t>
+          <t>controls.waiting_pad</t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>(The tunnel snaps back around you.)</t>
+          <t>Press the new key for {action}. [k:back] cancels.</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>(터널이 다시 당신을 에워싼다.)</t>
+          <t>{action}에 쓸 새 키를 누르세요. [k:back] 버튼으로 취소합니다.</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.4</t>
+          <t>combat.msg.overpower_prefix</t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>Huh?</t>
+          <t>You overpower {enemy}.</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>응?</t>
+          <t>{enemy}을(를) 가볍게 쓰러뜨렸습니다.</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.5</t>
+          <t>controls.reset_ask</t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>Reset every key to its default?</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>모든 키를 기본값으로 되돌릴까요?</t>
         </is>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.6</t>
+          <t>controls.reset_same</t>
         </is>
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>My head...</t>
+          <t>Keys were already the defaults.</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>머리가...</t>
+          <t>키가 이미 기본값입니다.</t>
         </is>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.7</t>
+          <t>profile.default_name</t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>It feels like it's about to split.</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>쪼개질 것 같아.</t>
+          <t>프로필</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>dialogue.sys_floor9_5_exit_reaction.8</t>
+          <t>save.slot.name</t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>(You clutch your head while walking toward the exit.)</t>
+          <t>Save {n}</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>(머리를 부여잡고 출구를 향해 걷는다.)</t>
+          <t>저장 {n}</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>controls.waiting_pad</t>
+          <t>save.slot.empty</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>Press the new key for {action}. [k:back] cancels.</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>{action}에 쓸 새 키를 누르세요. [k:back] 버튼으로 취소합니다.</t>
+          <t>비어 있음</t>
         </is>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>combat.msg.overpower_prefix</t>
+          <t>save.slot.cant</t>
         </is>
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>You overpower {enemy}.</t>
+          <t>Cannot load</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>{enemy}을(를) 가볍게 쓰러뜨렸습니다.</t>
+          <t>불러올 수 없음</t>
         </is>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>controls.reset_ask</t>
+          <t>save.lbl.saved</t>
         </is>
       </c>
       <c r="B1210" t="inlineStr">
         <is>
-          <t>Reset every key to its default?</t>
+          <t>Last Saved</t>
         </is>
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>모든 키를 기본값으로 되돌릴까요?</t>
+          <t>마지막 저장</t>
         </is>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>controls.reset_same</t>
+          <t>save.slot.help_load</t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>Keys were already the defaults.</t>
+          <t>Pick up this run where you left it.</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>키가 이미 기본값입니다.</t>
+          <t>중단한 곳에서 이 도전을 이어갑니다.</t>
         </is>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>profile.default_name</t>
+          <t>save.slot.help_over</t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>A new game here replaces this run.</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>여기서 새 게임을 시작하면 이 도전은 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>save.slot.name</t>
+          <t>save.slot.help_empty</t>
         </is>
       </c>
       <c r="B1213" t="inlineStr">
         <is>
-          <t>Save {n}</t>
+          <t>No run is saved in this file.</t>
         </is>
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>저장 {n}</t>
+          <t>이 파일에는 저장된 도전이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>save.slot.empty</t>
+          <t>save.overwrite.title</t>
         </is>
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Overwrite which save file?</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>비어 있음</t>
+          <t>어느 저장 파일을 덮어쓸까요?</t>
         </is>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>save.slot.cant</t>
+          <t>save.overwrite.ask</t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>Cannot load</t>
+          <t>Overwrite Save {n}? The run in it will be lost.</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>불러올 수 없음</t>
+          <t>저장 {n}을(를) 덮어쓸까요? 그 안의 도전은 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>save.lbl.saved</t>
+          <t>save.delete.ask</t>
         </is>
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Last Saved</t>
+          <t>Delete Save {n}? The run in it will be lost.</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>마지막 저장</t>
+          <t>저장 {n}을(를) 삭제할까요? 그 안의 도전은 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>save.slot.help_load</t>
+          <t>save.hint.load</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Pick up this run where you left it.</t>
+          <t>[k:confirm] Load</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>중단한 곳에서 이 도전을 이어갑니다.</t>
+          <t>[k:confirm] 불러오기</t>
         </is>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>save.slot.help_over</t>
+          <t>save.hint.overwrite</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>A new game here replaces this run.</t>
+          <t>[k:confirm] Overwrite</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>여기서 새 게임을 시작하면 이 도전은 사라집니다.</t>
+          <t>[k:confirm] 덮어쓰기</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>save.slot.help_empty</t>
+          <t>save.hint.delete</t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>No run is saved in this file.</t>
+          <t>[k:tab_prev] Delete</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>이 파일에는 저장된 도전이 없습니다.</t>
+          <t>[k:tab_prev] 삭제</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>save.overwrite.title</t>
+          <t>profile.btn</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Overwrite which save file?</t>
+          <t>[k:tab_prev] Profile</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>어느 저장 파일을 덮어쓸까요?</t>
+          <t>[k:tab_prev] 프로필</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>save.overwrite.ask</t>
+          <t>profile.title</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>Overwrite Save {n}? The run in it will be lost.</t>
+          <t>Profiles</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>저장 {n}을(를) 덮어쓸까요? 그 안의 도전은 사라집니다.</t>
+          <t>프로필</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>save.delete.ask</t>
+          <t>profile.row.new</t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>Delete Save {n}? The run in it will be lost.</t>
+          <t>New Profile</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>저장 {n}을(를) 삭제할까요? 그 안의 도전은 사라집니다.</t>
+          <t>새 프로필</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>save.hint.load</t>
+          <t>profile.val.active</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>[k:confirm] Load</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>[k:confirm] 불러오기</t>
+          <t>사용 중</t>
         </is>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>save.hint.overwrite</t>
+          <t>profile.lbl.runs</t>
         </is>
       </c>
       <c r="B1224" t="inlineStr">
         <is>
-          <t>[k:confirm] Overwrite</t>
+          <t>Runs</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>[k:confirm] 덮어쓰기</t>
+          <t>도전 횟수</t>
         </is>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>save.hint.delete</t>
+          <t>profile.help.active</t>
         </is>
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>[k:tab_prev] Delete</t>
+          <t>The profile in use. Its Codex, run history and story are the ones you see.</t>
         </is>
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>[k:tab_prev] 삭제</t>
+          <t>지금 쓰는 프로필입니다. 도감, 도전 기록, 이야기는 이 프로필의 것입니다.</t>
         </is>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>profile.btn</t>
+          <t>profile.help.other</t>
         </is>
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>[k:tab_prev] Profile</t>
+          <t>Switch to this profile. Its Codex, run history, story and save files come with it.</t>
         </is>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>[k:tab_prev] 프로필</t>
+          <t>이 프로필로 바꿉니다. 도감, 도전 기록, 이야기, 저장 파일도 함께 바뀝니다.</t>
         </is>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>profile.title</t>
+          <t>profile.help.new</t>
         </is>
       </c>
       <c r="B1227" t="inlineStr">
         <is>
-          <t>Profiles</t>
+          <t>Start a new profile. Its Codex and run history are empty and the story begins again.</t>
         </is>
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>프로필</t>
+          <t>새 프로필을 만듭니다. 도감과 도전 기록은 비어 있고 이야기는 처음부터 시작합니다.</t>
         </is>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>profile.row.new</t>
+          <t>profile.hint.switch</t>
         </is>
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>New Profile</t>
+          <t>[k:confirm] Switch</t>
         </is>
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>새 프로필</t>
+          <t>[k:confirm] 바꾸기</t>
         </is>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>profile.val.active</t>
+          <t>profile.hint.create</t>
         </is>
       </c>
       <c r="B1229" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>[k:confirm] Create</t>
         </is>
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>사용 중</t>
+          <t>[k:confirm] 만들기</t>
         </is>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>profile.lbl.runs</t>
+          <t>profile.delete.ask</t>
         </is>
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>Runs</t>
+          <t>Delete profile {name}? Its Codex, history and save files are lost.</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>도전 횟수</t>
+          <t>프로필 {name}을(를) 삭제할까요? 도감, 기록, 저장 파일이 모두 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>profile.help.active</t>
+          <t>profile.name.need</t>
         </is>
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>The profile in use. Its Codex, run history and story are the ones you see.</t>
+          <t>Enter a name.</t>
         </is>
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>지금 쓰는 프로필입니다. 도감, 도전 기록, 이야기는 이 프로필의 것입니다.</t>
+          <t>이름을 입력하세요.</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>profile.help.other</t>
+          <t>profile.name.key_space</t>
         </is>
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>Switch to this profile. Its Codex, run history, story and save files come with it.</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>이 프로필로 바꿉니다. 도감, 도전 기록, 이야기, 저장 파일도 함께 바뀝니다.</t>
+          <t>띄어쓰기</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>profile.help.new</t>
+          <t>profile.name.key_delete</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>Start a new profile. Its Codex and run history are empty and the story begins again.</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>새 프로필을 만듭니다. 도감과 도전 기록은 비어 있고 이야기는 처음부터 시작합니다.</t>
+          <t>삭제</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>profile.hint.switch</t>
+          <t>profile.name.key_ok</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>[k:confirm] Switch</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>[k:confirm] 바꾸기</t>
+          <t>확인</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>profile.hint.create</t>
+          <t>profile.name.hint_pick</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>[k:confirm] Create</t>
+          <t>[k:confirm] Pick</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>[k:confirm] 만들기</t>
+          <t>[k:confirm] 선택</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>profile.delete.ask</t>
+          <t>profile.name.hint_cancel</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Delete profile {name}? Its Codex, history and save files are lost.</t>
+          <t>[k:back] Cancel</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>프로필 {name}을(를) 삭제할까요? 도감, 기록, 저장 파일이 모두 사라집니다.</t>
+          <t>[k:back] 취소</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>profile.name.need</t>
+          <t>profile.name.info_kb</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>Enter a name.</t>
+          <t>Up to 12 letters. Backspace deletes, Enter finishes.</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>이름을 입력하세요.</t>
+          <t>최대 12자. Backspace로 지우고 Enter로 끝냅니다.</t>
         </is>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>profile.name.key_space</t>
+          <t>profile.name.info_pad</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Up to 12 letters. Pick them on the grid.</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>띄어쓰기</t>
+          <t>최대 12자. 칸에서 골라 입력하세요.</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>profile.name.key_delete</t>
+          <t>codex.btn</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>[k:tab_next] Codex</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>삭제</t>
+          <t>[k:tab_next] 도감</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>profile.name.key_ok</t>
+          <t>menu.tooltip.stat.vig.desc</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Raises max [t]HP[/t]. The more you add, the less each point gives.</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>최대 [t]HP[/t]를 늘립니다. 많이 올릴수록 포인트 하나의 효과는 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>profile.name.hint_pick</t>
+          <t>menu.tooltip.stat.mnd.desc</t>
         </is>
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>[k:confirm] Pick</t>
+          <t>Raises max [t]MP[/t]. The more you add, the less each point gives.</t>
         </is>
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>[k:confirm] 선택</t>
+          <t>최대 [t]MP[/t]를 늘립니다. 많이 올릴수록 포인트 하나의 효과는 줄어듭니다.</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>profile.name.hint_cancel</t>
+          <t>tab.lbl.max_hp</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>[k:back] Cancel</t>
+          <t>Max HP</t>
         </is>
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>[k:back] 취소</t>
+          <t>최대 HP</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>profile.name.info_kb</t>
+          <t>tab.lbl.max_mp</t>
         </is>
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Up to 12 letters. Backspace deletes, Enter finishes.</t>
+          <t>Max MP</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>최대 12자. Backspace로 지우고 Enter로 끝냅니다.</t>
+          <t>최대 MP</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>profile.name.info_pad</t>
+          <t>tab.val.level_up</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Up to 12 letters. Pick them on the grid.</t>
+          <t>Level Up</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>최대 12자. 칸에서 골라 입력하세요.</t>
+          <t>레벨 업</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>codex.btn</t>
+          <t>levelup.legend</t>
         </is>
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>[k:tab_next] Codex</t>
+          <t>Gold = your class grows these</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>[k:tab_next] 도감</t>
+          <t>금색 = 직업이 성장시키는 능력치</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>menu.tooltip.stat.vig.desc</t>
+          <t>cards.stat.hp_now</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Raises max [t]HP[/t]. The more you add, the less each point gives.</t>
+          <t>Max HP Now</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>최대 [t]HP[/t]를 늘립니다. 많이 올릴수록 포인트 하나의 효과는 줄어듭니다.</t>
+          <t>최대 HP 현재</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>menu.tooltip.stat.mnd.desc</t>
+          <t>cards.stat.hp_after</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Raises max [t]MP[/t]. The more you add, the less each point gives.</t>
+          <t>Max HP After</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>최대 [t]MP[/t]를 늘립니다. 많이 올릴수록 포인트 하나의 효과는 줄어듭니다.</t>
+          <t>최대 HP 이후</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>tab.lbl.max_hp</t>
+          <t>cards.stat.mp_now</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Max HP</t>
+          <t>Max MP Now</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>최대 HP</t>
+          <t>최대 MP 현재</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>tab.lbl.max_mp</t>
+          <t>cards.stat.mp_after</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Max MP</t>
+          <t>Max MP After</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>최대 MP</t>
-        </is>
-      </c>
-    </row>
-    <row r="1250">
-      <c r="A1250" t="inlineStr">
-        <is>
-          <t>tab.val.level_up</t>
-        </is>
-      </c>
-      <c r="B1250" t="inlineStr">
-        <is>
-          <t>Level Up</t>
-        </is>
-      </c>
-      <c r="C1250" t="inlineStr">
-        <is>
-          <t>레벨 업</t>
+          <t>최대 MP 이후</t>
         </is>
       </c>
     </row>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1269"/>
+  <dimension ref="A1:C1285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -21996,6 +21996,278 @@
         </is>
       </c>
     </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>combat.msg.weak_to</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>{enemy} is weak to [t]{status}[/t]!</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>{enemy}은(는) [t]{status}[/t]에 약합니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>combat.msg.resists</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>{enemy} resists [t]{status}[/t].</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>{enemy}은(는) [t]{status}[/t]에 저항합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>tab.lbl.weak</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>약점</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>tab.lbl.resists</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Resists</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>저항</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>death.tip.status_poison</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Poison killed you: an Antidote cures it.</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>독에 쓰러졌습니다. 해독제로 치료할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>death.tip.status_bleed</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Bleeding hurts when you act: a Bandage stops it.</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>출혈은 행동할 때 피해를 줍니다. 붕대로 멈출 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>death.tip.status_burn</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Burn lowers your DEF while it lasts: Guard to halve the hits.</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>화상이 지속되는 동안 DEF가 낮아집니다. 방어로 피해를 반으로 줄이세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>death.tip.skill_pale_hymn</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>{skill}: [a]BREAK[/a] it before it lands.</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>{skill}: 공격이 닿기 전에 [a]브레이크[/a]시키세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>death.tip.skill_ramming</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>{skill}: [a]BREAK[/a] it first, or Guard and time the defence bar.</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>{skill}: 먼저 [a]브레이크[/a]시키거나, 방어하고 막대의 타이밍을 맞추세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>death.tip.skill_windup</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>{skill} comes after a wind-up: [a]BREAK[/a] it first, or Guard.</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>{skill}은(는) 준비 동작 뒤에 옵니다. 먼저 [a]브레이크[/a]시키거나 방어하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>death.tip.gen_guard</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Guard halves all hits until your next turn and restores {pct}% of max MP.</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>방어는 다음 턴까지 모든 피해를 반으로 줄이고 최대 MP의 {pct}%를 회복합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>death.tip.gen_weak</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Every enemy has a weak point and a resistance. The Codex remembers them.</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>모든 적에게는 약점과 저항이 있습니다. 도감이 기억해 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>death.tip.gen_bed</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Each bed restores all your HP and MP, once per run.</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>침대는 도전마다 한 번, HP와 MP를 모두 회복해 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>death.tip.gen_break</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>When an enemy hits [a]BREAK[/a], it loses a turn and takes {pct}% more damage.</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>적이 [a]브레이크[/a] 상태가 되면 한 턴을 잃고 피해를 {pct}% 더 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>death.tip.gen_smoke</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>A [a]Perfect[/a] Smoke Bomb throw gets you out of any battle but a boss.</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>연막탄을 [a]완벽[/a]하게 던지면 보스 전투를 뺀 모든 전투에서 빠져나갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>death.tip.gen_throw</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>A thrown Firebomb or Poison Pot finds weak points like a skill does.</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>던진 화염병이나 독 항아리도 스킬처럼 약점을 찌릅니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1273"/>
+  <dimension ref="A1:C1281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -22064,6 +22064,142 @@
         </is>
       </c>
     </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>trap.line.trapped</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>It's trapped!</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>함정이다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>trap.bar.prompt</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Disarm it! [k:confirm]</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>해제하자! [k:confirm]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>trap.result.perfect</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Perfect! You disarm the trap and find a bonus item.</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>완벽해! 함정을 해제하고 보너스 아이템을 찾았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>trap.result.fine</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>The trap clicks harmlessly.</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>함정이 아무 일 없이 풀렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>trap.result.weak</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>The trap snaps! You lose {hp} HP.</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>함정이 작동했다! HP를 {hp} 잃었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>trap.result.weak_none</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>The trap snaps, but you barely feel it.</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>함정이 작동했지만 거의 아프지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>tutorial.trap.title</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Trapped Chest</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>함정 상자</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>tutorial.trap.body</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Each floor has one trapped chest. Press [k:confirm] on the bright zone: Perfect finds a bonus, Weak costs HP. You keep the chest's item.</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>층마다 함정 상자가 하나 있습니다. 밝은 구간에서 [k:confirm]을(를) 누르세요. 완벽은 보너스, 약함은 HP 손실입니다. 상자 속 아이템은 그대로 얻습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1297"/>
+  <dimension ref="A1:C1308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -22472,6 +22472,193 @@
         </is>
       </c>
     </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>pause.option.save</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>저장하기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>pause.option.save_quit</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Save &amp; Quit to Title</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>저장하고 타이틀로 나가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>pause.help.save</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Saves your run now. Continue picks it up from here.</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>지금 도전을 저장합니다. 이어하기로 여기서부터 계속할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>pause.help.save_quit</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Saves your run, then goes to the title. Continue picks it up from here.</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>도전을 저장하고 타이틀로 갑니다. 이어하기로 여기서부터 계속할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>tab.system.save_battle</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>You cannot save during a battle.</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>전투 중에는 저장할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>tab.system.save_cutscene</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>You cannot save during a cutscene.</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>컷신 중에는 저장할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>tab.system.save_none</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>There is no run to save.</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>저장할 도전이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>tab.system.save_busy</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>You cannot save right now.</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>지금은 저장할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>save.done</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Game saved.</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>게임이 저장되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>save.failed</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>The game could not be saved.</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>게임을 저장하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>confirm.save_quit</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Save and quit to title? Continue picks it up from here.</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>저장하고 타이틀로 나갈까요? 이어하기로 여기서부터 계속할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -21953,12 +21953,12 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Gold = your class grows these</t>
+          <t>Gold numbers: your class's growth</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>금색 = 직업이 성장시키는 능력치</t>
+          <t>금색 숫자: 직업의 성장</t>
         </is>
       </c>
     </row>
